--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2691,6 +2691,4929 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122841912</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>584384</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6320970</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122851862</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>584360</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6320915</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122839339</v>
+      </c>
+      <c r="B20" t="n">
+        <v>95118</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>584548</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6320905</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122840491</v>
+      </c>
+      <c r="B21" t="n">
+        <v>95118</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gränsborg, Gränsborg, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>584478</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6320912</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122851640</v>
+      </c>
+      <c r="B22" t="n">
+        <v>105453</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>584396</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6320930</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122851716</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>584419</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6320935</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122851741</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>584357</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6320937</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122851575</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>584415</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6320915</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122851540</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>584425</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6320900</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122842080</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vidflagen, Vidflagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>584434</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6320937</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122841088</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>584332</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6320935</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122840763</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>584289</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6320925</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122841518</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>584376</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6320937</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122851562</v>
+      </c>
+      <c r="B31" t="n">
+        <v>105453</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>584415</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6320915</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122851623</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>584406</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6320924</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122851479</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58156</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>584584</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6320910</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122851811</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>584350</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6320916</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122841878</v>
+      </c>
+      <c r="B35" t="n">
+        <v>105453</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Vidflagen, Vidflagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>584427</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6320982</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122851869</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>584369</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6320904</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122851927</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>584411</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6320904</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122839920</v>
+      </c>
+      <c r="B38" t="n">
+        <v>95118</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>584525</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6320880</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122851504</v>
+      </c>
+      <c r="B39" t="n">
+        <v>95118</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>584532</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6320881</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122840279</v>
+      </c>
+      <c r="B40" t="n">
+        <v>105453</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>584419</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6320836</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122851605</v>
+      </c>
+      <c r="B41" t="n">
+        <v>105453</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>584395</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6320916</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122851829</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>584348</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6320915</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122851469</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>584584</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6320910</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122841596</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Vidflagen, Vidflagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>584389</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6320931</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122841069</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>584349</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6320925</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122851724</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>584375</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6320924</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122841328</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>584336</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6320932</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>122841409</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>584384</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6320921</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>122841582</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>584345</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6320948</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122841533</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>584369</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6320926</v>
+      </c>
+      <c r="S50" t="n">
+        <v>20</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>122851662</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>584391</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6320923</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122851599</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>584395</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6320916</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>122851735</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>584357</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6320937</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>122851756</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>584359</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6320919</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>122839190</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>584581</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6320913</v>
+      </c>
+      <c r="S55" t="n">
+        <v>20</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>122851590</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>584409</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6320920</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>122841855</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Vidflagen, Vidflagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>584419</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6320986</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>122840797</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Spetalehult, Spetalehult, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>584406</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6320860</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>122840605</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>584384</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6320873</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>122851783</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57369</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>584336</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6320920</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122841912</v>
+        <v>122851640</v>
       </c>
       <c r="B18" t="n">
-        <v>98347</v>
+        <v>105461</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2705,55 +2705,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584384</v>
+        <v>584396</v>
       </c>
       <c r="R18" t="n">
-        <v>6320970</v>
+        <v>6320930</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2780,39 +2774,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851862</v>
+        <v>122851504</v>
       </c>
       <c r="B19" t="n">
-        <v>98347</v>
+        <v>95126</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2821,32 +2826,28 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -2857,10 +2858,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584360</v>
+        <v>584532</v>
       </c>
       <c r="R19" t="n">
-        <v>6320915</v>
+        <v>6320881</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2930,10 +2931,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122839339</v>
+        <v>122851479</v>
       </c>
       <c r="B20" t="n">
-        <v>95118</v>
+        <v>58156</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2946,37 +2947,49 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584548</v>
+        <v>584584</v>
       </c>
       <c r="R20" t="n">
-        <v>6320905</v>
+        <v>6320910</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3003,9 +3016,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3020,22 +3043,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122840491</v>
+        <v>122851741</v>
       </c>
       <c r="B21" t="n">
-        <v>95118</v>
+        <v>57848</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3048,37 +3071,49 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584478</v>
+        <v>584357</v>
       </c>
       <c r="R21" t="n">
-        <v>6320912</v>
+        <v>6320937</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3105,9 +3140,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3122,22 +3167,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851640</v>
+        <v>122851540</v>
       </c>
       <c r="B22" t="n">
-        <v>105453</v>
+        <v>98355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3146,30 +3191,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -3182,10 +3227,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584396</v>
+        <v>584425</v>
       </c>
       <c r="R22" t="n">
-        <v>6320930</v>
+        <v>6320900</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3255,10 +3300,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122851716</v>
+        <v>122851575</v>
       </c>
       <c r="B23" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3290,7 +3335,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -3303,10 +3348,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584419</v>
+        <v>584415</v>
       </c>
       <c r="R23" t="n">
-        <v>6320935</v>
+        <v>6320915</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3376,10 +3421,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851741</v>
+        <v>122851469</v>
       </c>
       <c r="B24" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3388,39 +3433,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3428,10 +3469,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584357</v>
+        <v>584584</v>
       </c>
       <c r="R24" t="n">
-        <v>6320937</v>
+        <v>6320910</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3482,6 +3523,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3500,10 +3542,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122851575</v>
+        <v>122841855</v>
       </c>
       <c r="B25" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3533,28 +3575,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584415</v>
+        <v>584419</v>
       </c>
       <c r="R25" t="n">
-        <v>6320915</v>
+        <v>6320986</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3581,50 +3615,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122851540</v>
+        <v>122841328</v>
       </c>
       <c r="B26" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3654,28 +3677,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584425</v>
+        <v>584336</v>
       </c>
       <c r="R26" t="n">
-        <v>6320900</v>
+        <v>6320932</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3702,19 +3717,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3723,29 +3733,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122842080</v>
+        <v>122841088</v>
       </c>
       <c r="B27" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3775,17 +3784,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584434</v>
+        <v>584332</v>
       </c>
       <c r="R27" t="n">
-        <v>6320937</v>
+        <v>6320935</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3832,22 +3855,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122841088</v>
+        <v>122841596</v>
       </c>
       <c r="B28" t="n">
-        <v>98347</v>
+        <v>57494</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3856,55 +3879,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584332</v>
+        <v>584389</v>
       </c>
       <c r="R28" t="n">
-        <v>6320935</v>
+        <v>6320931</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3934,6 +3943,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3948,22 +3962,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122840763</v>
+        <v>122841533</v>
       </c>
       <c r="B29" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3972,25 +3986,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4000,13 +4014,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584289</v>
+        <v>584369</v>
       </c>
       <c r="R29" t="n">
-        <v>6320925</v>
+        <v>6320926</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4040,7 +4054,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4067,10 +4081,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122841518</v>
+        <v>122851605</v>
       </c>
       <c r="B30" t="n">
-        <v>98347</v>
+        <v>105461</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4079,55 +4093,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584376</v>
+        <v>584395</v>
       </c>
       <c r="R30" t="n">
-        <v>6320937</v>
+        <v>6320916</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4154,39 +4162,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851562</v>
+        <v>122840763</v>
       </c>
       <c r="B31" t="n">
-        <v>105453</v>
+        <v>57494</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4195,49 +4214,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584415</v>
+        <v>584289</v>
       </c>
       <c r="R31" t="n">
-        <v>6320915</v>
+        <v>6320925</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4264,19 +4275,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4285,29 +4291,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851623</v>
+        <v>122851862</v>
       </c>
       <c r="B32" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4339,7 +4344,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -4352,10 +4357,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584406</v>
+        <v>584360</v>
       </c>
       <c r="R32" t="n">
-        <v>6320924</v>
+        <v>6320915</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4425,10 +4430,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851479</v>
+        <v>122851756</v>
       </c>
       <c r="B33" t="n">
-        <v>58156</v>
+        <v>98355</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4437,39 +4442,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4477,10 +4478,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584584</v>
+        <v>584359</v>
       </c>
       <c r="R33" t="n">
-        <v>6320910</v>
+        <v>6320919</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4531,6 +4532,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4549,10 +4551,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851811</v>
+        <v>122840279</v>
       </c>
       <c r="B34" t="n">
-        <v>98347</v>
+        <v>105461</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4561,49 +4563,45 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584350</v>
+        <v>584419</v>
       </c>
       <c r="R34" t="n">
-        <v>6320916</v>
+        <v>6320836</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4630,50 +4628,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122841878</v>
+        <v>122851724</v>
       </c>
       <c r="B35" t="n">
-        <v>105453</v>
+        <v>98355</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4682,41 +4669,49 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584427</v>
+        <v>584375</v>
       </c>
       <c r="R35" t="n">
-        <v>6320982</v>
+        <v>6320924</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4743,39 +4738,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122851869</v>
+        <v>122851829</v>
       </c>
       <c r="B36" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4807,7 +4813,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -4820,10 +4826,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584369</v>
+        <v>584348</v>
       </c>
       <c r="R36" t="n">
-        <v>6320904</v>
+        <v>6320915</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4893,10 +4899,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851927</v>
+        <v>122851783</v>
       </c>
       <c r="B37" t="n">
-        <v>98347</v>
+        <v>57369</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4905,35 +4911,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4941,10 +4951,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584411</v>
+        <v>584336</v>
       </c>
       <c r="R37" t="n">
-        <v>6320904</v>
+        <v>6320920</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4995,7 +5005,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5014,10 +5023,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122839920</v>
+        <v>122841518</v>
       </c>
       <c r="B38" t="n">
-        <v>95118</v>
+        <v>98355</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5026,41 +5035,55 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584525</v>
+        <v>584376</v>
       </c>
       <c r="R38" t="n">
-        <v>6320880</v>
+        <v>6320937</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5090,11 +5113,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5109,22 +5127,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851504</v>
+        <v>122841069</v>
       </c>
       <c r="B39" t="n">
-        <v>95118</v>
+        <v>98355</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5133,45 +5151,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584532</v>
+        <v>584349</v>
       </c>
       <c r="R39" t="n">
-        <v>6320881</v>
+        <v>6320925</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5198,19 +5212,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5219,29 +5228,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122840279</v>
+        <v>122851735</v>
       </c>
       <c r="B40" t="n">
-        <v>105453</v>
+        <v>98355</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5250,45 +5258,49 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584419</v>
+        <v>584357</v>
       </c>
       <c r="R40" t="n">
-        <v>6320836</v>
+        <v>6320937</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5315,39 +5327,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851605</v>
+        <v>122840491</v>
       </c>
       <c r="B41" t="n">
-        <v>105453</v>
+        <v>95126</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5360,45 +5383,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584395</v>
+        <v>584478</v>
       </c>
       <c r="R41" t="n">
-        <v>6320916</v>
+        <v>6320912</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5425,50 +5440,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851829</v>
+        <v>122851623</v>
       </c>
       <c r="B42" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5500,7 +5504,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -5513,10 +5517,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584348</v>
+        <v>584406</v>
       </c>
       <c r="R42" t="n">
-        <v>6320915</v>
+        <v>6320924</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5586,10 +5590,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851469</v>
+        <v>122839920</v>
       </c>
       <c r="B43" t="n">
-        <v>98347</v>
+        <v>95126</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5598,49 +5602,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584584</v>
+        <v>584525</v>
       </c>
       <c r="R43" t="n">
-        <v>6320910</v>
+        <v>6320880</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5667,19 +5663,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5688,29 +5679,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122841596</v>
+        <v>122839339</v>
       </c>
       <c r="B44" t="n">
-        <v>57494</v>
+        <v>95126</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5719,41 +5709,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584389</v>
+        <v>584548</v>
       </c>
       <c r="R44" t="n">
-        <v>6320931</v>
+        <v>6320905</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5783,11 +5773,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5802,22 +5787,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122841069</v>
+        <v>122842080</v>
       </c>
       <c r="B45" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5850,17 +5835,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584349</v>
+        <v>584434</v>
       </c>
       <c r="R45" t="n">
-        <v>6320925</v>
+        <v>6320937</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5890,11 +5875,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5921,10 +5901,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851724</v>
+        <v>122851811</v>
       </c>
       <c r="B46" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5956,7 +5936,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5969,10 +5949,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584375</v>
+        <v>584350</v>
       </c>
       <c r="R46" t="n">
-        <v>6320924</v>
+        <v>6320916</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6042,10 +6022,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122841328</v>
+        <v>122851590</v>
       </c>
       <c r="B47" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6075,20 +6055,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584336</v>
+        <v>584409</v>
       </c>
       <c r="R47" t="n">
-        <v>6320932</v>
+        <v>6320920</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6115,14 +6103,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6131,18 +6124,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6256,10 +6250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122841582</v>
+        <v>122851562</v>
       </c>
       <c r="B49" t="n">
-        <v>98347</v>
+        <v>105461</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6268,55 +6262,49 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584345</v>
+        <v>584415</v>
       </c>
       <c r="R49" t="n">
-        <v>6320948</v>
+        <v>6320915</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6343,39 +6331,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122841533</v>
+        <v>122840797</v>
       </c>
       <c r="B50" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6408,17 +6407,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584369</v>
+        <v>584406</v>
       </c>
       <c r="R50" t="n">
-        <v>6320926</v>
+        <v>6320860</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6448,11 +6447,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6467,22 +6461,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851662</v>
+        <v>122840605</v>
       </c>
       <c r="B51" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6512,28 +6506,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584391</v>
+        <v>584384</v>
       </c>
       <c r="R51" t="n">
-        <v>6320923</v>
+        <v>6320873</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6560,50 +6546,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851599</v>
+        <v>122839190</v>
       </c>
       <c r="B52" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6633,28 +6608,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584395</v>
+        <v>584581</v>
       </c>
       <c r="R52" t="n">
-        <v>6320916</v>
+        <v>6320913</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6681,50 +6648,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851735</v>
+        <v>122851869</v>
       </c>
       <c r="B53" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6756,7 +6712,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -6769,10 +6725,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584357</v>
+        <v>584369</v>
       </c>
       <c r="R53" t="n">
-        <v>6320937</v>
+        <v>6320904</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6842,10 +6798,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851756</v>
+        <v>122851662</v>
       </c>
       <c r="B54" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6877,7 +6833,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6890,10 +6846,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584359</v>
+        <v>584391</v>
       </c>
       <c r="R54" t="n">
-        <v>6320919</v>
+        <v>6320923</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6963,10 +6919,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122839190</v>
+        <v>122841912</v>
       </c>
       <c r="B55" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6996,20 +6952,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584581</v>
+        <v>584384</v>
       </c>
       <c r="R55" t="n">
-        <v>6320913</v>
+        <v>6320970</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7053,22 +7023,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851590</v>
+        <v>122851599</v>
       </c>
       <c r="B56" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7100,7 +7070,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -7113,10 +7083,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584409</v>
+        <v>584395</v>
       </c>
       <c r="R56" t="n">
-        <v>6320920</v>
+        <v>6320916</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7186,10 +7156,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122841855</v>
+        <v>122851927</v>
       </c>
       <c r="B57" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7219,20 +7189,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584419</v>
+        <v>584411</v>
       </c>
       <c r="R57" t="n">
-        <v>6320986</v>
+        <v>6320904</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7259,39 +7237,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122840797</v>
+        <v>122851716</v>
       </c>
       <c r="B58" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7321,20 +7310,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584406</v>
+        <v>584419</v>
       </c>
       <c r="R58" t="n">
-        <v>6320860</v>
+        <v>6320935</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7361,39 +7358,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122840605</v>
+        <v>122841582</v>
       </c>
       <c r="B59" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7423,20 +7431,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584384</v>
+        <v>584345</v>
       </c>
       <c r="R59" t="n">
-        <v>6320873</v>
+        <v>6320948</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7480,22 +7502,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851783</v>
+        <v>122841878</v>
       </c>
       <c r="B60" t="n">
-        <v>57369</v>
+        <v>105461</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7504,53 +7526,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100001</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584336</v>
+        <v>584427</v>
       </c>
       <c r="R60" t="n">
-        <v>6320920</v>
+        <v>6320982</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7577,19 +7587,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7604,12 +7604,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2814,10 +2814,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851504</v>
+        <v>122851741</v>
       </c>
       <c r="B19" t="n">
-        <v>95126</v>
+        <v>57848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2830,27 +2830,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2858,10 +2866,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584532</v>
+        <v>584357</v>
       </c>
       <c r="R19" t="n">
-        <v>6320881</v>
+        <v>6320937</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2912,7 +2920,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2931,10 +2938,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851479</v>
+        <v>122851504</v>
       </c>
       <c r="B20" t="n">
-        <v>58156</v>
+        <v>95126</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2947,35 +2954,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2983,10 +2982,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584584</v>
+        <v>584532</v>
       </c>
       <c r="R20" t="n">
-        <v>6320910</v>
+        <v>6320881</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3037,6 +3036,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3055,10 +3055,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122851741</v>
+        <v>122851479</v>
       </c>
       <c r="B21" t="n">
-        <v>57848</v>
+        <v>58156</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3071,16 +3071,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3090,14 +3090,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584357</v>
+        <v>584584</v>
       </c>
       <c r="R21" t="n">
-        <v>6320937</v>
+        <v>6320910</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122841596</v>
+        <v>122841533</v>
       </c>
       <c r="B28" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3879,38 +3879,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584389</v>
+        <v>584369</v>
       </c>
       <c r="R28" t="n">
-        <v>6320931</v>
+        <v>6320926</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3974,10 +3974,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122841533</v>
+        <v>122841596</v>
       </c>
       <c r="B29" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3986,38 +3986,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584369</v>
+        <v>584389</v>
       </c>
       <c r="R29" t="n">
-        <v>6320926</v>
+        <v>6320931</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>100-tal plantor</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4202,10 +4202,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122840763</v>
+        <v>122851862</v>
       </c>
       <c r="B31" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4214,41 +4214,49 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584289</v>
+        <v>584360</v>
       </c>
       <c r="R31" t="n">
-        <v>6320925</v>
+        <v>6320915</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4275,14 +4283,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4291,25 +4304,26 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851862</v>
+        <v>122851756</v>
       </c>
       <c r="B32" t="n">
         <v>98355</v>
@@ -4344,7 +4358,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -4357,10 +4371,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584360</v>
+        <v>584359</v>
       </c>
       <c r="R32" t="n">
-        <v>6320915</v>
+        <v>6320919</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4430,10 +4444,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851756</v>
+        <v>122840279</v>
       </c>
       <c r="B33" t="n">
-        <v>98355</v>
+        <v>105461</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4442,49 +4456,45 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584359</v>
+        <v>584419</v>
       </c>
       <c r="R33" t="n">
-        <v>6320919</v>
+        <v>6320836</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4511,50 +4521,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122840279</v>
+        <v>122840763</v>
       </c>
       <c r="B34" t="n">
-        <v>105461</v>
+        <v>57494</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4563,45 +4562,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584419</v>
+        <v>584289</v>
       </c>
       <c r="R34" t="n">
-        <v>6320836</v>
+        <v>6320925</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4631,6 +4626,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851640</v>
+        <v>122851504</v>
       </c>
       <c r="B18" t="n">
-        <v>105461</v>
+        <v>95126</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2709,28 +2709,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -2741,10 +2737,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584396</v>
+        <v>584532</v>
       </c>
       <c r="R18" t="n">
-        <v>6320930</v>
+        <v>6320881</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2814,10 +2810,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851741</v>
+        <v>122851623</v>
       </c>
       <c r="B19" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2826,39 +2822,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2866,10 +2858,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584357</v>
+        <v>584406</v>
       </c>
       <c r="R19" t="n">
-        <v>6320937</v>
+        <v>6320924</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2920,6 +2912,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2938,10 +2931,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851504</v>
+        <v>122851927</v>
       </c>
       <c r="B20" t="n">
-        <v>95126</v>
+        <v>98355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2950,28 +2943,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -2982,10 +2979,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584532</v>
+        <v>584411</v>
       </c>
       <c r="R20" t="n">
-        <v>6320881</v>
+        <v>6320904</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3055,10 +3052,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122851479</v>
+        <v>122851605</v>
       </c>
       <c r="B21" t="n">
-        <v>58156</v>
+        <v>105461</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3071,35 +3068,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103044</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3107,10 +3100,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584584</v>
+        <v>584395</v>
       </c>
       <c r="R21" t="n">
-        <v>6320910</v>
+        <v>6320916</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3161,6 +3154,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3179,7 +3173,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851540</v>
+        <v>122841518</v>
       </c>
       <c r="B22" t="n">
         <v>98355</v>
@@ -3214,26 +3208,32 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584425</v>
+        <v>584376</v>
       </c>
       <c r="R22" t="n">
-        <v>6320900</v>
+        <v>6320937</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3260,47 +3260,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122851575</v>
+        <v>122840605</v>
       </c>
       <c r="B23" t="n">
         <v>98355</v>
@@ -3333,28 +3322,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584415</v>
+        <v>584384</v>
       </c>
       <c r="R23" t="n">
-        <v>6320915</v>
+        <v>6320873</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3381,50 +3362,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851469</v>
+        <v>122840491</v>
       </c>
       <c r="B24" t="n">
-        <v>98355</v>
+        <v>95126</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3433,49 +3403,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584584</v>
+        <v>584478</v>
       </c>
       <c r="R24" t="n">
-        <v>6320910</v>
+        <v>6320912</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3502,47 +3464,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122841855</v>
+        <v>122841069</v>
       </c>
       <c r="B25" t="n">
         <v>98355</v>
@@ -3578,17 +3529,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584419</v>
+        <v>584349</v>
       </c>
       <c r="R25" t="n">
-        <v>6320986</v>
+        <v>6320925</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3618,6 +3569,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3644,10 +3600,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122841328</v>
+        <v>122841409</v>
       </c>
       <c r="B26" t="n">
-        <v>98355</v>
+        <v>57369</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3656,41 +3612,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584336</v>
+        <v>584384</v>
       </c>
       <c r="R26" t="n">
-        <v>6320932</v>
+        <v>6320921</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3720,11 +3681,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3751,7 +3707,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122841088</v>
+        <v>122851540</v>
       </c>
       <c r="B27" t="n">
         <v>98355</v>
@@ -3786,32 +3742,26 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584332</v>
+        <v>584425</v>
       </c>
       <c r="R27" t="n">
-        <v>6320935</v>
+        <v>6320900</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3838,36 +3788,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122841533</v>
+        <v>122851862</v>
       </c>
       <c r="B28" t="n">
         <v>98355</v>
@@ -3900,20 +3861,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584369</v>
+        <v>584360</v>
       </c>
       <c r="R28" t="n">
-        <v>6320926</v>
+        <v>6320915</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3940,14 +3909,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3956,28 +3930,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122841596</v>
+        <v>122839339</v>
       </c>
       <c r="B29" t="n">
-        <v>57494</v>
+        <v>95126</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3986,41 +3961,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584389</v>
+        <v>584548</v>
       </c>
       <c r="R29" t="n">
-        <v>6320931</v>
+        <v>6320905</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4050,11 +4025,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4069,22 +4039,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851605</v>
+        <v>122851869</v>
       </c>
       <c r="B30" t="n">
-        <v>105461</v>
+        <v>98355</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4093,30 +4063,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -4129,10 +4099,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584395</v>
+        <v>584369</v>
       </c>
       <c r="R30" t="n">
-        <v>6320916</v>
+        <v>6320904</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4202,10 +4172,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851862</v>
+        <v>122841596</v>
       </c>
       <c r="B31" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4214,49 +4184,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584360</v>
+        <v>584389</v>
       </c>
       <c r="R31" t="n">
-        <v>6320915</v>
+        <v>6320931</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4283,19 +4245,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4304,29 +4261,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851756</v>
+        <v>122839920</v>
       </c>
       <c r="B32" t="n">
-        <v>98355</v>
+        <v>95126</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4335,49 +4291,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584359</v>
+        <v>584525</v>
       </c>
       <c r="R32" t="n">
-        <v>6320919</v>
+        <v>6320880</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4404,19 +4352,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4425,29 +4368,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122840279</v>
+        <v>122851599</v>
       </c>
       <c r="B33" t="n">
-        <v>105461</v>
+        <v>98355</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4456,45 +4398,49 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584419</v>
+        <v>584395</v>
       </c>
       <c r="R33" t="n">
-        <v>6320836</v>
+        <v>6320916</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4521,39 +4467,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122840763</v>
+        <v>122851469</v>
       </c>
       <c r="B34" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4562,41 +4519,49 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584289</v>
+        <v>584584</v>
       </c>
       <c r="R34" t="n">
-        <v>6320925</v>
+        <v>6320910</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4623,14 +4588,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4639,25 +4609,26 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851724</v>
+        <v>122841088</v>
       </c>
       <c r="B35" t="n">
         <v>98355</v>
@@ -4692,26 +4663,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584375</v>
+        <v>584332</v>
       </c>
       <c r="R35" t="n">
-        <v>6320924</v>
+        <v>6320935</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4738,47 +4715,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122851829</v>
+        <v>122851756</v>
       </c>
       <c r="B36" t="n">
         <v>98355</v>
@@ -4813,7 +4779,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -4826,10 +4792,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584348</v>
+        <v>584359</v>
       </c>
       <c r="R36" t="n">
-        <v>6320915</v>
+        <v>6320919</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4899,10 +4865,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851783</v>
+        <v>122851716</v>
       </c>
       <c r="B37" t="n">
-        <v>57369</v>
+        <v>98355</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4911,39 +4877,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4951,10 +4913,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584336</v>
+        <v>584419</v>
       </c>
       <c r="R37" t="n">
-        <v>6320920</v>
+        <v>6320935</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -5005,6 +4967,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5023,10 +4986,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122841518</v>
+        <v>122840763</v>
       </c>
       <c r="B38" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5035,55 +4998,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584376</v>
+        <v>584289</v>
       </c>
       <c r="R38" t="n">
-        <v>6320937</v>
+        <v>6320925</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5113,6 +5062,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5127,22 +5081,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122841069</v>
+        <v>122851783</v>
       </c>
       <c r="B39" t="n">
-        <v>98355</v>
+        <v>57369</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5151,41 +5105,53 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584349</v>
+        <v>584336</v>
       </c>
       <c r="R39" t="n">
-        <v>6320925</v>
+        <v>6320920</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5212,14 +5178,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5234,19 +5205,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851735</v>
+        <v>122851590</v>
       </c>
       <c r="B40" t="n">
         <v>98355</v>
@@ -5281,7 +5252,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -5294,10 +5265,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584357</v>
+        <v>584409</v>
       </c>
       <c r="R40" t="n">
-        <v>6320937</v>
+        <v>6320920</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5367,10 +5338,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122840491</v>
+        <v>122840797</v>
       </c>
       <c r="B41" t="n">
-        <v>95126</v>
+        <v>98355</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5379,38 +5350,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584478</v>
+        <v>584406</v>
       </c>
       <c r="R41" t="n">
-        <v>6320912</v>
+        <v>6320860</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5469,7 +5440,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851623</v>
+        <v>122842080</v>
       </c>
       <c r="B42" t="n">
         <v>98355</v>
@@ -5502,28 +5473,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584406</v>
+        <v>584434</v>
       </c>
       <c r="R42" t="n">
-        <v>6320924</v>
+        <v>6320937</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5550,50 +5513,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122839920</v>
+        <v>122851741</v>
       </c>
       <c r="B43" t="n">
-        <v>95126</v>
+        <v>57848</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5606,37 +5558,49 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584525</v>
+        <v>584357</v>
       </c>
       <c r="R43" t="n">
-        <v>6320880</v>
+        <v>6320937</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5663,14 +5627,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5685,22 +5654,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122839339</v>
+        <v>122841912</v>
       </c>
       <c r="B44" t="n">
-        <v>95126</v>
+        <v>98355</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5709,38 +5678,52 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584548</v>
+        <v>584384</v>
       </c>
       <c r="R44" t="n">
-        <v>6320905</v>
+        <v>6320970</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5799,7 +5782,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122842080</v>
+        <v>122841533</v>
       </c>
       <c r="B45" t="n">
         <v>98355</v>
@@ -5835,17 +5818,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584434</v>
+        <v>584369</v>
       </c>
       <c r="R45" t="n">
-        <v>6320937</v>
+        <v>6320926</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5875,6 +5858,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5901,7 +5889,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851811</v>
+        <v>122841855</v>
       </c>
       <c r="B46" t="n">
         <v>98355</v>
@@ -5934,28 +5922,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584350</v>
+        <v>584419</v>
       </c>
       <c r="R46" t="n">
-        <v>6320916</v>
+        <v>6320986</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5982,47 +5962,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851590</v>
+        <v>122841328</v>
       </c>
       <c r="B47" t="n">
         <v>98355</v>
@@ -6055,28 +6024,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584409</v>
+        <v>584336</v>
       </c>
       <c r="R47" t="n">
-        <v>6320920</v>
+        <v>6320932</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6103,19 +6064,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6124,29 +6080,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122841409</v>
+        <v>122851662</v>
       </c>
       <c r="B48" t="n">
-        <v>57369</v>
+        <v>98355</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6155,43 +6110,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584384</v>
+        <v>584391</v>
       </c>
       <c r="R48" t="n">
-        <v>6320921</v>
+        <v>6320923</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6221,39 +6179,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851562</v>
+        <v>122851735</v>
       </c>
       <c r="B49" t="n">
-        <v>105461</v>
+        <v>98355</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6262,30 +6231,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -6298,10 +6267,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584415</v>
+        <v>584357</v>
       </c>
       <c r="R49" t="n">
-        <v>6320915</v>
+        <v>6320937</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6371,7 +6340,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122840797</v>
+        <v>122851724</v>
       </c>
       <c r="B50" t="n">
         <v>98355</v>
@@ -6404,20 +6373,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584406</v>
+        <v>584375</v>
       </c>
       <c r="R50" t="n">
-        <v>6320860</v>
+        <v>6320924</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6444,36 +6421,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122840605</v>
+        <v>122851829</v>
       </c>
       <c r="B51" t="n">
         <v>98355</v>
@@ -6506,20 +6494,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584384</v>
+        <v>584348</v>
       </c>
       <c r="R51" t="n">
-        <v>6320873</v>
+        <v>6320915</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6546,39 +6542,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122839190</v>
+        <v>122851479</v>
       </c>
       <c r="B52" t="n">
-        <v>98355</v>
+        <v>58156</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6587,41 +6594,53 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584581</v>
+        <v>584584</v>
       </c>
       <c r="R52" t="n">
-        <v>6320913</v>
+        <v>6320910</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6648,9 +6667,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6665,19 +6694,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851869</v>
+        <v>122839190</v>
       </c>
       <c r="B53" t="n">
         <v>98355</v>
@@ -6710,28 +6739,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584369</v>
+        <v>584581</v>
       </c>
       <c r="R53" t="n">
-        <v>6320904</v>
+        <v>6320913</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6758,50 +6779,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851662</v>
+        <v>122841878</v>
       </c>
       <c r="B54" t="n">
-        <v>98355</v>
+        <v>105461</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6810,49 +6820,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584391</v>
+        <v>584427</v>
       </c>
       <c r="R54" t="n">
-        <v>6320923</v>
+        <v>6320982</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6879,50 +6881,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122841912</v>
+        <v>122851640</v>
       </c>
       <c r="B55" t="n">
-        <v>98355</v>
+        <v>105461</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6931,55 +6922,49 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584384</v>
+        <v>584396</v>
       </c>
       <c r="R55" t="n">
-        <v>6320970</v>
+        <v>6320930</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7006,36 +6991,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851599</v>
+        <v>122851575</v>
       </c>
       <c r="B56" t="n">
         <v>98355</v>
@@ -7070,7 +7066,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -7083,10 +7079,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584395</v>
+        <v>584415</v>
       </c>
       <c r="R56" t="n">
-        <v>6320916</v>
+        <v>6320915</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7156,7 +7152,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851927</v>
+        <v>122841582</v>
       </c>
       <c r="B57" t="n">
         <v>98355</v>
@@ -7191,26 +7187,32 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584411</v>
+        <v>584345</v>
       </c>
       <c r="R57" t="n">
-        <v>6320904</v>
+        <v>6320948</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7237,50 +7239,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122851716</v>
+        <v>122840279</v>
       </c>
       <c r="B58" t="n">
-        <v>98355</v>
+        <v>105461</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7289,49 +7280,45 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
         <v>584419</v>
       </c>
       <c r="R58" t="n">
-        <v>6320935</v>
+        <v>6320836</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7358,47 +7345,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122841582</v>
+        <v>122851811</v>
       </c>
       <c r="B59" t="n">
         <v>98355</v>
@@ -7433,32 +7409,26 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584345</v>
+        <v>584350</v>
       </c>
       <c r="R59" t="n">
-        <v>6320948</v>
+        <v>6320916</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7485,36 +7455,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122841878</v>
+        <v>122851562</v>
       </c>
       <c r="B60" t="n">
         <v>105461</v>
@@ -7547,20 +7528,28 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584427</v>
+        <v>584415</v>
       </c>
       <c r="R60" t="n">
-        <v>6320982</v>
+        <v>6320915</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7587,29 +7576,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851504</v>
+        <v>122851599</v>
       </c>
       <c r="B18" t="n">
-        <v>95126</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2705,28 +2705,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -2737,10 +2741,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584532</v>
+        <v>584395</v>
       </c>
       <c r="R18" t="n">
-        <v>6320881</v>
+        <v>6320916</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2810,10 +2814,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851623</v>
+        <v>122841533</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2843,28 +2847,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584406</v>
+        <v>584369</v>
       </c>
       <c r="R19" t="n">
-        <v>6320924</v>
+        <v>6320926</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2891,19 +2887,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2912,29 +2903,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851927</v>
+        <v>122842080</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2964,28 +2954,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584411</v>
+        <v>584434</v>
       </c>
       <c r="R20" t="n">
-        <v>6320904</v>
+        <v>6320937</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3012,50 +2994,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122851605</v>
+        <v>122840763</v>
       </c>
       <c r="B21" t="n">
-        <v>105461</v>
+        <v>57494</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3064,49 +3035,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584395</v>
+        <v>584289</v>
       </c>
       <c r="R21" t="n">
-        <v>6320916</v>
+        <v>6320925</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3133,19 +3096,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3154,29 +3112,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122841518</v>
+        <v>122841596</v>
       </c>
       <c r="B22" t="n">
-        <v>98355</v>
+        <v>57494</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3185,55 +3142,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584376</v>
+        <v>584389</v>
       </c>
       <c r="R22" t="n">
-        <v>6320937</v>
+        <v>6320931</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3263,6 +3206,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3277,22 +3225,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122840605</v>
+        <v>122851756</v>
       </c>
       <c r="B23" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3322,20 +3270,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584384</v>
+        <v>584359</v>
       </c>
       <c r="R23" t="n">
-        <v>6320873</v>
+        <v>6320919</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3362,39 +3318,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122840491</v>
+        <v>122841328</v>
       </c>
       <c r="B24" t="n">
-        <v>95126</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3403,41 +3370,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584478</v>
+        <v>584336</v>
       </c>
       <c r="R24" t="n">
-        <v>6320912</v>
+        <v>6320932</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3467,6 +3434,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3481,12 +3453,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3496,7 +3468,7 @@
         <v>122841069</v>
       </c>
       <c r="B25" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3600,10 +3572,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122841409</v>
+        <v>122851575</v>
       </c>
       <c r="B26" t="n">
-        <v>57369</v>
+        <v>98357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3612,43 +3584,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584384</v>
+        <v>584415</v>
       </c>
       <c r="R26" t="n">
-        <v>6320921</v>
+        <v>6320915</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3678,39 +3653,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851540</v>
+        <v>122851469</v>
       </c>
       <c r="B27" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3755,10 +3741,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584425</v>
+        <v>584584</v>
       </c>
       <c r="R27" t="n">
-        <v>6320900</v>
+        <v>6320910</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3828,10 +3814,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122851862</v>
+        <v>122851562</v>
       </c>
       <c r="B28" t="n">
-        <v>98355</v>
+        <v>105463</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3840,30 +3826,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3876,7 +3862,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584360</v>
+        <v>584415</v>
       </c>
       <c r="R28" t="n">
         <v>6320915</v>
@@ -3949,10 +3935,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122839339</v>
+        <v>122841518</v>
       </c>
       <c r="B29" t="n">
-        <v>95126</v>
+        <v>98357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3961,41 +3947,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584548</v>
+        <v>584376</v>
       </c>
       <c r="R29" t="n">
-        <v>6320905</v>
+        <v>6320937</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4051,10 +4051,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851869</v>
+        <v>122840279</v>
       </c>
       <c r="B30" t="n">
-        <v>98355</v>
+        <v>105463</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4063,49 +4063,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584369</v>
+        <v>584419</v>
       </c>
       <c r="R30" t="n">
-        <v>6320904</v>
+        <v>6320836</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4132,50 +4128,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122841596</v>
+        <v>122840491</v>
       </c>
       <c r="B31" t="n">
-        <v>57494</v>
+        <v>95128</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4184,41 +4169,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584389</v>
+        <v>584478</v>
       </c>
       <c r="R31" t="n">
-        <v>6320931</v>
+        <v>6320912</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4248,11 +4233,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4267,22 +4247,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122839920</v>
+        <v>122851862</v>
       </c>
       <c r="B32" t="n">
-        <v>95126</v>
+        <v>98357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4291,41 +4271,49 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584525</v>
+        <v>584360</v>
       </c>
       <c r="R32" t="n">
-        <v>6320880</v>
+        <v>6320915</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4352,14 +4340,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4368,28 +4361,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851599</v>
+        <v>122851590</v>
       </c>
       <c r="B33" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4421,7 +4415,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4434,10 +4428,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584395</v>
+        <v>584409</v>
       </c>
       <c r="R33" t="n">
-        <v>6320916</v>
+        <v>6320920</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4507,10 +4501,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851469</v>
+        <v>122851716</v>
       </c>
       <c r="B34" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4542,7 +4536,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -4555,10 +4549,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584584</v>
+        <v>584419</v>
       </c>
       <c r="R34" t="n">
-        <v>6320910</v>
+        <v>6320935</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4628,10 +4622,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122841088</v>
+        <v>122841582</v>
       </c>
       <c r="B35" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4663,7 +4657,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4678,17 +4672,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584332</v>
+        <v>584345</v>
       </c>
       <c r="R35" t="n">
-        <v>6320935</v>
+        <v>6320948</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4744,10 +4738,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122851756</v>
+        <v>122841855</v>
       </c>
       <c r="B36" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4777,28 +4771,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584359</v>
+        <v>584419</v>
       </c>
       <c r="R36" t="n">
-        <v>6320919</v>
+        <v>6320986</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4825,50 +4811,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851716</v>
+        <v>122851724</v>
       </c>
       <c r="B37" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4900,7 +4875,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -4913,10 +4888,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584419</v>
+        <v>584375</v>
       </c>
       <c r="R37" t="n">
-        <v>6320935</v>
+        <v>6320924</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4986,10 +4961,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122840763</v>
+        <v>122851662</v>
       </c>
       <c r="B38" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4998,41 +4973,49 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584289</v>
+        <v>584391</v>
       </c>
       <c r="R38" t="n">
-        <v>6320925</v>
+        <v>6320923</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5059,14 +5042,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5075,28 +5063,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851783</v>
+        <v>122851829</v>
       </c>
       <c r="B39" t="n">
-        <v>57369</v>
+        <v>98357</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5105,39 +5094,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5145,10 +5130,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584336</v>
+        <v>584348</v>
       </c>
       <c r="R39" t="n">
-        <v>6320920</v>
+        <v>6320915</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5199,6 +5184,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5217,10 +5203,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851590</v>
+        <v>122851741</v>
       </c>
       <c r="B40" t="n">
-        <v>98355</v>
+        <v>57848</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5229,25 +5215,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5255,9 +5241,13 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5265,10 +5255,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584409</v>
+        <v>584357</v>
       </c>
       <c r="R40" t="n">
-        <v>6320920</v>
+        <v>6320937</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5319,7 +5309,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5341,7 +5330,7 @@
         <v>122840797</v>
       </c>
       <c r="B41" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5440,10 +5429,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122842080</v>
+        <v>122851811</v>
       </c>
       <c r="B42" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5473,20 +5462,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584434</v>
+        <v>584350</v>
       </c>
       <c r="R42" t="n">
-        <v>6320937</v>
+        <v>6320916</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5513,39 +5510,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851741</v>
+        <v>122851927</v>
       </c>
       <c r="B43" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5554,39 +5562,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5594,10 +5598,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584357</v>
+        <v>584411</v>
       </c>
       <c r="R43" t="n">
-        <v>6320937</v>
+        <v>6320904</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5648,6 +5652,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5666,10 +5671,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122841912</v>
+        <v>122841088</v>
       </c>
       <c r="B44" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5701,7 +5706,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5716,17 +5721,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584384</v>
+        <v>584332</v>
       </c>
       <c r="R44" t="n">
-        <v>6320970</v>
+        <v>6320935</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5782,10 +5787,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122841533</v>
+        <v>122841878</v>
       </c>
       <c r="B45" t="n">
-        <v>98355</v>
+        <v>105463</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5794,41 +5799,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584369</v>
+        <v>584427</v>
       </c>
       <c r="R45" t="n">
-        <v>6320926</v>
+        <v>6320982</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5858,11 +5863,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5889,10 +5889,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122841855</v>
+        <v>122851504</v>
       </c>
       <c r="B46" t="n">
-        <v>98355</v>
+        <v>95128</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5901,41 +5901,45 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584419</v>
+        <v>584532</v>
       </c>
       <c r="R46" t="n">
-        <v>6320986</v>
+        <v>6320881</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5962,39 +5966,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122841328</v>
+        <v>122851640</v>
       </c>
       <c r="B47" t="n">
-        <v>98355</v>
+        <v>105463</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6003,41 +6018,49 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584336</v>
+        <v>584396</v>
       </c>
       <c r="R47" t="n">
-        <v>6320932</v>
+        <v>6320930</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6064,14 +6087,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6080,28 +6108,29 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851662</v>
+        <v>122851623</v>
       </c>
       <c r="B48" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6133,7 +6162,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -6146,10 +6175,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584391</v>
+        <v>584406</v>
       </c>
       <c r="R48" t="n">
-        <v>6320923</v>
+        <v>6320924</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6219,10 +6248,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851735</v>
+        <v>122839190</v>
       </c>
       <c r="B49" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6252,28 +6281,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584357</v>
+        <v>584581</v>
       </c>
       <c r="R49" t="n">
-        <v>6320937</v>
+        <v>6320913</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6300,50 +6321,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851724</v>
+        <v>122839339</v>
       </c>
       <c r="B50" t="n">
-        <v>98355</v>
+        <v>95128</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6352,49 +6362,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584375</v>
+        <v>584548</v>
       </c>
       <c r="R50" t="n">
-        <v>6320924</v>
+        <v>6320905</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6421,50 +6423,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851829</v>
+        <v>122851869</v>
       </c>
       <c r="B51" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6496,7 +6487,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -6509,10 +6500,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584348</v>
+        <v>584369</v>
       </c>
       <c r="R51" t="n">
-        <v>6320915</v>
+        <v>6320904</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6582,10 +6573,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851479</v>
+        <v>122851605</v>
       </c>
       <c r="B52" t="n">
-        <v>58156</v>
+        <v>105463</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6598,35 +6589,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103044</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6634,10 +6621,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584584</v>
+        <v>584395</v>
       </c>
       <c r="R52" t="n">
-        <v>6320910</v>
+        <v>6320916</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6688,6 +6675,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6706,10 +6694,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122839190</v>
+        <v>122839920</v>
       </c>
       <c r="B53" t="n">
-        <v>98355</v>
+        <v>95128</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6718,25 +6706,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6746,10 +6734,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584581</v>
+        <v>584525</v>
       </c>
       <c r="R53" t="n">
-        <v>6320913</v>
+        <v>6320880</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6782,6 +6770,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6808,10 +6801,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122841878</v>
+        <v>122851735</v>
       </c>
       <c r="B54" t="n">
-        <v>105461</v>
+        <v>98357</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6820,41 +6813,49 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584427</v>
+        <v>584357</v>
       </c>
       <c r="R54" t="n">
-        <v>6320982</v>
+        <v>6320937</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6881,39 +6882,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851640</v>
+        <v>122840605</v>
       </c>
       <c r="B55" t="n">
-        <v>105461</v>
+        <v>98357</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6922,49 +6934,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584396</v>
+        <v>584384</v>
       </c>
       <c r="R55" t="n">
-        <v>6320930</v>
+        <v>6320873</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6991,50 +6995,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851575</v>
+        <v>122851783</v>
       </c>
       <c r="B56" t="n">
-        <v>98355</v>
+        <v>57369</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7043,35 +7036,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7079,10 +7076,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584415</v>
+        <v>584336</v>
       </c>
       <c r="R56" t="n">
-        <v>6320915</v>
+        <v>6320920</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7133,7 +7130,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7152,10 +7148,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122841582</v>
+        <v>122851479</v>
       </c>
       <c r="B57" t="n">
-        <v>98355</v>
+        <v>58156</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7164,55 +7160,53 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584345</v>
+        <v>584584</v>
       </c>
       <c r="R57" t="n">
-        <v>6320948</v>
+        <v>6320910</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7239,9 +7233,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7256,22 +7260,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122840279</v>
+        <v>122841912</v>
       </c>
       <c r="B58" t="n">
-        <v>105461</v>
+        <v>98357</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7280,45 +7284,55 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584419</v>
+        <v>584384</v>
       </c>
       <c r="R58" t="n">
-        <v>6320836</v>
+        <v>6320970</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7362,22 +7376,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122851811</v>
+        <v>122841409</v>
       </c>
       <c r="B59" t="n">
-        <v>98355</v>
+        <v>57369</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7386,46 +7400,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584350</v>
+        <v>584384</v>
       </c>
       <c r="R59" t="n">
-        <v>6320916</v>
+        <v>6320921</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7455,50 +7466,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851562</v>
+        <v>122851540</v>
       </c>
       <c r="B60" t="n">
-        <v>105461</v>
+        <v>98357</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7507,30 +7507,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584415</v>
+        <v>584425</v>
       </c>
       <c r="R60" t="n">
-        <v>6320915</v>
+        <v>6320900</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851599</v>
+        <v>122840763</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2705,49 +2705,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584395</v>
+        <v>584289</v>
       </c>
       <c r="R18" t="n">
-        <v>6320916</v>
+        <v>6320925</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2774,19 +2766,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2795,26 +2782,25 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122841533</v>
+        <v>122851599</v>
       </c>
       <c r="B19" t="n">
         <v>98357</v>
@@ -2847,20 +2833,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584369</v>
+        <v>584395</v>
       </c>
       <c r="R19" t="n">
-        <v>6320926</v>
+        <v>6320916</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2887,14 +2881,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2903,25 +2902,26 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122842080</v>
+        <v>122841533</v>
       </c>
       <c r="B20" t="n">
         <v>98357</v>
@@ -2957,17 +2957,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584434</v>
+        <v>584369</v>
       </c>
       <c r="R20" t="n">
-        <v>6320937</v>
+        <v>6320926</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2997,6 +2997,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3023,10 +3028,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122840763</v>
+        <v>122842080</v>
       </c>
       <c r="B21" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3035,41 +3040,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584289</v>
+        <v>584434</v>
       </c>
       <c r="R21" t="n">
-        <v>6320925</v>
+        <v>6320937</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3099,11 +3104,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3130,10 +3130,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122841596</v>
+        <v>122851756</v>
       </c>
       <c r="B22" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3142,41 +3142,49 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584389</v>
+        <v>584359</v>
       </c>
       <c r="R22" t="n">
-        <v>6320931</v>
+        <v>6320919</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3203,14 +3211,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3219,28 +3232,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122851756</v>
+        <v>122841596</v>
       </c>
       <c r="B23" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3249,49 +3263,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584359</v>
+        <v>584389</v>
       </c>
       <c r="R23" t="n">
-        <v>6320919</v>
+        <v>6320931</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3318,19 +3324,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3339,19 +3340,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122851562</v>
+        <v>122841518</v>
       </c>
       <c r="B28" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3826,49 +3826,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584415</v>
+        <v>584376</v>
       </c>
       <c r="R28" t="n">
-        <v>6320915</v>
+        <v>6320937</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3895,50 +3901,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122841518</v>
+        <v>122851562</v>
       </c>
       <c r="B29" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3947,55 +3942,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584376</v>
+        <v>584415</v>
       </c>
       <c r="R29" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4022,29 +4011,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4738,7 +4738,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122841855</v>
+        <v>122851724</v>
       </c>
       <c r="B36" t="n">
         <v>98357</v>
@@ -4771,20 +4771,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584419</v>
+        <v>584375</v>
       </c>
       <c r="R36" t="n">
-        <v>6320986</v>
+        <v>6320924</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4811,36 +4819,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851724</v>
+        <v>122851662</v>
       </c>
       <c r="B37" t="n">
         <v>98357</v>
@@ -4875,7 +4894,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -4888,10 +4907,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584375</v>
+        <v>584391</v>
       </c>
       <c r="R37" t="n">
-        <v>6320924</v>
+        <v>6320923</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4961,7 +4980,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851662</v>
+        <v>122851829</v>
       </c>
       <c r="B38" t="n">
         <v>98357</v>
@@ -4996,7 +5015,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5009,10 +5028,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584391</v>
+        <v>584348</v>
       </c>
       <c r="R38" t="n">
-        <v>6320923</v>
+        <v>6320915</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5082,7 +5101,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851829</v>
+        <v>122841855</v>
       </c>
       <c r="B39" t="n">
         <v>98357</v>
@@ -5115,28 +5134,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584348</v>
+        <v>584419</v>
       </c>
       <c r="R39" t="n">
-        <v>6320915</v>
+        <v>6320986</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5163,40 +5174,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5429,7 +5429,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851811</v>
+        <v>122841088</v>
       </c>
       <c r="B42" t="n">
         <v>98357</v>
@@ -5464,26 +5464,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584350</v>
+        <v>584332</v>
       </c>
       <c r="R42" t="n">
-        <v>6320916</v>
+        <v>6320935</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5510,47 +5516,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851927</v>
+        <v>122851811</v>
       </c>
       <c r="B43" t="n">
         <v>98357</v>
@@ -5585,7 +5580,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -5598,10 +5593,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584411</v>
+        <v>584350</v>
       </c>
       <c r="R43" t="n">
-        <v>6320904</v>
+        <v>6320916</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5671,7 +5666,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122841088</v>
+        <v>122851927</v>
       </c>
       <c r="B44" t="n">
         <v>98357</v>
@@ -5706,32 +5701,26 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584332</v>
+        <v>584411</v>
       </c>
       <c r="R44" t="n">
-        <v>6320935</v>
+        <v>6320904</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5758,29 +5747,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6801,7 +6801,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851735</v>
+        <v>122840605</v>
       </c>
       <c r="B54" t="n">
         <v>98357</v>
@@ -6834,28 +6834,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584357</v>
+        <v>584384</v>
       </c>
       <c r="R54" t="n">
-        <v>6320937</v>
+        <v>6320873</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6882,47 +6874,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122840605</v>
+        <v>122851735</v>
       </c>
       <c r="B55" t="n">
         <v>98357</v>
@@ -6955,20 +6936,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584384</v>
+        <v>584357</v>
       </c>
       <c r="R55" t="n">
-        <v>6320873</v>
+        <v>6320937</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6995,29 +6984,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -4157,10 +4157,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122840491</v>
+        <v>122841582</v>
       </c>
       <c r="B31" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4169,41 +4169,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584478</v>
+        <v>584345</v>
       </c>
       <c r="R31" t="n">
-        <v>6320912</v>
+        <v>6320948</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4259,10 +4273,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851862</v>
+        <v>122840491</v>
       </c>
       <c r="B32" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4271,49 +4285,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584360</v>
+        <v>584478</v>
       </c>
       <c r="R32" t="n">
-        <v>6320915</v>
+        <v>6320912</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4340,47 +4346,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851590</v>
+        <v>122851862</v>
       </c>
       <c r="B33" t="n">
         <v>98357</v>
@@ -4415,7 +4410,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4428,10 +4423,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584409</v>
+        <v>584360</v>
       </c>
       <c r="R33" t="n">
-        <v>6320920</v>
+        <v>6320915</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4501,7 +4496,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851716</v>
+        <v>122851590</v>
       </c>
       <c r="B34" t="n">
         <v>98357</v>
@@ -4536,7 +4531,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -4549,10 +4544,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584419</v>
+        <v>584409</v>
       </c>
       <c r="R34" t="n">
-        <v>6320935</v>
+        <v>6320920</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4622,7 +4617,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122841582</v>
+        <v>122851716</v>
       </c>
       <c r="B35" t="n">
         <v>98357</v>
@@ -4657,32 +4652,26 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584345</v>
+        <v>584419</v>
       </c>
       <c r="R35" t="n">
-        <v>6320948</v>
+        <v>6320935</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4709,36 +4698,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122851724</v>
+        <v>122841855</v>
       </c>
       <c r="B36" t="n">
         <v>98357</v>
@@ -4771,28 +4771,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584375</v>
+        <v>584419</v>
       </c>
       <c r="R36" t="n">
-        <v>6320924</v>
+        <v>6320986</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4819,47 +4811,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851662</v>
+        <v>122851724</v>
       </c>
       <c r="B37" t="n">
         <v>98357</v>
@@ -4894,7 +4875,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -4907,10 +4888,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584391</v>
+        <v>584375</v>
       </c>
       <c r="R37" t="n">
-        <v>6320923</v>
+        <v>6320924</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4980,7 +4961,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851829</v>
+        <v>122851662</v>
       </c>
       <c r="B38" t="n">
         <v>98357</v>
@@ -5015,7 +4996,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5028,10 +5009,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584348</v>
+        <v>584391</v>
       </c>
       <c r="R38" t="n">
-        <v>6320915</v>
+        <v>6320923</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5101,7 +5082,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122841855</v>
+        <v>122851829</v>
       </c>
       <c r="B39" t="n">
         <v>98357</v>
@@ -5134,20 +5115,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584419</v>
+        <v>584348</v>
       </c>
       <c r="R39" t="n">
-        <v>6320986</v>
+        <v>6320915</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5174,29 +5163,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5429,7 +5429,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122841088</v>
+        <v>122851811</v>
       </c>
       <c r="B42" t="n">
         <v>98357</v>
@@ -5464,32 +5464,26 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584332</v>
+        <v>584350</v>
       </c>
       <c r="R42" t="n">
-        <v>6320935</v>
+        <v>6320916</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5516,36 +5510,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851811</v>
+        <v>122851927</v>
       </c>
       <c r="B43" t="n">
         <v>98357</v>
@@ -5580,7 +5585,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -5593,10 +5598,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584350</v>
+        <v>584411</v>
       </c>
       <c r="R43" t="n">
-        <v>6320916</v>
+        <v>6320904</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5666,7 +5671,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122851927</v>
+        <v>122841088</v>
       </c>
       <c r="B44" t="n">
         <v>98357</v>
@@ -5701,26 +5706,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584411</v>
+        <v>584332</v>
       </c>
       <c r="R44" t="n">
-        <v>6320904</v>
+        <v>6320935</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5747,40 +5758,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6801,7 +6801,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122840605</v>
+        <v>122851735</v>
       </c>
       <c r="B54" t="n">
         <v>98357</v>
@@ -6834,20 +6834,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584384</v>
+        <v>584357</v>
       </c>
       <c r="R54" t="n">
-        <v>6320873</v>
+        <v>6320937</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6874,36 +6882,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851735</v>
+        <v>122840605</v>
       </c>
       <c r="B55" t="n">
         <v>98357</v>
@@ -6936,28 +6955,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584357</v>
+        <v>584384</v>
       </c>
       <c r="R55" t="n">
-        <v>6320937</v>
+        <v>6320873</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6984,40 +6995,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -4738,7 +4738,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122841855</v>
+        <v>122851724</v>
       </c>
       <c r="B36" t="n">
         <v>98357</v>
@@ -4771,20 +4771,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584419</v>
+        <v>584375</v>
       </c>
       <c r="R36" t="n">
-        <v>6320986</v>
+        <v>6320924</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4811,36 +4819,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851724</v>
+        <v>122851662</v>
       </c>
       <c r="B37" t="n">
         <v>98357</v>
@@ -4875,7 +4894,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -4888,10 +4907,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584375</v>
+        <v>584391</v>
       </c>
       <c r="R37" t="n">
-        <v>6320924</v>
+        <v>6320923</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4961,7 +4980,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851662</v>
+        <v>122851829</v>
       </c>
       <c r="B38" t="n">
         <v>98357</v>
@@ -4996,7 +5015,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5009,10 +5028,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584391</v>
+        <v>584348</v>
       </c>
       <c r="R38" t="n">
-        <v>6320923</v>
+        <v>6320915</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5082,7 +5101,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851829</v>
+        <v>122841855</v>
       </c>
       <c r="B39" t="n">
         <v>98357</v>
@@ -5115,28 +5134,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584348</v>
+        <v>584419</v>
       </c>
       <c r="R39" t="n">
-        <v>6320915</v>
+        <v>6320986</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5163,40 +5174,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5429,7 +5429,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851811</v>
+        <v>122841088</v>
       </c>
       <c r="B42" t="n">
         <v>98357</v>
@@ -5464,26 +5464,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584350</v>
+        <v>584332</v>
       </c>
       <c r="R42" t="n">
-        <v>6320916</v>
+        <v>6320935</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5510,47 +5516,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851927</v>
+        <v>122851811</v>
       </c>
       <c r="B43" t="n">
         <v>98357</v>
@@ -5585,7 +5580,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -5598,10 +5593,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584411</v>
+        <v>584350</v>
       </c>
       <c r="R43" t="n">
-        <v>6320904</v>
+        <v>6320916</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5671,7 +5666,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122841088</v>
+        <v>122851927</v>
       </c>
       <c r="B44" t="n">
         <v>98357</v>
@@ -5706,32 +5701,26 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584332</v>
+        <v>584411</v>
       </c>
       <c r="R44" t="n">
-        <v>6320935</v>
+        <v>6320904</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5758,29 +5747,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6801,7 +6801,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851735</v>
+        <v>122840605</v>
       </c>
       <c r="B54" t="n">
         <v>98357</v>
@@ -6834,28 +6834,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584357</v>
+        <v>584384</v>
       </c>
       <c r="R54" t="n">
-        <v>6320937</v>
+        <v>6320873</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6882,47 +6874,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122840605</v>
+        <v>122851735</v>
       </c>
       <c r="B55" t="n">
         <v>98357</v>
@@ -6955,20 +6936,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584384</v>
+        <v>584357</v>
       </c>
       <c r="R55" t="n">
-        <v>6320873</v>
+        <v>6320937</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6995,29 +6984,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122840763</v>
+        <v>122841088</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2705,41 +2705,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584289</v>
+        <v>584332</v>
       </c>
       <c r="R18" t="n">
-        <v>6320925</v>
+        <v>6320935</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2769,11 +2783,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2788,19 +2797,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851599</v>
+        <v>122851623</v>
       </c>
       <c r="B19" t="n">
         <v>98357</v>
@@ -2835,7 +2844,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2848,10 +2857,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584395</v>
+        <v>584406</v>
       </c>
       <c r="R19" t="n">
-        <v>6320916</v>
+        <v>6320924</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2921,7 +2930,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841533</v>
+        <v>122851862</v>
       </c>
       <c r="B20" t="n">
         <v>98357</v>
@@ -2954,20 +2963,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584369</v>
+        <v>584360</v>
       </c>
       <c r="R20" t="n">
-        <v>6320926</v>
+        <v>6320915</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2994,14 +3011,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3010,28 +3032,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122842080</v>
+        <v>122851605</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3040,41 +3063,49 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584434</v>
+        <v>584395</v>
       </c>
       <c r="R21" t="n">
-        <v>6320937</v>
+        <v>6320916</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3101,36 +3132,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851756</v>
+        <v>122851590</v>
       </c>
       <c r="B22" t="n">
         <v>98357</v>
@@ -3165,7 +3207,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -3178,10 +3220,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584359</v>
+        <v>584409</v>
       </c>
       <c r="R22" t="n">
-        <v>6320919</v>
+        <v>6320920</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3251,7 +3293,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122841596</v>
+        <v>122840763</v>
       </c>
       <c r="B23" t="n">
         <v>57494</v>
@@ -3287,17 +3329,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584389</v>
+        <v>584289</v>
       </c>
       <c r="R23" t="n">
-        <v>6320931</v>
+        <v>6320925</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3358,7 +3400,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122841328</v>
+        <v>122841518</v>
       </c>
       <c r="B24" t="n">
         <v>98357</v>
@@ -3391,20 +3433,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584336</v>
+        <v>584376</v>
       </c>
       <c r="R24" t="n">
-        <v>6320932</v>
+        <v>6320937</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3434,11 +3490,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3453,22 +3504,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122841069</v>
+        <v>122839920</v>
       </c>
       <c r="B25" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3477,25 +3528,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3505,10 +3556,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584349</v>
+        <v>584525</v>
       </c>
       <c r="R25" t="n">
-        <v>6320925</v>
+        <v>6320880</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3545,7 +3596,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>50-tal plantor</t>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3572,7 +3623,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122851575</v>
+        <v>122851662</v>
       </c>
       <c r="B26" t="n">
         <v>98357</v>
@@ -3607,7 +3658,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -3620,10 +3671,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584415</v>
+        <v>584391</v>
       </c>
       <c r="R26" t="n">
-        <v>6320915</v>
+        <v>6320923</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3693,7 +3744,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851469</v>
+        <v>122851724</v>
       </c>
       <c r="B27" t="n">
         <v>98357</v>
@@ -3728,7 +3779,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -3741,10 +3792,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584584</v>
+        <v>584375</v>
       </c>
       <c r="R27" t="n">
-        <v>6320910</v>
+        <v>6320924</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3814,7 +3865,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122841518</v>
+        <v>122851575</v>
       </c>
       <c r="B28" t="n">
         <v>98357</v>
@@ -3849,32 +3900,26 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584376</v>
+        <v>584415</v>
       </c>
       <c r="R28" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3901,39 +3946,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122851562</v>
+        <v>122839339</v>
       </c>
       <c r="B29" t="n">
-        <v>105463</v>
+        <v>95128</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3946,45 +4002,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584415</v>
+        <v>584548</v>
       </c>
       <c r="R29" t="n">
-        <v>6320915</v>
+        <v>6320905</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4011,47 +4059,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122840279</v>
+        <v>122851640</v>
       </c>
       <c r="B30" t="n">
         <v>105463</v>
@@ -4086,22 +4123,26 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584419</v>
+        <v>584396</v>
       </c>
       <c r="R30" t="n">
-        <v>6320836</v>
+        <v>6320930</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4128,36 +4169,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122841582</v>
+        <v>122840605</v>
       </c>
       <c r="B31" t="n">
         <v>98357</v>
@@ -4190,34 +4242,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584345</v>
+        <v>584384</v>
       </c>
       <c r="R31" t="n">
-        <v>6320948</v>
+        <v>6320873</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4261,12 +4299,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4375,10 +4413,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851862</v>
+        <v>122841878</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4387,49 +4425,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584360</v>
+        <v>584427</v>
       </c>
       <c r="R33" t="n">
-        <v>6320915</v>
+        <v>6320982</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4456,47 +4486,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851590</v>
+        <v>122839190</v>
       </c>
       <c r="B34" t="n">
         <v>98357</v>
@@ -4529,28 +4548,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584409</v>
+        <v>584581</v>
       </c>
       <c r="R34" t="n">
-        <v>6320920</v>
+        <v>6320913</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4577,47 +4588,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851716</v>
+        <v>122841855</v>
       </c>
       <c r="B35" t="n">
         <v>98357</v>
@@ -4650,28 +4650,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
         <v>584419</v>
       </c>
       <c r="R35" t="n">
-        <v>6320935</v>
+        <v>6320986</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4698,50 +4690,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122851724</v>
+        <v>122851479</v>
       </c>
       <c r="B36" t="n">
-        <v>98357</v>
+        <v>58156</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4750,35 +4731,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4786,10 +4771,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584375</v>
+        <v>584584</v>
       </c>
       <c r="R36" t="n">
-        <v>6320924</v>
+        <v>6320910</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4840,7 +4825,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4859,7 +4843,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851662</v>
+        <v>122851540</v>
       </c>
       <c r="B37" t="n">
         <v>98357</v>
@@ -4894,7 +4878,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -4907,10 +4891,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584391</v>
+        <v>584425</v>
       </c>
       <c r="R37" t="n">
-        <v>6320923</v>
+        <v>6320900</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4980,7 +4964,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851829</v>
+        <v>122842080</v>
       </c>
       <c r="B38" t="n">
         <v>98357</v>
@@ -5013,28 +4997,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584348</v>
+        <v>584434</v>
       </c>
       <c r="R38" t="n">
-        <v>6320915</v>
+        <v>6320937</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5061,50 +5037,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122841855</v>
+        <v>122841409</v>
       </c>
       <c r="B39" t="n">
-        <v>98357</v>
+        <v>57369</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5113,41 +5078,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584419</v>
+        <v>584384</v>
       </c>
       <c r="R39" t="n">
-        <v>6320986</v>
+        <v>6320921</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5203,10 +5173,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851741</v>
+        <v>122840797</v>
       </c>
       <c r="B40" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5215,53 +5185,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584357</v>
+        <v>584406</v>
       </c>
       <c r="R40" t="n">
-        <v>6320937</v>
+        <v>6320860</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5288,19 +5246,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5315,22 +5263,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122840797</v>
+        <v>122851504</v>
       </c>
       <c r="B41" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5339,41 +5287,45 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584406</v>
+        <v>584532</v>
       </c>
       <c r="R41" t="n">
-        <v>6320860</v>
+        <v>6320881</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5400,36 +5352,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122841088</v>
+        <v>122851869</v>
       </c>
       <c r="B42" t="n">
         <v>98357</v>
@@ -5464,32 +5427,26 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584332</v>
+        <v>584369</v>
       </c>
       <c r="R42" t="n">
-        <v>6320935</v>
+        <v>6320904</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5516,36 +5473,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851811</v>
+        <v>122841328</v>
       </c>
       <c r="B43" t="n">
         <v>98357</v>
@@ -5578,28 +5546,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584350</v>
+        <v>584336</v>
       </c>
       <c r="R43" t="n">
-        <v>6320916</v>
+        <v>6320932</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5626,19 +5586,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5647,26 +5602,25 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122851927</v>
+        <v>122851811</v>
       </c>
       <c r="B44" t="n">
         <v>98357</v>
@@ -5701,7 +5655,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -5714,10 +5668,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584411</v>
+        <v>584350</v>
       </c>
       <c r="R44" t="n">
-        <v>6320904</v>
+        <v>6320916</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5787,10 +5741,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122841878</v>
+        <v>122841069</v>
       </c>
       <c r="B45" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5799,41 +5753,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584427</v>
+        <v>584349</v>
       </c>
       <c r="R45" t="n">
-        <v>6320982</v>
+        <v>6320925</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5863,6 +5817,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5889,10 +5848,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851504</v>
+        <v>122851562</v>
       </c>
       <c r="B46" t="n">
-        <v>95128</v>
+        <v>105463</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5905,24 +5864,28 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -5933,10 +5896,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584532</v>
+        <v>584415</v>
       </c>
       <c r="R46" t="n">
-        <v>6320881</v>
+        <v>6320915</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6006,10 +5969,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851640</v>
+        <v>122851756</v>
       </c>
       <c r="B47" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6018,30 +5981,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -6054,10 +6017,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584396</v>
+        <v>584359</v>
       </c>
       <c r="R47" t="n">
-        <v>6320930</v>
+        <v>6320919</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6127,7 +6090,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851623</v>
+        <v>122851735</v>
       </c>
       <c r="B48" t="n">
         <v>98357</v>
@@ -6162,7 +6125,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -6175,10 +6138,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584406</v>
+        <v>584357</v>
       </c>
       <c r="R48" t="n">
-        <v>6320924</v>
+        <v>6320937</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6248,7 +6211,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122839190</v>
+        <v>122851716</v>
       </c>
       <c r="B49" t="n">
         <v>98357</v>
@@ -6281,20 +6244,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584581</v>
+        <v>584419</v>
       </c>
       <c r="R49" t="n">
-        <v>6320913</v>
+        <v>6320935</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6321,39 +6292,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122839339</v>
+        <v>122851783</v>
       </c>
       <c r="B50" t="n">
-        <v>95128</v>
+        <v>57369</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6362,41 +6344,53 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2180</v>
+        <v>100001</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584548</v>
+        <v>584336</v>
       </c>
       <c r="R50" t="n">
-        <v>6320905</v>
+        <v>6320920</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6423,9 +6417,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6440,22 +6444,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851869</v>
+        <v>122851741</v>
       </c>
       <c r="B51" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6464,35 +6468,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6500,10 +6508,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584369</v>
+        <v>584357</v>
       </c>
       <c r="R51" t="n">
-        <v>6320904</v>
+        <v>6320937</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6554,7 +6562,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6573,10 +6580,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851605</v>
+        <v>122841582</v>
       </c>
       <c r="B52" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6585,49 +6592,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584395</v>
+        <v>584345</v>
       </c>
       <c r="R52" t="n">
-        <v>6320916</v>
+        <v>6320948</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6654,50 +6667,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122839920</v>
+        <v>122841533</v>
       </c>
       <c r="B53" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6706,25 +6708,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6734,10 +6736,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584525</v>
+        <v>584369</v>
       </c>
       <c r="R53" t="n">
-        <v>6320880</v>
+        <v>6320926</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6774,7 +6776,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Stora kuddar</t>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6801,7 +6803,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122840605</v>
+        <v>122841912</v>
       </c>
       <c r="B54" t="n">
         <v>98357</v>
@@ -6834,20 +6836,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>584384</v>
       </c>
       <c r="R54" t="n">
-        <v>6320873</v>
+        <v>6320970</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6891,19 +6907,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851735</v>
+        <v>122851829</v>
       </c>
       <c r="B55" t="n">
         <v>98357</v>
@@ -6938,7 +6954,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -6951,10 +6967,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584357</v>
+        <v>584348</v>
       </c>
       <c r="R55" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7024,10 +7040,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851783</v>
+        <v>122841596</v>
       </c>
       <c r="B56" t="n">
-        <v>57369</v>
+        <v>57494</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7040,16 +7056,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7057,32 +7073,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584336</v>
+        <v>584389</v>
       </c>
       <c r="R56" t="n">
-        <v>6320920</v>
+        <v>6320931</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7109,19 +7113,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7136,22 +7135,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851479</v>
+        <v>122851469</v>
       </c>
       <c r="B57" t="n">
-        <v>58156</v>
+        <v>98357</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7160,39 +7159,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7254,6 +7249,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7272,10 +7268,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122841912</v>
+        <v>122840279</v>
       </c>
       <c r="B58" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7284,55 +7280,45 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584384</v>
+        <v>584419</v>
       </c>
       <c r="R58" t="n">
-        <v>6320970</v>
+        <v>6320836</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7376,22 +7362,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122841409</v>
+        <v>122851599</v>
       </c>
       <c r="B59" t="n">
-        <v>57369</v>
+        <v>98357</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7400,43 +7386,46 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584384</v>
+        <v>584395</v>
       </c>
       <c r="R59" t="n">
-        <v>6320921</v>
+        <v>6320916</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7466,36 +7455,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851540</v>
+        <v>122851927</v>
       </c>
       <c r="B60" t="n">
         <v>98357</v>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584425</v>
+        <v>584411</v>
       </c>
       <c r="R60" t="n">
-        <v>6320900</v>
+        <v>6320904</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -5275,10 +5275,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851504</v>
+        <v>122841328</v>
       </c>
       <c r="B41" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5287,45 +5287,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584532</v>
+        <v>584336</v>
       </c>
       <c r="R41" t="n">
-        <v>6320881</v>
+        <v>6320932</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5352,19 +5348,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5373,19 +5364,18 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5513,10 +5503,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122841328</v>
+        <v>122851504</v>
       </c>
       <c r="B43" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5525,41 +5515,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584336</v>
+        <v>584532</v>
       </c>
       <c r="R43" t="n">
-        <v>6320932</v>
+        <v>6320881</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5586,14 +5580,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5602,18 +5601,19 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5969,7 +5969,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851756</v>
+        <v>122851735</v>
       </c>
       <c r="B47" t="n">
         <v>98357</v>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584359</v>
+        <v>584357</v>
       </c>
       <c r="R47" t="n">
-        <v>6320919</v>
+        <v>6320937</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6090,7 +6090,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851735</v>
+        <v>122851716</v>
       </c>
       <c r="B48" t="n">
         <v>98357</v>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584357</v>
+        <v>584419</v>
       </c>
       <c r="R48" t="n">
-        <v>6320937</v>
+        <v>6320935</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6211,7 +6211,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851716</v>
+        <v>122851756</v>
       </c>
       <c r="B49" t="n">
         <v>98357</v>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584419</v>
+        <v>584359</v>
       </c>
       <c r="R49" t="n">
-        <v>6320935</v>
+        <v>6320919</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122841596</v>
+        <v>122840279</v>
       </c>
       <c r="B56" t="n">
-        <v>57494</v>
+        <v>105463</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7052,38 +7052,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584389</v>
+        <v>584419</v>
       </c>
       <c r="R56" t="n">
-        <v>6320931</v>
+        <v>6320836</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -7116,11 +7120,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7147,10 +7146,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851469</v>
+        <v>122841596</v>
       </c>
       <c r="B57" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7159,49 +7158,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584584</v>
+        <v>584389</v>
       </c>
       <c r="R57" t="n">
-        <v>6320910</v>
+        <v>6320931</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7228,19 +7219,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7249,29 +7235,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122840279</v>
+        <v>122851469</v>
       </c>
       <c r="B58" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7280,45 +7265,49 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584419</v>
+        <v>584584</v>
       </c>
       <c r="R58" t="n">
-        <v>6320836</v>
+        <v>6320910</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7345,29 +7334,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -3986,10 +3986,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122839339</v>
+        <v>122840605</v>
       </c>
       <c r="B29" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3998,41 +3998,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584548</v>
+        <v>584384</v>
       </c>
       <c r="R29" t="n">
-        <v>6320905</v>
+        <v>6320873</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4076,12 +4076,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122840605</v>
+        <v>122839339</v>
       </c>
       <c r="B31" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4221,41 +4221,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584384</v>
+        <v>584548</v>
       </c>
       <c r="R31" t="n">
-        <v>6320873</v>
+        <v>6320905</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4299,22 +4299,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122840491</v>
+        <v>122839190</v>
       </c>
       <c r="B32" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4323,41 +4323,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584478</v>
+        <v>584581</v>
       </c>
       <c r="R32" t="n">
-        <v>6320912</v>
+        <v>6320913</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4401,22 +4401,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122841878</v>
+        <v>122841855</v>
       </c>
       <c r="B33" t="n">
-        <v>105463</v>
+        <v>98357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4425,25 +4425,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584427</v>
+        <v>584419</v>
       </c>
       <c r="R33" t="n">
-        <v>6320982</v>
+        <v>6320986</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4515,10 +4515,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122839190</v>
+        <v>122840491</v>
       </c>
       <c r="B34" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4527,41 +4527,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584581</v>
+        <v>584478</v>
       </c>
       <c r="R34" t="n">
-        <v>6320913</v>
+        <v>6320912</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4605,22 +4605,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122841855</v>
+        <v>122841878</v>
       </c>
       <c r="B35" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4629,25 +4629,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584419</v>
+        <v>584427</v>
       </c>
       <c r="R35" t="n">
-        <v>6320986</v>
+        <v>6320982</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122851479</v>
+        <v>122842080</v>
       </c>
       <c r="B36" t="n">
-        <v>58156</v>
+        <v>98357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4731,53 +4731,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584584</v>
+        <v>584434</v>
       </c>
       <c r="R36" t="n">
-        <v>6320910</v>
+        <v>6320937</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4804,19 +4792,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4831,22 +4809,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851540</v>
+        <v>122851479</v>
       </c>
       <c r="B37" t="n">
-        <v>98357</v>
+        <v>58156</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4855,35 +4833,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4891,10 +4873,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584425</v>
+        <v>584584</v>
       </c>
       <c r="R37" t="n">
-        <v>6320900</v>
+        <v>6320910</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4945,7 +4927,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4964,7 +4945,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122842080</v>
+        <v>122851540</v>
       </c>
       <c r="B38" t="n">
         <v>98357</v>
@@ -4997,20 +4978,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584434</v>
+        <v>584425</v>
       </c>
       <c r="R38" t="n">
-        <v>6320937</v>
+        <v>6320900</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5037,29 +5026,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5275,10 +5275,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122841328</v>
+        <v>122851504</v>
       </c>
       <c r="B41" t="n">
-        <v>98357</v>
+        <v>95128</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5287,41 +5287,45 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584336</v>
+        <v>584532</v>
       </c>
       <c r="R41" t="n">
-        <v>6320932</v>
+        <v>6320881</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5348,14 +5352,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5364,18 +5373,19 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5503,10 +5513,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851504</v>
+        <v>122841328</v>
       </c>
       <c r="B43" t="n">
-        <v>95128</v>
+        <v>98357</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5515,45 +5525,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584532</v>
+        <v>584336</v>
       </c>
       <c r="R43" t="n">
-        <v>6320881</v>
+        <v>6320932</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5580,19 +5586,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5601,19 +5602,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5969,7 +5969,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851735</v>
+        <v>122851756</v>
       </c>
       <c r="B47" t="n">
         <v>98357</v>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584357</v>
+        <v>584359</v>
       </c>
       <c r="R47" t="n">
-        <v>6320937</v>
+        <v>6320919</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6090,7 +6090,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851716</v>
+        <v>122851735</v>
       </c>
       <c r="B48" t="n">
         <v>98357</v>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -6138,10 +6138,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584419</v>
+        <v>584357</v>
       </c>
       <c r="R48" t="n">
-        <v>6320935</v>
+        <v>6320937</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6211,7 +6211,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851756</v>
+        <v>122851716</v>
       </c>
       <c r="B49" t="n">
         <v>98357</v>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584359</v>
+        <v>584419</v>
       </c>
       <c r="R49" t="n">
-        <v>6320919</v>
+        <v>6320935</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6332,10 +6332,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851783</v>
+        <v>122851741</v>
       </c>
       <c r="B50" t="n">
-        <v>57369</v>
+        <v>57848</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6344,20 +6344,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100001</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6367,14 +6367,14 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584336</v>
+        <v>584357</v>
       </c>
       <c r="R50" t="n">
-        <v>6320920</v>
+        <v>6320937</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6456,10 +6456,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851741</v>
+        <v>122851783</v>
       </c>
       <c r="B51" t="n">
-        <v>57848</v>
+        <v>57369</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6468,20 +6468,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>100001</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6491,14 +6491,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584357</v>
+        <v>584336</v>
       </c>
       <c r="R51" t="n">
-        <v>6320937</v>
+        <v>6320920</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122840279</v>
+        <v>122841596</v>
       </c>
       <c r="B56" t="n">
-        <v>105463</v>
+        <v>57494</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7052,42 +7052,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584419</v>
+        <v>584389</v>
       </c>
       <c r="R56" t="n">
-        <v>6320836</v>
+        <v>6320931</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -7120,6 +7116,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7146,10 +7147,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122841596</v>
+        <v>122851469</v>
       </c>
       <c r="B57" t="n">
-        <v>57494</v>
+        <v>98357</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7158,41 +7159,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584389</v>
+        <v>584584</v>
       </c>
       <c r="R57" t="n">
-        <v>6320931</v>
+        <v>6320910</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7219,14 +7228,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7235,28 +7249,29 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122851469</v>
+        <v>122840279</v>
       </c>
       <c r="B58" t="n">
-        <v>98357</v>
+        <v>105463</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7265,49 +7280,45 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584584</v>
+        <v>584419</v>
       </c>
       <c r="R58" t="n">
-        <v>6320910</v>
+        <v>6320836</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7334,40 +7345,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122841088</v>
+        <v>122851927</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2728,32 +2728,26 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584332</v>
+        <v>584411</v>
       </c>
       <c r="R18" t="n">
-        <v>6320935</v>
+        <v>6320904</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2780,39 +2774,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851623</v>
+        <v>122841518</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2844,26 +2849,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584406</v>
+        <v>584376</v>
       </c>
       <c r="R19" t="n">
-        <v>6320924</v>
+        <v>6320937</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2890,50 +2901,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851862</v>
+        <v>122841409</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>57369</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2942,46 +2942,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584360</v>
+        <v>584384</v>
       </c>
       <c r="R20" t="n">
-        <v>6320915</v>
+        <v>6320921</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3011,50 +3008,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122851605</v>
+        <v>122851716</v>
       </c>
       <c r="B21" t="n">
-        <v>105463</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3063,30 +3049,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -3099,10 +3085,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584395</v>
+        <v>584419</v>
       </c>
       <c r="R21" t="n">
-        <v>6320916</v>
+        <v>6320935</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3172,10 +3158,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851590</v>
+        <v>122851869</v>
       </c>
       <c r="B22" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3207,7 +3193,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -3220,10 +3206,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584409</v>
+        <v>584369</v>
       </c>
       <c r="R22" t="n">
-        <v>6320920</v>
+        <v>6320904</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3293,10 +3279,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122840763</v>
+        <v>122851575</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3305,41 +3291,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584289</v>
+        <v>584415</v>
       </c>
       <c r="R23" t="n">
-        <v>6320925</v>
+        <v>6320915</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3366,14 +3360,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3382,28 +3381,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122841518</v>
+        <v>122851811</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3435,32 +3435,26 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584376</v>
+        <v>584350</v>
       </c>
       <c r="R24" t="n">
-        <v>6320937</v>
+        <v>6320916</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3487,39 +3481,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122839920</v>
+        <v>122840797</v>
       </c>
       <c r="B25" t="n">
-        <v>95128</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3528,41 +3533,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584525</v>
+        <v>584406</v>
       </c>
       <c r="R25" t="n">
-        <v>6320880</v>
+        <v>6320860</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3592,11 +3597,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3611,22 +3611,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122851662</v>
+        <v>122840491</v>
       </c>
       <c r="B26" t="n">
-        <v>98357</v>
+        <v>95136</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3635,49 +3635,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584391</v>
+        <v>584478</v>
       </c>
       <c r="R26" t="n">
-        <v>6320923</v>
+        <v>6320912</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3704,50 +3696,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851724</v>
+        <v>122840605</v>
       </c>
       <c r="B27" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3777,28 +3758,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584375</v>
+        <v>584384</v>
       </c>
       <c r="R27" t="n">
-        <v>6320924</v>
+        <v>6320873</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3825,50 +3798,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122851575</v>
+        <v>122851640</v>
       </c>
       <c r="B28" t="n">
-        <v>98357</v>
+        <v>105471</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3877,30 +3839,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3913,10 +3875,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584415</v>
+        <v>584396</v>
       </c>
       <c r="R28" t="n">
-        <v>6320915</v>
+        <v>6320930</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3986,10 +3948,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122840605</v>
+        <v>122851741</v>
       </c>
       <c r="B29" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3998,41 +3960,53 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584384</v>
+        <v>584357</v>
       </c>
       <c r="R29" t="n">
-        <v>6320873</v>
+        <v>6320937</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4059,9 +4033,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4076,22 +4060,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851640</v>
+        <v>122851599</v>
       </c>
       <c r="B30" t="n">
-        <v>105463</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4100,30 +4084,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -4136,10 +4120,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584396</v>
+        <v>584395</v>
       </c>
       <c r="R30" t="n">
-        <v>6320930</v>
+        <v>6320916</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4209,10 +4193,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122839339</v>
+        <v>122851829</v>
       </c>
       <c r="B31" t="n">
-        <v>95128</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4221,41 +4205,49 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584548</v>
+        <v>584348</v>
       </c>
       <c r="R31" t="n">
-        <v>6320905</v>
+        <v>6320915</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4282,39 +4274,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122839190</v>
+        <v>122839339</v>
       </c>
       <c r="B32" t="n">
-        <v>98357</v>
+        <v>95136</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4323,41 +4326,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584581</v>
+        <v>584548</v>
       </c>
       <c r="R32" t="n">
-        <v>6320913</v>
+        <v>6320905</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4401,22 +4404,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122841855</v>
+        <v>122841088</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4446,20 +4449,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584419</v>
+        <v>584332</v>
       </c>
       <c r="R33" t="n">
-        <v>6320986</v>
+        <v>6320935</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4503,22 +4520,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122840491</v>
+        <v>122841582</v>
       </c>
       <c r="B34" t="n">
-        <v>95128</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4527,41 +4544,55 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584478</v>
+        <v>584345</v>
       </c>
       <c r="R34" t="n">
-        <v>6320912</v>
+        <v>6320948</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4617,10 +4648,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122841878</v>
+        <v>122851479</v>
       </c>
       <c r="B35" t="n">
-        <v>105463</v>
+        <v>58156</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4633,37 +4664,49 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>103044</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584427</v>
+        <v>584584</v>
       </c>
       <c r="R35" t="n">
-        <v>6320982</v>
+        <v>6320910</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4690,9 +4733,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4707,22 +4760,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122842080</v>
+        <v>122839920</v>
       </c>
       <c r="B36" t="n">
-        <v>98357</v>
+        <v>95136</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4731,41 +4784,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584434</v>
+        <v>584525</v>
       </c>
       <c r="R36" t="n">
-        <v>6320937</v>
+        <v>6320880</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4795,6 +4848,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4821,10 +4879,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851479</v>
+        <v>122851504</v>
       </c>
       <c r="B37" t="n">
-        <v>58156</v>
+        <v>95136</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4837,35 +4895,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4873,10 +4923,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584584</v>
+        <v>584532</v>
       </c>
       <c r="R37" t="n">
-        <v>6320910</v>
+        <v>6320881</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4927,6 +4977,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4945,10 +4996,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851540</v>
+        <v>122851735</v>
       </c>
       <c r="B38" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4980,7 +5031,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -4993,10 +5044,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584425</v>
+        <v>584357</v>
       </c>
       <c r="R38" t="n">
-        <v>6320900</v>
+        <v>6320937</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5066,10 +5117,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122841409</v>
+        <v>122851562</v>
       </c>
       <c r="B39" t="n">
-        <v>57369</v>
+        <v>105471</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5078,43 +5129,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100001</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584384</v>
+        <v>584415</v>
       </c>
       <c r="R39" t="n">
-        <v>6320921</v>
+        <v>6320915</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5144,39 +5198,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122840797</v>
+        <v>122841533</v>
       </c>
       <c r="B40" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5209,17 +5274,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584406</v>
+        <v>584369</v>
       </c>
       <c r="R40" t="n">
-        <v>6320860</v>
+        <v>6320926</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5249,6 +5314,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5263,22 +5333,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851504</v>
+        <v>122851783</v>
       </c>
       <c r="B41" t="n">
-        <v>95128</v>
+        <v>57369</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5287,31 +5357,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>100001</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5319,10 +5397,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584532</v>
+        <v>584336</v>
       </c>
       <c r="R41" t="n">
-        <v>6320881</v>
+        <v>6320920</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5373,7 +5451,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5392,10 +5469,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851869</v>
+        <v>122851623</v>
       </c>
       <c r="B42" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5427,7 +5504,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -5440,10 +5517,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584369</v>
+        <v>584406</v>
       </c>
       <c r="R42" t="n">
-        <v>6320904</v>
+        <v>6320924</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5513,10 +5590,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122841328</v>
+        <v>122840279</v>
       </c>
       <c r="B43" t="n">
-        <v>98357</v>
+        <v>105471</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5525,38 +5602,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584336</v>
+        <v>584419</v>
       </c>
       <c r="R43" t="n">
-        <v>6320932</v>
+        <v>6320836</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5589,11 +5670,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5620,10 +5696,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122851811</v>
+        <v>122839190</v>
       </c>
       <c r="B44" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5653,28 +5729,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584350</v>
+        <v>584581</v>
       </c>
       <c r="R44" t="n">
-        <v>6320916</v>
+        <v>6320913</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5701,40 +5769,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5744,7 +5801,7 @@
         <v>122841069</v>
       </c>
       <c r="B45" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5848,10 +5905,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851562</v>
+        <v>122851724</v>
       </c>
       <c r="B46" t="n">
-        <v>105463</v>
+        <v>98365</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5860,30 +5917,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5896,10 +5953,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584415</v>
+        <v>584375</v>
       </c>
       <c r="R46" t="n">
-        <v>6320915</v>
+        <v>6320924</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5969,10 +6026,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851756</v>
+        <v>122841328</v>
       </c>
       <c r="B47" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6002,28 +6059,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584359</v>
+        <v>584336</v>
       </c>
       <c r="R47" t="n">
-        <v>6320919</v>
+        <v>6320932</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6050,19 +6099,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6071,29 +6115,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851735</v>
+        <v>122841855</v>
       </c>
       <c r="B48" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6123,28 +6166,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584357</v>
+        <v>584419</v>
       </c>
       <c r="R48" t="n">
-        <v>6320937</v>
+        <v>6320986</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6171,50 +6206,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851716</v>
+        <v>122841596</v>
       </c>
       <c r="B49" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6223,49 +6247,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584419</v>
+        <v>584389</v>
       </c>
       <c r="R49" t="n">
-        <v>6320935</v>
+        <v>6320931</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6292,19 +6308,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6313,29 +6324,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851741</v>
+        <v>122840763</v>
       </c>
       <c r="B50" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6344,20 +6354,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6365,32 +6375,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584357</v>
+        <v>584289</v>
       </c>
       <c r="R50" t="n">
-        <v>6320937</v>
+        <v>6320925</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6417,19 +6415,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6444,22 +6437,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851783</v>
+        <v>122851540</v>
       </c>
       <c r="B51" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6468,39 +6461,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6508,10 +6497,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584336</v>
+        <v>584425</v>
       </c>
       <c r="R51" t="n">
-        <v>6320920</v>
+        <v>6320900</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6562,6 +6551,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6580,10 +6570,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122841582</v>
+        <v>122851756</v>
       </c>
       <c r="B52" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6618,29 +6608,23 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584345</v>
+        <v>584359</v>
       </c>
       <c r="R52" t="n">
-        <v>6320948</v>
+        <v>6320919</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6667,39 +6651,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122841533</v>
+        <v>122851469</v>
       </c>
       <c r="B53" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6729,20 +6724,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584369</v>
+        <v>584584</v>
       </c>
       <c r="R53" t="n">
-        <v>6320926</v>
+        <v>6320910</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6769,14 +6772,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6785,28 +6793,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122841912</v>
+        <v>122851590</v>
       </c>
       <c r="B54" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6838,32 +6847,26 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584384</v>
+        <v>584409</v>
       </c>
       <c r="R54" t="n">
-        <v>6320970</v>
+        <v>6320920</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6890,39 +6893,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851829</v>
+        <v>122851662</v>
       </c>
       <c r="B55" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6954,7 +6968,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -6967,10 +6981,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584348</v>
+        <v>584391</v>
       </c>
       <c r="R55" t="n">
-        <v>6320915</v>
+        <v>6320923</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7040,10 +7054,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122841596</v>
+        <v>122851605</v>
       </c>
       <c r="B56" t="n">
-        <v>57494</v>
+        <v>105471</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7052,41 +7066,49 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584389</v>
+        <v>584395</v>
       </c>
       <c r="R56" t="n">
-        <v>6320931</v>
+        <v>6320916</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7113,14 +7135,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7129,28 +7156,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851469</v>
+        <v>122841878</v>
       </c>
       <c r="B57" t="n">
-        <v>98357</v>
+        <v>105471</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7159,49 +7187,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584584</v>
+        <v>584427</v>
       </c>
       <c r="R57" t="n">
-        <v>6320910</v>
+        <v>6320982</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7228,50 +7248,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122840279</v>
+        <v>122842080</v>
       </c>
       <c r="B58" t="n">
-        <v>105463</v>
+        <v>98365</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7280,45 +7289,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584419</v>
+        <v>584434</v>
       </c>
       <c r="R58" t="n">
-        <v>6320836</v>
+        <v>6320937</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7374,10 +7379,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122851599</v>
+        <v>122841912</v>
       </c>
       <c r="B59" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7409,26 +7414,32 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584395</v>
+        <v>584384</v>
       </c>
       <c r="R59" t="n">
-        <v>6320916</v>
+        <v>6320970</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7455,50 +7466,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851927</v>
+        <v>122851862</v>
       </c>
       <c r="B60" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584411</v>
+        <v>584360</v>
       </c>
       <c r="R60" t="n">
-        <v>6320904</v>
+        <v>6320915</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2814,10 +2814,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122841518</v>
+        <v>122841409</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>57369</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2826,55 +2826,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584376</v>
+        <v>584384</v>
       </c>
       <c r="R19" t="n">
-        <v>6320937</v>
+        <v>6320921</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2918,22 +2909,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841409</v>
+        <v>122841518</v>
       </c>
       <c r="B20" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2942,46 +2933,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584384</v>
+        <v>584376</v>
       </c>
       <c r="R20" t="n">
-        <v>6320921</v>
+        <v>6320937</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3025,12 +3025,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3725,10 +3725,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122840605</v>
+        <v>122851640</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3737,41 +3737,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584384</v>
+        <v>584396</v>
       </c>
       <c r="R27" t="n">
-        <v>6320873</v>
+        <v>6320930</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3798,39 +3806,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122851640</v>
+        <v>122840605</v>
       </c>
       <c r="B28" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3839,49 +3858,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584396</v>
+        <v>584384</v>
       </c>
       <c r="R28" t="n">
-        <v>6320930</v>
+        <v>6320873</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3908,40 +3919,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122839339</v>
+        <v>122841088</v>
       </c>
       <c r="B32" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4326,41 +4326,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584548</v>
+        <v>584332</v>
       </c>
       <c r="R32" t="n">
-        <v>6320905</v>
+        <v>6320935</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4416,7 +4430,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122841088</v>
+        <v>122841582</v>
       </c>
       <c r="B33" t="n">
         <v>98365</v>
@@ -4451,7 +4465,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4466,17 +4480,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584332</v>
+        <v>584345</v>
       </c>
       <c r="R33" t="n">
-        <v>6320935</v>
+        <v>6320948</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4532,10 +4546,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122841582</v>
+        <v>122839339</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4544,52 +4558,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584345</v>
+        <v>584548</v>
       </c>
       <c r="R34" t="n">
-        <v>6320948</v>
+        <v>6320905</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4772,10 +4772,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122839920</v>
+        <v>122841533</v>
       </c>
       <c r="B36" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4784,25 +4784,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584525</v>
+        <v>584369</v>
       </c>
       <c r="R36" t="n">
-        <v>6320880</v>
+        <v>6320926</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Stora kuddar</t>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4879,10 +4879,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851504</v>
+        <v>122851735</v>
       </c>
       <c r="B37" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4891,28 +4891,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -4923,10 +4927,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584532</v>
+        <v>584357</v>
       </c>
       <c r="R37" t="n">
-        <v>6320881</v>
+        <v>6320937</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4996,10 +5000,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851735</v>
+        <v>122851562</v>
       </c>
       <c r="B38" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5008,30 +5012,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5044,10 +5048,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584357</v>
+        <v>584415</v>
       </c>
       <c r="R38" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5117,10 +5121,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851562</v>
+        <v>122839920</v>
       </c>
       <c r="B39" t="n">
-        <v>105471</v>
+        <v>95136</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5133,45 +5137,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584415</v>
+        <v>584525</v>
       </c>
       <c r="R39" t="n">
-        <v>6320915</v>
+        <v>6320880</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5198,19 +5194,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5219,29 +5210,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122841533</v>
+        <v>122851504</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5250,41 +5240,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584369</v>
+        <v>584532</v>
       </c>
       <c r="R40" t="n">
-        <v>6320926</v>
+        <v>6320881</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5311,14 +5305,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5327,28 +5326,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851783</v>
+        <v>122851623</v>
       </c>
       <c r="B41" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5357,39 +5357,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5397,10 +5393,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584336</v>
+        <v>584406</v>
       </c>
       <c r="R41" t="n">
-        <v>6320920</v>
+        <v>6320924</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5451,6 +5447,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5469,10 +5466,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851623</v>
+        <v>122851783</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>57369</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5481,35 +5478,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5517,10 +5518,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584406</v>
+        <v>584336</v>
       </c>
       <c r="R42" t="n">
-        <v>6320924</v>
+        <v>6320920</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5571,7 +5572,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6026,7 +6026,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122841328</v>
+        <v>122851540</v>
       </c>
       <c r="B47" t="n">
         <v>98365</v>
@@ -6059,20 +6059,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584336</v>
+        <v>584425</v>
       </c>
       <c r="R47" t="n">
-        <v>6320932</v>
+        <v>6320900</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6099,14 +6107,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6115,25 +6128,26 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122841855</v>
+        <v>122851756</v>
       </c>
       <c r="B48" t="n">
         <v>98365</v>
@@ -6166,20 +6180,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584419</v>
+        <v>584359</v>
       </c>
       <c r="R48" t="n">
-        <v>6320986</v>
+        <v>6320919</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6206,39 +6228,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122841596</v>
+        <v>122851469</v>
       </c>
       <c r="B49" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6247,41 +6280,49 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584389</v>
+        <v>584584</v>
       </c>
       <c r="R49" t="n">
-        <v>6320931</v>
+        <v>6320910</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6308,14 +6349,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6324,28 +6370,29 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122840763</v>
+        <v>122851590</v>
       </c>
       <c r="B50" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6354,41 +6401,49 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584289</v>
+        <v>584409</v>
       </c>
       <c r="R50" t="n">
-        <v>6320925</v>
+        <v>6320920</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6415,14 +6470,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6431,25 +6491,26 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851540</v>
+        <v>122851662</v>
       </c>
       <c r="B51" t="n">
         <v>98365</v>
@@ -6484,7 +6545,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -6497,10 +6558,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584425</v>
+        <v>584391</v>
       </c>
       <c r="R51" t="n">
-        <v>6320900</v>
+        <v>6320923</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6570,7 +6631,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851756</v>
+        <v>122841328</v>
       </c>
       <c r="B52" t="n">
         <v>98365</v>
@@ -6603,28 +6664,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584359</v>
+        <v>584336</v>
       </c>
       <c r="R52" t="n">
-        <v>6320919</v>
+        <v>6320932</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6651,19 +6704,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6672,26 +6720,25 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851469</v>
+        <v>122841855</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6724,28 +6771,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584584</v>
+        <v>584419</v>
       </c>
       <c r="R53" t="n">
-        <v>6320910</v>
+        <v>6320986</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6772,50 +6811,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851590</v>
+        <v>122851605</v>
       </c>
       <c r="B54" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6824,30 +6852,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6860,10 +6888,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584409</v>
+        <v>584395</v>
       </c>
       <c r="R54" t="n">
-        <v>6320920</v>
+        <v>6320916</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6933,10 +6961,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851662</v>
+        <v>122841596</v>
       </c>
       <c r="B55" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6945,49 +6973,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584391</v>
+        <v>584389</v>
       </c>
       <c r="R55" t="n">
-        <v>6320923</v>
+        <v>6320931</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7014,19 +7034,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7035,29 +7050,28 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851605</v>
+        <v>122840763</v>
       </c>
       <c r="B56" t="n">
-        <v>105471</v>
+        <v>57494</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7066,49 +7080,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584395</v>
+        <v>584289</v>
       </c>
       <c r="R56" t="n">
-        <v>6320916</v>
+        <v>6320925</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7135,19 +7141,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7156,29 +7157,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122841878</v>
+        <v>122851862</v>
       </c>
       <c r="B57" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7187,41 +7187,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584427</v>
+        <v>584360</v>
       </c>
       <c r="R57" t="n">
-        <v>6320982</v>
+        <v>6320915</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7248,39 +7256,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122842080</v>
+        <v>122841878</v>
       </c>
       <c r="B58" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7289,25 +7308,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7317,13 +7336,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584434</v>
+        <v>584427</v>
       </c>
       <c r="R58" t="n">
-        <v>6320937</v>
+        <v>6320982</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7379,7 +7398,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122841912</v>
+        <v>122842080</v>
       </c>
       <c r="B59" t="n">
         <v>98365</v>
@@ -7412,34 +7431,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584384</v>
+        <v>584434</v>
       </c>
       <c r="R59" t="n">
-        <v>6320970</v>
+        <v>6320937</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7483,19 +7488,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851862</v>
+        <v>122841912</v>
       </c>
       <c r="B60" t="n">
         <v>98365</v>
@@ -7530,26 +7535,32 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584360</v>
+        <v>584384</v>
       </c>
       <c r="R60" t="n">
-        <v>6320915</v>
+        <v>6320970</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7576,40 +7587,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2693,7 +2693,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851927</v>
+        <v>122839190</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2726,28 +2726,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584411</v>
+        <v>584581</v>
       </c>
       <c r="R18" t="n">
-        <v>6320904</v>
+        <v>6320913</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2774,50 +2766,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122841409</v>
+        <v>122851662</v>
       </c>
       <c r="B19" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2826,43 +2807,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584384</v>
+        <v>584391</v>
       </c>
       <c r="R19" t="n">
-        <v>6320921</v>
+        <v>6320923</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2892,36 +2876,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841518</v>
+        <v>122841088</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2956,7 +2951,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2971,14 +2966,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584376</v>
+        <v>584332</v>
       </c>
       <c r="R20" t="n">
-        <v>6320937</v>
+        <v>6320935</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3037,7 +3032,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122851716</v>
+        <v>122841328</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -3070,28 +3065,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584419</v>
+        <v>584336</v>
       </c>
       <c r="R21" t="n">
-        <v>6320935</v>
+        <v>6320932</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3118,19 +3105,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3139,26 +3121,25 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851869</v>
+        <v>122840605</v>
       </c>
       <c r="B22" t="n">
         <v>98365</v>
@@ -3191,28 +3172,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584369</v>
+        <v>584384</v>
       </c>
       <c r="R22" t="n">
-        <v>6320904</v>
+        <v>6320873</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3239,47 +3212,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122851575</v>
+        <v>122841069</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3312,28 +3274,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584415</v>
+        <v>584349</v>
       </c>
       <c r="R23" t="n">
-        <v>6320915</v>
+        <v>6320925</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3360,19 +3314,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3381,26 +3330,25 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851811</v>
+        <v>122851623</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3435,7 +3383,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -3448,10 +3396,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584350</v>
+        <v>584406</v>
       </c>
       <c r="R24" t="n">
-        <v>6320916</v>
+        <v>6320924</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3521,7 +3469,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122840797</v>
+        <v>122851862</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3554,20 +3502,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584406</v>
+        <v>584360</v>
       </c>
       <c r="R25" t="n">
-        <v>6320860</v>
+        <v>6320915</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3594,39 +3550,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122840491</v>
+        <v>122841409</v>
       </c>
       <c r="B26" t="n">
-        <v>95136</v>
+        <v>57369</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3635,41 +3602,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>100001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584478</v>
+        <v>584384</v>
       </c>
       <c r="R26" t="n">
-        <v>6320912</v>
+        <v>6320921</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3713,22 +3685,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851640</v>
+        <v>122851575</v>
       </c>
       <c r="B27" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3737,30 +3709,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -3773,10 +3745,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584396</v>
+        <v>584415</v>
       </c>
       <c r="R27" t="n">
-        <v>6320930</v>
+        <v>6320915</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3846,10 +3818,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122840605</v>
+        <v>122840491</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3858,38 +3830,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584384</v>
+        <v>584478</v>
       </c>
       <c r="R28" t="n">
-        <v>6320873</v>
+        <v>6320912</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3936,22 +3908,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122851741</v>
+        <v>122841878</v>
       </c>
       <c r="B29" t="n">
-        <v>57848</v>
+        <v>105471</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3964,49 +3936,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584357</v>
+        <v>584427</v>
       </c>
       <c r="R29" t="n">
-        <v>6320937</v>
+        <v>6320982</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4033,19 +3993,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4060,22 +4010,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851599</v>
+        <v>122839339</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4084,49 +4034,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584395</v>
+        <v>584548</v>
       </c>
       <c r="R30" t="n">
-        <v>6320916</v>
+        <v>6320905</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4153,50 +4095,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851829</v>
+        <v>122851605</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4205,30 +4136,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -4241,10 +4172,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584348</v>
+        <v>584395</v>
       </c>
       <c r="R31" t="n">
-        <v>6320915</v>
+        <v>6320916</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4314,10 +4245,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122841088</v>
+        <v>122851504</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4326,55 +4257,45 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584332</v>
+        <v>584532</v>
       </c>
       <c r="R32" t="n">
-        <v>6320935</v>
+        <v>6320881</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4401,36 +4322,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122841582</v>
+        <v>122841912</v>
       </c>
       <c r="B33" t="n">
         <v>98365</v>
@@ -4465,7 +4397,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4484,10 +4416,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584345</v>
+        <v>584384</v>
       </c>
       <c r="R33" t="n">
-        <v>6320948</v>
+        <v>6320970</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4546,10 +4478,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122839339</v>
+        <v>122851829</v>
       </c>
       <c r="B34" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4558,41 +4490,49 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584548</v>
+        <v>584348</v>
       </c>
       <c r="R34" t="n">
-        <v>6320905</v>
+        <v>6320915</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4619,29 +4559,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4772,10 +4723,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122841533</v>
+        <v>122841596</v>
       </c>
       <c r="B36" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4784,38 +4735,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584369</v>
+        <v>584389</v>
       </c>
       <c r="R36" t="n">
-        <v>6320926</v>
+        <v>6320931</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4852,7 +4803,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>100-tal plantor</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4879,7 +4830,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851735</v>
+        <v>122841582</v>
       </c>
       <c r="B37" t="n">
         <v>98365</v>
@@ -4914,26 +4865,32 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584357</v>
+        <v>584345</v>
       </c>
       <c r="R37" t="n">
-        <v>6320937</v>
+        <v>6320948</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4960,50 +4917,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851562</v>
+        <v>122841855</v>
       </c>
       <c r="B38" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5012,49 +4958,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584415</v>
+        <v>584419</v>
       </c>
       <c r="R38" t="n">
-        <v>6320915</v>
+        <v>6320986</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5081,50 +5019,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122839920</v>
+        <v>122841518</v>
       </c>
       <c r="B39" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5133,41 +5060,55 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584525</v>
+        <v>584376</v>
       </c>
       <c r="R39" t="n">
-        <v>6320880</v>
+        <v>6320937</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5197,11 +5138,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5216,22 +5152,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851504</v>
+        <v>122851599</v>
       </c>
       <c r="B40" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5240,28 +5176,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -5272,10 +5212,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584532</v>
+        <v>584395</v>
       </c>
       <c r="R40" t="n">
-        <v>6320881</v>
+        <v>6320916</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5345,7 +5285,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851623</v>
+        <v>122851540</v>
       </c>
       <c r="B41" t="n">
         <v>98365</v>
@@ -5380,7 +5320,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -5393,10 +5333,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584406</v>
+        <v>584425</v>
       </c>
       <c r="R41" t="n">
-        <v>6320924</v>
+        <v>6320900</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5466,10 +5406,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851783</v>
+        <v>122851724</v>
       </c>
       <c r="B42" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5478,39 +5418,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5518,10 +5454,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584336</v>
+        <v>584375</v>
       </c>
       <c r="R42" t="n">
-        <v>6320920</v>
+        <v>6320924</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5572,6 +5508,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5590,10 +5527,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122840279</v>
+        <v>122851927</v>
       </c>
       <c r="B43" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5602,45 +5539,49 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584419</v>
+        <v>584411</v>
       </c>
       <c r="R43" t="n">
-        <v>6320836</v>
+        <v>6320904</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5667,39 +5608,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122839190</v>
+        <v>122840763</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5708,25 +5660,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5736,13 +5688,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584581</v>
+        <v>584289</v>
       </c>
       <c r="R44" t="n">
-        <v>6320913</v>
+        <v>6320925</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5772,6 +5724,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5798,7 +5755,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122841069</v>
+        <v>122851869</v>
       </c>
       <c r="B45" t="n">
         <v>98365</v>
@@ -5831,20 +5788,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584349</v>
+        <v>584369</v>
       </c>
       <c r="R45" t="n">
-        <v>6320925</v>
+        <v>6320904</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5871,14 +5836,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5887,28 +5857,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851724</v>
+        <v>122851640</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5917,30 +5888,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5953,10 +5924,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584375</v>
+        <v>584396</v>
       </c>
       <c r="R46" t="n">
-        <v>6320924</v>
+        <v>6320930</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6026,10 +5997,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851540</v>
+        <v>122839920</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6038,49 +6009,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584425</v>
+        <v>584525</v>
       </c>
       <c r="R47" t="n">
-        <v>6320900</v>
+        <v>6320880</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6107,19 +6070,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6128,29 +6086,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851756</v>
+        <v>122851783</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>57369</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6159,35 +6116,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6195,10 +6156,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584359</v>
+        <v>584336</v>
       </c>
       <c r="R48" t="n">
-        <v>6320919</v>
+        <v>6320920</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6249,7 +6210,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6268,7 +6228,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851469</v>
+        <v>122851716</v>
       </c>
       <c r="B49" t="n">
         <v>98365</v>
@@ -6303,7 +6263,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -6316,10 +6276,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584584</v>
+        <v>584419</v>
       </c>
       <c r="R49" t="n">
-        <v>6320910</v>
+        <v>6320935</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6389,7 +6349,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851590</v>
+        <v>122842080</v>
       </c>
       <c r="B50" t="n">
         <v>98365</v>
@@ -6422,28 +6382,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584409</v>
+        <v>584434</v>
       </c>
       <c r="R50" t="n">
-        <v>6320920</v>
+        <v>6320937</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6470,50 +6422,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851662</v>
+        <v>122851741</v>
       </c>
       <c r="B51" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6522,35 +6463,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6558,10 +6503,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584391</v>
+        <v>584357</v>
       </c>
       <c r="R51" t="n">
-        <v>6320923</v>
+        <v>6320937</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6612,7 +6557,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6631,7 +6575,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122841328</v>
+        <v>122851469</v>
       </c>
       <c r="B52" t="n">
         <v>98365</v>
@@ -6664,20 +6608,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584336</v>
+        <v>584584</v>
       </c>
       <c r="R52" t="n">
-        <v>6320932</v>
+        <v>6320910</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6704,14 +6656,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6720,25 +6677,26 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122841855</v>
+        <v>122851756</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6771,20 +6729,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584419</v>
+        <v>584359</v>
       </c>
       <c r="R53" t="n">
-        <v>6320986</v>
+        <v>6320919</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6811,39 +6777,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851605</v>
+        <v>122851735</v>
       </c>
       <c r="B54" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6852,30 +6829,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6888,10 +6865,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584395</v>
+        <v>584357</v>
       </c>
       <c r="R54" t="n">
-        <v>6320916</v>
+        <v>6320937</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6961,10 +6938,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122841596</v>
+        <v>122851811</v>
       </c>
       <c r="B55" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6973,41 +6950,49 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584389</v>
+        <v>584350</v>
       </c>
       <c r="R55" t="n">
-        <v>6320931</v>
+        <v>6320916</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7034,14 +7019,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7050,28 +7040,29 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122840763</v>
+        <v>122841533</v>
       </c>
       <c r="B56" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7080,25 +7071,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7108,13 +7099,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584289</v>
+        <v>584369</v>
       </c>
       <c r="R56" t="n">
-        <v>6320925</v>
+        <v>6320926</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7148,7 +7139,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7175,10 +7166,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851862</v>
+        <v>122840279</v>
       </c>
       <c r="B57" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7187,49 +7178,45 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584360</v>
+        <v>584419</v>
       </c>
       <c r="R57" t="n">
-        <v>6320915</v>
+        <v>6320836</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7256,50 +7243,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122841878</v>
+        <v>122840797</v>
       </c>
       <c r="B58" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7308,41 +7284,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584427</v>
+        <v>584406</v>
       </c>
       <c r="R58" t="n">
-        <v>6320982</v>
+        <v>6320860</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7386,22 +7362,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122842080</v>
+        <v>122851562</v>
       </c>
       <c r="B59" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7410,41 +7386,49 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584434</v>
+        <v>584415</v>
       </c>
       <c r="R59" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7471,36 +7455,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122841912</v>
+        <v>122851590</v>
       </c>
       <c r="B60" t="n">
         <v>98365</v>
@@ -7535,32 +7530,26 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584384</v>
+        <v>584409</v>
       </c>
       <c r="R60" t="n">
-        <v>6320970</v>
+        <v>6320920</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7587,29 +7576,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -5527,10 +5527,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851927</v>
+        <v>122840763</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5539,49 +5539,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584411</v>
+        <v>584289</v>
       </c>
       <c r="R43" t="n">
-        <v>6320904</v>
+        <v>6320925</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5608,19 +5600,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5629,29 +5616,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122840763</v>
+        <v>122851927</v>
       </c>
       <c r="B44" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5660,41 +5646,49 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584289</v>
+        <v>584411</v>
       </c>
       <c r="R44" t="n">
-        <v>6320925</v>
+        <v>6320904</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5721,14 +5715,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5737,18 +5736,19 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6696,7 +6696,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851756</v>
+        <v>122851735</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -6744,10 +6744,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584359</v>
+        <v>584357</v>
       </c>
       <c r="R53" t="n">
-        <v>6320919</v>
+        <v>6320937</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6817,7 +6817,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851735</v>
+        <v>122851756</v>
       </c>
       <c r="B54" t="n">
         <v>98365</v>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6865,10 +6865,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584357</v>
+        <v>584359</v>
       </c>
       <c r="R54" t="n">
-        <v>6320937</v>
+        <v>6320919</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2693,7 +2693,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122839190</v>
+        <v>122851623</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2726,20 +2726,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584581</v>
+        <v>584406</v>
       </c>
       <c r="R18" t="n">
-        <v>6320913</v>
+        <v>6320924</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2766,29 +2774,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3032,7 +3051,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122841328</v>
+        <v>122839190</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -3072,10 +3091,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584336</v>
+        <v>584581</v>
       </c>
       <c r="R21" t="n">
-        <v>6320932</v>
+        <v>6320913</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -3108,11 +3127,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3139,7 +3153,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122840605</v>
+        <v>122841328</v>
       </c>
       <c r="B22" t="n">
         <v>98365</v>
@@ -3179,13 +3193,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584384</v>
+        <v>584336</v>
       </c>
       <c r="R22" t="n">
-        <v>6320873</v>
+        <v>6320932</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3215,6 +3229,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3241,7 +3260,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122841069</v>
+        <v>122840605</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3281,13 +3300,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584349</v>
+        <v>584384</v>
       </c>
       <c r="R23" t="n">
-        <v>6320925</v>
+        <v>6320873</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3317,11 +3336,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3348,7 +3362,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851623</v>
+        <v>122841069</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3381,28 +3395,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584406</v>
+        <v>584349</v>
       </c>
       <c r="R24" t="n">
-        <v>6320924</v>
+        <v>6320925</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3429,19 +3435,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3450,19 +3451,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -4946,7 +4946,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122841855</v>
+        <v>122841518</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -4979,20 +4979,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584419</v>
+        <v>584376</v>
       </c>
       <c r="R38" t="n">
-        <v>6320986</v>
+        <v>6320937</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5036,19 +5050,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122841518</v>
+        <v>122841855</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -5081,34 +5095,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584376</v>
+        <v>584419</v>
       </c>
       <c r="R39" t="n">
-        <v>6320937</v>
+        <v>6320986</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5152,12 +5152,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5755,10 +5755,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122851869</v>
+        <v>122839920</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5767,49 +5767,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584369</v>
+        <v>584525</v>
       </c>
       <c r="R45" t="n">
-        <v>6320904</v>
+        <v>6320880</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5836,19 +5828,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5857,19 +5844,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5997,10 +5983,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122839920</v>
+        <v>122851869</v>
       </c>
       <c r="B47" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6009,41 +5995,49 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584525</v>
+        <v>584369</v>
       </c>
       <c r="R47" t="n">
-        <v>6320880</v>
+        <v>6320904</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6070,14 +6064,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6086,18 +6085,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851623</v>
+        <v>122840763</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2705,49 +2705,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584406</v>
+        <v>584289</v>
       </c>
       <c r="R18" t="n">
-        <v>6320924</v>
+        <v>6320925</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2774,19 +2766,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2795,26 +2782,25 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851662</v>
+        <v>122851599</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2849,7 +2835,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2862,10 +2848,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584391</v>
+        <v>584395</v>
       </c>
       <c r="R19" t="n">
-        <v>6320923</v>
+        <v>6320916</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2935,10 +2921,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841088</v>
+        <v>122841596</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2947,55 +2933,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584332</v>
+        <v>584389</v>
       </c>
       <c r="R20" t="n">
-        <v>6320935</v>
+        <v>6320931</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3025,6 +2997,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3039,22 +3016,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122839190</v>
+        <v>122851479</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>58156</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3063,41 +3040,53 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584581</v>
+        <v>584584</v>
       </c>
       <c r="R21" t="n">
-        <v>6320913</v>
+        <v>6320910</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3124,9 +3113,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3141,19 +3140,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122841328</v>
+        <v>122851716</v>
       </c>
       <c r="B22" t="n">
         <v>98365</v>
@@ -3186,20 +3185,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584336</v>
+        <v>584419</v>
       </c>
       <c r="R22" t="n">
-        <v>6320932</v>
+        <v>6320935</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3226,14 +3233,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3242,28 +3254,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122840605</v>
+        <v>122839339</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3272,41 +3285,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584384</v>
+        <v>584548</v>
       </c>
       <c r="R23" t="n">
-        <v>6320873</v>
+        <v>6320905</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3350,22 +3363,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122841069</v>
+        <v>122841409</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>57369</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3374,41 +3387,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584349</v>
+        <v>584384</v>
       </c>
       <c r="R24" t="n">
-        <v>6320925</v>
+        <v>6320921</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3438,11 +3456,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3469,10 +3482,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122851862</v>
+        <v>122840279</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3481,49 +3494,45 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584360</v>
+        <v>584419</v>
       </c>
       <c r="R25" t="n">
-        <v>6320915</v>
+        <v>6320836</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3550,50 +3559,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122841409</v>
+        <v>122841878</v>
       </c>
       <c r="B26" t="n">
-        <v>57369</v>
+        <v>105471</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3602,46 +3600,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100001</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584384</v>
+        <v>584427</v>
       </c>
       <c r="R26" t="n">
-        <v>6320921</v>
+        <v>6320982</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3697,7 +3690,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851575</v>
+        <v>122841088</v>
       </c>
       <c r="B27" t="n">
         <v>98365</v>
@@ -3732,26 +3725,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584415</v>
+        <v>584332</v>
       </c>
       <c r="R27" t="n">
-        <v>6320915</v>
+        <v>6320935</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3778,50 +3777,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122840491</v>
+        <v>122841912</v>
       </c>
       <c r="B28" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3830,41 +3818,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584478</v>
+        <v>584384</v>
       </c>
       <c r="R28" t="n">
-        <v>6320912</v>
+        <v>6320970</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3920,10 +3922,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122841878</v>
+        <v>122851756</v>
       </c>
       <c r="B29" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3932,41 +3934,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584427</v>
+        <v>584359</v>
       </c>
       <c r="R29" t="n">
-        <v>6320982</v>
+        <v>6320919</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3993,39 +4003,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122839339</v>
+        <v>122851811</v>
       </c>
       <c r="B30" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4034,41 +4055,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584548</v>
+        <v>584350</v>
       </c>
       <c r="R30" t="n">
-        <v>6320905</v>
+        <v>6320916</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4095,39 +4124,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851605</v>
+        <v>122851623</v>
       </c>
       <c r="B31" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4136,30 +4176,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -4172,10 +4212,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584395</v>
+        <v>584406</v>
       </c>
       <c r="R31" t="n">
-        <v>6320916</v>
+        <v>6320924</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4245,10 +4285,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851504</v>
+        <v>122851605</v>
       </c>
       <c r="B32" t="n">
-        <v>95136</v>
+        <v>105471</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4261,24 +4301,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -4289,10 +4333,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584532</v>
+        <v>584395</v>
       </c>
       <c r="R32" t="n">
-        <v>6320881</v>
+        <v>6320916</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4362,10 +4406,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122841912</v>
+        <v>122851783</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>57369</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4374,55 +4418,53 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584384</v>
+        <v>584336</v>
       </c>
       <c r="R33" t="n">
-        <v>6320970</v>
+        <v>6320920</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4449,9 +4491,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4466,19 +4518,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851829</v>
+        <v>122851575</v>
       </c>
       <c r="B34" t="n">
         <v>98365</v>
@@ -4513,7 +4565,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -4526,7 +4578,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584348</v>
+        <v>584415</v>
       </c>
       <c r="R34" t="n">
         <v>6320915</v>
@@ -4599,10 +4651,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851479</v>
+        <v>122840491</v>
       </c>
       <c r="B35" t="n">
-        <v>58156</v>
+        <v>95136</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4615,49 +4667,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584584</v>
+        <v>584478</v>
       </c>
       <c r="R35" t="n">
-        <v>6320910</v>
+        <v>6320912</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4684,19 +4724,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4711,22 +4741,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122841596</v>
+        <v>122841069</v>
       </c>
       <c r="B36" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4735,38 +4765,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584389</v>
+        <v>584349</v>
       </c>
       <c r="R36" t="n">
-        <v>6320931</v>
+        <v>6320925</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4803,7 +4833,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4830,7 +4860,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122841582</v>
+        <v>122839190</v>
       </c>
       <c r="B37" t="n">
         <v>98365</v>
@@ -4863,34 +4893,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584345</v>
+        <v>584581</v>
       </c>
       <c r="R37" t="n">
-        <v>6320948</v>
+        <v>6320913</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4934,19 +4950,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122841518</v>
+        <v>122841582</v>
       </c>
       <c r="B38" t="n">
         <v>98365</v>
@@ -5000,13 +5016,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584376</v>
+        <v>584345</v>
       </c>
       <c r="R38" t="n">
-        <v>6320937</v>
+        <v>6320948</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5062,7 +5078,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122841855</v>
+        <v>122851540</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -5095,20 +5111,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584419</v>
+        <v>584425</v>
       </c>
       <c r="R39" t="n">
-        <v>6320986</v>
+        <v>6320900</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5135,36 +5159,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851599</v>
+        <v>122851829</v>
       </c>
       <c r="B40" t="n">
         <v>98365</v>
@@ -5199,7 +5234,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -5212,10 +5247,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584395</v>
+        <v>584348</v>
       </c>
       <c r="R40" t="n">
-        <v>6320916</v>
+        <v>6320915</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5285,7 +5320,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851540</v>
+        <v>122841533</v>
       </c>
       <c r="B41" t="n">
         <v>98365</v>
@@ -5318,28 +5353,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584425</v>
+        <v>584369</v>
       </c>
       <c r="R41" t="n">
-        <v>6320900</v>
+        <v>6320926</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5366,19 +5393,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5387,29 +5409,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851724</v>
+        <v>122839920</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5418,49 +5439,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584375</v>
+        <v>584525</v>
       </c>
       <c r="R42" t="n">
-        <v>6320924</v>
+        <v>6320880</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5487,19 +5500,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5508,29 +5516,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122840763</v>
+        <v>122851735</v>
       </c>
       <c r="B43" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5539,41 +5546,49 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584289</v>
+        <v>584357</v>
       </c>
       <c r="R43" t="n">
-        <v>6320925</v>
+        <v>6320937</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5600,14 +5615,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5616,25 +5636,26 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122851927</v>
+        <v>122851469</v>
       </c>
       <c r="B44" t="n">
         <v>98365</v>
@@ -5669,7 +5690,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -5682,10 +5703,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584411</v>
+        <v>584584</v>
       </c>
       <c r="R44" t="n">
-        <v>6320904</v>
+        <v>6320910</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5755,10 +5776,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122839920</v>
+        <v>122840605</v>
       </c>
       <c r="B45" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5767,25 +5788,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5795,13 +5816,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584525</v>
+        <v>584384</v>
       </c>
       <c r="R45" t="n">
-        <v>6320880</v>
+        <v>6320873</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5831,11 +5852,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5862,10 +5878,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851640</v>
+        <v>122851927</v>
       </c>
       <c r="B46" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5874,30 +5890,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5910,10 +5926,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584396</v>
+        <v>584411</v>
       </c>
       <c r="R46" t="n">
-        <v>6320930</v>
+        <v>6320904</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5983,7 +5999,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851869</v>
+        <v>122851724</v>
       </c>
       <c r="B47" t="n">
         <v>98365</v>
@@ -6018,7 +6034,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -6031,10 +6047,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584369</v>
+        <v>584375</v>
       </c>
       <c r="R47" t="n">
-        <v>6320904</v>
+        <v>6320924</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6104,10 +6120,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851783</v>
+        <v>122851640</v>
       </c>
       <c r="B48" t="n">
-        <v>57369</v>
+        <v>105471</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6116,39 +6132,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100001</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6156,10 +6168,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584336</v>
+        <v>584396</v>
       </c>
       <c r="R48" t="n">
-        <v>6320920</v>
+        <v>6320930</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6210,6 +6222,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6228,7 +6241,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851716</v>
+        <v>122851869</v>
       </c>
       <c r="B49" t="n">
         <v>98365</v>
@@ -6263,7 +6276,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -6276,10 +6289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584419</v>
+        <v>584369</v>
       </c>
       <c r="R49" t="n">
-        <v>6320935</v>
+        <v>6320904</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6349,7 +6362,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122842080</v>
+        <v>122841328</v>
       </c>
       <c r="B50" t="n">
         <v>98365</v>
@@ -6385,17 +6398,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584434</v>
+        <v>584336</v>
       </c>
       <c r="R50" t="n">
-        <v>6320937</v>
+        <v>6320932</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6425,6 +6438,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6451,10 +6469,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851741</v>
+        <v>122851590</v>
       </c>
       <c r="B51" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6463,25 +6481,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6489,13 +6507,9 @@
           <t>5</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6503,10 +6517,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584357</v>
+        <v>584409</v>
       </c>
       <c r="R51" t="n">
-        <v>6320937</v>
+        <v>6320920</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6557,6 +6571,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6575,10 +6590,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851469</v>
+        <v>122851562</v>
       </c>
       <c r="B52" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6587,30 +6602,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -6623,10 +6638,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584584</v>
+        <v>584415</v>
       </c>
       <c r="R52" t="n">
-        <v>6320910</v>
+        <v>6320915</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6696,7 +6711,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851735</v>
+        <v>122840797</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6729,28 +6744,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584357</v>
+        <v>584406</v>
       </c>
       <c r="R53" t="n">
-        <v>6320937</v>
+        <v>6320860</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6777,47 +6784,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851756</v>
+        <v>122842080</v>
       </c>
       <c r="B54" t="n">
         <v>98365</v>
@@ -6850,28 +6846,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584359</v>
+        <v>584434</v>
       </c>
       <c r="R54" t="n">
-        <v>6320919</v>
+        <v>6320937</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6898,47 +6886,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851811</v>
+        <v>122841855</v>
       </c>
       <c r="B55" t="n">
         <v>98365</v>
@@ -6971,28 +6948,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584350</v>
+        <v>584419</v>
       </c>
       <c r="R55" t="n">
-        <v>6320916</v>
+        <v>6320986</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7019,50 +6988,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122841533</v>
+        <v>122851504</v>
       </c>
       <c r="B56" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7071,41 +7029,45 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584369</v>
+        <v>584532</v>
       </c>
       <c r="R56" t="n">
-        <v>6320926</v>
+        <v>6320881</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7132,14 +7094,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7148,28 +7115,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122840279</v>
+        <v>122851662</v>
       </c>
       <c r="B57" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7178,45 +7146,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584419</v>
+        <v>584391</v>
       </c>
       <c r="R57" t="n">
-        <v>6320836</v>
+        <v>6320923</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7243,36 +7215,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122840797</v>
+        <v>122841518</v>
       </c>
       <c r="B58" t="n">
         <v>98365</v>
@@ -7305,17 +7288,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584406</v>
+        <v>584376</v>
       </c>
       <c r="R58" t="n">
-        <v>6320860</v>
+        <v>6320937</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7374,10 +7371,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122851562</v>
+        <v>122851862</v>
       </c>
       <c r="B59" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7386,30 +7383,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
@@ -7422,7 +7419,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584415</v>
+        <v>584360</v>
       </c>
       <c r="R59" t="n">
         <v>6320915</v>
@@ -7495,10 +7492,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851590</v>
+        <v>122851741</v>
       </c>
       <c r="B60" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7507,25 +7504,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7533,9 +7530,13 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7543,10 +7544,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584409</v>
+        <v>584357</v>
       </c>
       <c r="R60" t="n">
-        <v>6320920</v>
+        <v>6320937</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7597,7 +7598,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122840763</v>
+        <v>122841409</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>57369</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2709,16 +2709,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2727,19 +2727,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584289</v>
+        <v>584384</v>
       </c>
       <c r="R18" t="n">
-        <v>6320925</v>
+        <v>6320921</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2769,11 +2774,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2800,7 +2800,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851599</v>
+        <v>122851735</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584395</v>
+        <v>584357</v>
       </c>
       <c r="R19" t="n">
-        <v>6320916</v>
+        <v>6320937</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841596</v>
+        <v>122841328</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2933,38 +2933,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584389</v>
+        <v>584336</v>
       </c>
       <c r="R20" t="n">
-        <v>6320931</v>
+        <v>6320932</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3028,10 +3028,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122851479</v>
+        <v>122851540</v>
       </c>
       <c r="B21" t="n">
-        <v>58156</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3040,39 +3040,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3080,10 +3076,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584584</v>
+        <v>584425</v>
       </c>
       <c r="R21" t="n">
-        <v>6320910</v>
+        <v>6320900</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3134,6 +3130,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3152,10 +3149,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851716</v>
+        <v>122840491</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3164,49 +3161,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584419</v>
+        <v>584478</v>
       </c>
       <c r="R22" t="n">
-        <v>6320935</v>
+        <v>6320912</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3233,50 +3222,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122839339</v>
+        <v>122851783</v>
       </c>
       <c r="B23" t="n">
-        <v>95136</v>
+        <v>57369</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3285,41 +3263,53 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>100001</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584548</v>
+        <v>584336</v>
       </c>
       <c r="R23" t="n">
-        <v>6320905</v>
+        <v>6320920</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3346,9 +3336,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3363,22 +3363,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122841409</v>
+        <v>122840797</v>
       </c>
       <c r="B24" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3387,46 +3387,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584384</v>
+        <v>584406</v>
       </c>
       <c r="R24" t="n">
-        <v>6320921</v>
+        <v>6320860</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3470,22 +3465,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122840279</v>
+        <v>122851724</v>
       </c>
       <c r="B25" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3494,45 +3489,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584419</v>
+        <v>584375</v>
       </c>
       <c r="R25" t="n">
-        <v>6320836</v>
+        <v>6320924</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3559,39 +3558,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122841878</v>
+        <v>122842080</v>
       </c>
       <c r="B26" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3600,25 +3610,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3628,13 +3638,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584427</v>
+        <v>584434</v>
       </c>
       <c r="R26" t="n">
-        <v>6320982</v>
+        <v>6320937</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3690,7 +3700,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122841088</v>
+        <v>122840605</v>
       </c>
       <c r="B27" t="n">
         <v>98365</v>
@@ -3723,31 +3733,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584332</v>
+        <v>584384</v>
       </c>
       <c r="R27" t="n">
-        <v>6320935</v>
+        <v>6320873</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3794,22 +3790,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122841912</v>
+        <v>122851479</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>58156</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3818,55 +3814,53 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584384</v>
+        <v>584584</v>
       </c>
       <c r="R28" t="n">
-        <v>6320970</v>
+        <v>6320910</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3893,9 +3887,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3910,19 +3914,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122851756</v>
+        <v>122851662</v>
       </c>
       <c r="B29" t="n">
         <v>98365</v>
@@ -3957,7 +3961,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3970,10 +3974,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584359</v>
+        <v>584391</v>
       </c>
       <c r="R29" t="n">
-        <v>6320919</v>
+        <v>6320923</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4043,7 +4047,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851811</v>
+        <v>122851716</v>
       </c>
       <c r="B30" t="n">
         <v>98365</v>
@@ -4078,7 +4082,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -4091,10 +4095,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584350</v>
+        <v>584419</v>
       </c>
       <c r="R30" t="n">
-        <v>6320916</v>
+        <v>6320935</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4164,7 +4168,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851623</v>
+        <v>122851599</v>
       </c>
       <c r="B31" t="n">
         <v>98365</v>
@@ -4199,7 +4203,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -4212,10 +4216,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584406</v>
+        <v>584395</v>
       </c>
       <c r="R31" t="n">
-        <v>6320924</v>
+        <v>6320916</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4285,10 +4289,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851605</v>
+        <v>122851862</v>
       </c>
       <c r="B32" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4297,30 +4301,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -4333,10 +4337,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584395</v>
+        <v>584360</v>
       </c>
       <c r="R32" t="n">
-        <v>6320916</v>
+        <v>6320915</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4406,10 +4410,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851783</v>
+        <v>122851562</v>
       </c>
       <c r="B33" t="n">
-        <v>57369</v>
+        <v>105471</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4418,39 +4422,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100001</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584336</v>
+        <v>584415</v>
       </c>
       <c r="R33" t="n">
-        <v>6320920</v>
+        <v>6320915</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4512,6 +4512,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4530,10 +4531,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851575</v>
+        <v>122839339</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4542,49 +4543,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584415</v>
+        <v>584548</v>
       </c>
       <c r="R34" t="n">
-        <v>6320915</v>
+        <v>6320905</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4611,50 +4604,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122840491</v>
+        <v>122851575</v>
       </c>
       <c r="B35" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4663,41 +4645,49 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584478</v>
+        <v>584415</v>
       </c>
       <c r="R35" t="n">
-        <v>6320912</v>
+        <v>6320915</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4724,39 +4714,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122841069</v>
+        <v>122840763</v>
       </c>
       <c r="B36" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4765,25 +4766,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4793,13 +4794,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584349</v>
+        <v>584289</v>
       </c>
       <c r="R36" t="n">
         <v>6320925</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4833,7 +4834,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>50-tal plantor</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4860,10 +4861,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122839190</v>
+        <v>122839920</v>
       </c>
       <c r="B37" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4872,25 +4873,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4900,10 +4901,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584581</v>
+        <v>584525</v>
       </c>
       <c r="R37" t="n">
-        <v>6320913</v>
+        <v>6320880</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4936,6 +4937,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4962,10 +4968,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122841582</v>
+        <v>122841596</v>
       </c>
       <c r="B38" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4974,55 +4980,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584345</v>
+        <v>584389</v>
       </c>
       <c r="R38" t="n">
-        <v>6320948</v>
+        <v>6320931</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5052,6 +5044,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5066,19 +5063,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851540</v>
+        <v>122851623</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -5113,7 +5110,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -5126,10 +5123,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584425</v>
+        <v>584406</v>
       </c>
       <c r="R39" t="n">
-        <v>6320900</v>
+        <v>6320924</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5199,7 +5196,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851829</v>
+        <v>122851590</v>
       </c>
       <c r="B40" t="n">
         <v>98365</v>
@@ -5234,7 +5231,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -5247,10 +5244,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584348</v>
+        <v>584409</v>
       </c>
       <c r="R40" t="n">
-        <v>6320915</v>
+        <v>6320920</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5320,7 +5317,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122841533</v>
+        <v>122851756</v>
       </c>
       <c r="B41" t="n">
         <v>98365</v>
@@ -5353,20 +5350,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584369</v>
+        <v>584359</v>
       </c>
       <c r="R41" t="n">
-        <v>6320926</v>
+        <v>6320919</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5393,14 +5398,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5409,28 +5419,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122839920</v>
+        <v>122841518</v>
       </c>
       <c r="B42" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5439,41 +5450,55 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584525</v>
+        <v>584376</v>
       </c>
       <c r="R42" t="n">
-        <v>6320880</v>
+        <v>6320937</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5503,11 +5528,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5522,22 +5542,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851735</v>
+        <v>122840279</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5546,49 +5566,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584357</v>
+        <v>584419</v>
       </c>
       <c r="R43" t="n">
-        <v>6320937</v>
+        <v>6320836</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5615,47 +5631,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122851469</v>
+        <v>122841912</v>
       </c>
       <c r="B44" t="n">
         <v>98365</v>
@@ -5690,26 +5695,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584584</v>
+        <v>584384</v>
       </c>
       <c r="R44" t="n">
-        <v>6320910</v>
+        <v>6320970</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5736,50 +5747,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122840605</v>
+        <v>122851504</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5788,41 +5788,45 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584384</v>
+        <v>584532</v>
       </c>
       <c r="R45" t="n">
-        <v>6320873</v>
+        <v>6320881</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5849,39 +5853,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851927</v>
+        <v>122851640</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5890,30 +5905,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5926,10 +5941,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584411</v>
+        <v>584396</v>
       </c>
       <c r="R46" t="n">
-        <v>6320904</v>
+        <v>6320930</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5999,10 +6014,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851724</v>
+        <v>122851605</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6011,30 +6026,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -6047,10 +6062,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584375</v>
+        <v>584395</v>
       </c>
       <c r="R47" t="n">
-        <v>6320924</v>
+        <v>6320916</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6120,10 +6135,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851640</v>
+        <v>122839190</v>
       </c>
       <c r="B48" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6132,49 +6147,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584396</v>
+        <v>584581</v>
       </c>
       <c r="R48" t="n">
-        <v>6320930</v>
+        <v>6320913</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6201,50 +6208,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851869</v>
+        <v>122841878</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6253,49 +6249,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584369</v>
+        <v>584427</v>
       </c>
       <c r="R49" t="n">
-        <v>6320904</v>
+        <v>6320982</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6322,47 +6310,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122841328</v>
+        <v>122841582</v>
       </c>
       <c r="B50" t="n">
         <v>98365</v>
@@ -6395,20 +6372,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584336</v>
+        <v>584345</v>
       </c>
       <c r="R50" t="n">
-        <v>6320932</v>
+        <v>6320948</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6438,11 +6429,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6457,22 +6443,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851590</v>
+        <v>122851741</v>
       </c>
       <c r="B51" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6481,25 +6467,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6507,9 +6493,13 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6517,10 +6507,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584409</v>
+        <v>584357</v>
       </c>
       <c r="R51" t="n">
-        <v>6320920</v>
+        <v>6320937</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6571,7 +6561,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6590,10 +6579,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851562</v>
+        <v>122841855</v>
       </c>
       <c r="B52" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6602,49 +6591,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584415</v>
+        <v>584419</v>
       </c>
       <c r="R52" t="n">
-        <v>6320915</v>
+        <v>6320986</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6671,47 +6652,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122840797</v>
+        <v>122851869</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6744,20 +6714,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584406</v>
+        <v>584369</v>
       </c>
       <c r="R53" t="n">
-        <v>6320860</v>
+        <v>6320904</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6784,36 +6762,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122842080</v>
+        <v>122851829</v>
       </c>
       <c r="B54" t="n">
         <v>98365</v>
@@ -6846,20 +6835,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584434</v>
+        <v>584348</v>
       </c>
       <c r="R54" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6886,36 +6883,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122841855</v>
+        <v>122851469</v>
       </c>
       <c r="B55" t="n">
         <v>98365</v>
@@ -6948,20 +6956,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584419</v>
+        <v>584584</v>
       </c>
       <c r="R55" t="n">
-        <v>6320986</v>
+        <v>6320910</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6988,39 +7004,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851504</v>
+        <v>122851811</v>
       </c>
       <c r="B56" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7029,28 +7056,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -7061,10 +7092,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584532</v>
+        <v>584350</v>
       </c>
       <c r="R56" t="n">
-        <v>6320881</v>
+        <v>6320916</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7134,7 +7165,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851662</v>
+        <v>122841069</v>
       </c>
       <c r="B57" t="n">
         <v>98365</v>
@@ -7167,28 +7198,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584391</v>
+        <v>584349</v>
       </c>
       <c r="R57" t="n">
-        <v>6320923</v>
+        <v>6320925</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7215,19 +7238,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7236,26 +7254,25 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122841518</v>
+        <v>122841088</v>
       </c>
       <c r="B58" t="n">
         <v>98365</v>
@@ -7290,7 +7307,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7305,14 +7322,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584376</v>
+        <v>584332</v>
       </c>
       <c r="R58" t="n">
-        <v>6320937</v>
+        <v>6320935</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7371,7 +7388,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122851862</v>
+        <v>122841533</v>
       </c>
       <c r="B59" t="n">
         <v>98365</v>
@@ -7404,28 +7421,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584360</v>
+        <v>584369</v>
       </c>
       <c r="R59" t="n">
-        <v>6320915</v>
+        <v>6320926</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7452,19 +7461,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7473,29 +7477,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851741</v>
+        <v>122851927</v>
       </c>
       <c r="B60" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7504,39 +7507,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7544,10 +7543,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584357</v>
+        <v>584411</v>
       </c>
       <c r="R60" t="n">
-        <v>6320937</v>
+        <v>6320904</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7598,6 +7597,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122841409</v>
+        <v>122851735</v>
       </c>
       <c r="B18" t="n">
-        <v>57369</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2705,43 +2705,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584384</v>
+        <v>584357</v>
       </c>
       <c r="R18" t="n">
-        <v>6320921</v>
+        <v>6320937</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2771,39 +2774,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851735</v>
+        <v>122841409</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>57369</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2812,46 +2826,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584357</v>
+        <v>584384</v>
       </c>
       <c r="R19" t="n">
-        <v>6320937</v>
+        <v>6320921</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2881,40 +2892,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122839339</v>
+        <v>122851575</v>
       </c>
       <c r="B34" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4543,41 +4543,49 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584548</v>
+        <v>584415</v>
       </c>
       <c r="R34" t="n">
-        <v>6320905</v>
+        <v>6320915</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4604,39 +4612,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122851575</v>
+        <v>122839339</v>
       </c>
       <c r="B35" t="n">
-        <v>98365</v>
+        <v>95136</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4645,49 +4664,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584415</v>
+        <v>584548</v>
       </c>
       <c r="R35" t="n">
-        <v>6320915</v>
+        <v>6320905</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4714,40 +4725,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5776,10 +5776,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122851504</v>
+        <v>122851640</v>
       </c>
       <c r="B45" t="n">
-        <v>95136</v>
+        <v>105471</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5792,24 +5792,28 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -5820,10 +5824,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584532</v>
+        <v>584396</v>
       </c>
       <c r="R45" t="n">
-        <v>6320881</v>
+        <v>6320930</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5893,7 +5897,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851640</v>
+        <v>122851605</v>
       </c>
       <c r="B46" t="n">
         <v>105471</v>
@@ -5928,7 +5932,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5941,10 +5945,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584396</v>
+        <v>584395</v>
       </c>
       <c r="R46" t="n">
-        <v>6320930</v>
+        <v>6320916</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6014,10 +6018,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851605</v>
+        <v>122851504</v>
       </c>
       <c r="B47" t="n">
-        <v>105471</v>
+        <v>95136</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6030,28 +6034,24 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -6062,10 +6062,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584395</v>
+        <v>584532</v>
       </c>
       <c r="R47" t="n">
-        <v>6320916</v>
+        <v>6320881</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6135,7 +6135,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122839190</v>
+        <v>122841582</v>
       </c>
       <c r="B48" t="n">
         <v>98365</v>
@@ -6168,20 +6168,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584581</v>
+        <v>584345</v>
       </c>
       <c r="R48" t="n">
-        <v>6320913</v>
+        <v>6320948</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6225,22 +6239,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122841878</v>
+        <v>122839190</v>
       </c>
       <c r="B49" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6249,41 +6263,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584427</v>
+        <v>584581</v>
       </c>
       <c r="R49" t="n">
-        <v>6320982</v>
+        <v>6320913</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6339,10 +6353,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122841582</v>
+        <v>122841878</v>
       </c>
       <c r="B50" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6351,52 +6365,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584345</v>
+        <v>584427</v>
       </c>
       <c r="R50" t="n">
-        <v>6320948</v>
+        <v>6320982</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6443,22 +6443,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851741</v>
+        <v>122851869</v>
       </c>
       <c r="B51" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6467,39 +6467,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6507,10 +6503,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584357</v>
+        <v>584369</v>
       </c>
       <c r="R51" t="n">
-        <v>6320937</v>
+        <v>6320904</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6561,6 +6557,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6579,7 +6576,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122841855</v>
+        <v>122851829</v>
       </c>
       <c r="B52" t="n">
         <v>98365</v>
@@ -6612,20 +6609,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584419</v>
+        <v>584348</v>
       </c>
       <c r="R52" t="n">
-        <v>6320986</v>
+        <v>6320915</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6652,36 +6657,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851869</v>
+        <v>122851469</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6716,7 +6732,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -6729,10 +6745,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584369</v>
+        <v>584584</v>
       </c>
       <c r="R53" t="n">
-        <v>6320904</v>
+        <v>6320910</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6802,10 +6818,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851829</v>
+        <v>122851741</v>
       </c>
       <c r="B54" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6814,35 +6830,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6850,10 +6870,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584348</v>
+        <v>584357</v>
       </c>
       <c r="R54" t="n">
-        <v>6320915</v>
+        <v>6320937</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6904,7 +6924,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6923,7 +6942,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851469</v>
+        <v>122841855</v>
       </c>
       <c r="B55" t="n">
         <v>98365</v>
@@ -6956,28 +6975,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584584</v>
+        <v>584419</v>
       </c>
       <c r="R55" t="n">
-        <v>6320910</v>
+        <v>6320986</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7004,40 +7015,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2921,7 +2921,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841328</v>
+        <v>122851540</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -2954,20 +2954,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584336</v>
+        <v>584425</v>
       </c>
       <c r="R20" t="n">
-        <v>6320932</v>
+        <v>6320900</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2994,14 +3002,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3010,25 +3023,26 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122851540</v>
+        <v>122841328</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -3061,28 +3075,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584425</v>
+        <v>584336</v>
       </c>
       <c r="R21" t="n">
-        <v>6320900</v>
+        <v>6320932</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3109,19 +3115,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3130,19 +3131,18 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -5776,10 +5776,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122851640</v>
+        <v>122851504</v>
       </c>
       <c r="B45" t="n">
-        <v>105471</v>
+        <v>95136</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5792,28 +5792,24 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -5824,10 +5820,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584396</v>
+        <v>584532</v>
       </c>
       <c r="R45" t="n">
-        <v>6320930</v>
+        <v>6320881</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5897,7 +5893,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851605</v>
+        <v>122851640</v>
       </c>
       <c r="B46" t="n">
         <v>105471</v>
@@ -5932,7 +5928,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5945,10 +5941,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584395</v>
+        <v>584396</v>
       </c>
       <c r="R46" t="n">
-        <v>6320916</v>
+        <v>6320930</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6018,10 +6014,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851504</v>
+        <v>122851605</v>
       </c>
       <c r="B47" t="n">
-        <v>95136</v>
+        <v>105471</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6034,24 +6030,28 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -6062,10 +6062,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584532</v>
+        <v>584395</v>
       </c>
       <c r="R47" t="n">
-        <v>6320881</v>
+        <v>6320916</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6455,10 +6455,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851869</v>
+        <v>122851741</v>
       </c>
       <c r="B51" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6467,35 +6467,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6503,10 +6507,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584369</v>
+        <v>584357</v>
       </c>
       <c r="R51" t="n">
-        <v>6320904</v>
+        <v>6320937</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6557,7 +6561,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6576,7 +6579,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851829</v>
+        <v>122841855</v>
       </c>
       <c r="B52" t="n">
         <v>98365</v>
@@ -6609,28 +6612,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584348</v>
+        <v>584419</v>
       </c>
       <c r="R52" t="n">
-        <v>6320915</v>
+        <v>6320986</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6657,47 +6652,36 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851469</v>
+        <v>122851869</v>
       </c>
       <c r="B53" t="n">
         <v>98365</v>
@@ -6732,7 +6716,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -6745,10 +6729,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584584</v>
+        <v>584369</v>
       </c>
       <c r="R53" t="n">
-        <v>6320910</v>
+        <v>6320904</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6818,10 +6802,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851741</v>
+        <v>122851829</v>
       </c>
       <c r="B54" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6830,39 +6814,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6870,10 +6850,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584357</v>
+        <v>584348</v>
       </c>
       <c r="R54" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6924,6 +6904,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6942,7 +6923,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122841855</v>
+        <v>122851469</v>
       </c>
       <c r="B55" t="n">
         <v>98365</v>
@@ -6975,20 +6956,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584419</v>
+        <v>584584</v>
       </c>
       <c r="R55" t="n">
-        <v>6320986</v>
+        <v>6320910</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7015,29 +7004,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -6135,7 +6135,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122841582</v>
+        <v>122839190</v>
       </c>
       <c r="B48" t="n">
         <v>98365</v>
@@ -6168,34 +6168,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584345</v>
+        <v>584581</v>
       </c>
       <c r="R48" t="n">
-        <v>6320948</v>
+        <v>6320913</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6239,22 +6225,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122839190</v>
+        <v>122841878</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6263,41 +6249,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584581</v>
+        <v>584427</v>
       </c>
       <c r="R49" t="n">
-        <v>6320913</v>
+        <v>6320982</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6353,10 +6339,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122841878</v>
+        <v>122841582</v>
       </c>
       <c r="B50" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6365,38 +6351,52 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584427</v>
+        <v>584345</v>
       </c>
       <c r="R50" t="n">
-        <v>6320982</v>
+        <v>6320948</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6443,12 +6443,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -6135,7 +6135,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122839190</v>
+        <v>122841582</v>
       </c>
       <c r="B48" t="n">
         <v>98365</v>
@@ -6168,20 +6168,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584581</v>
+        <v>584345</v>
       </c>
       <c r="R48" t="n">
-        <v>6320913</v>
+        <v>6320948</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6225,22 +6239,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122841878</v>
+        <v>122839190</v>
       </c>
       <c r="B49" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6249,41 +6263,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584427</v>
+        <v>584581</v>
       </c>
       <c r="R49" t="n">
-        <v>6320982</v>
+        <v>6320913</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6339,10 +6353,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122841582</v>
+        <v>122841878</v>
       </c>
       <c r="B50" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6351,52 +6365,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584345</v>
+        <v>584427</v>
       </c>
       <c r="R50" t="n">
-        <v>6320948</v>
+        <v>6320982</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6443,12 +6443,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851735</v>
+        <v>122839920</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>95139</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2705,49 +2705,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584357</v>
+        <v>584525</v>
       </c>
       <c r="R18" t="n">
-        <v>6320937</v>
+        <v>6320880</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2774,19 +2766,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2795,29 +2782,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122841409</v>
+        <v>122839190</v>
       </c>
       <c r="B19" t="n">
-        <v>57369</v>
+        <v>98368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2826,46 +2812,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584384</v>
+        <v>584581</v>
       </c>
       <c r="R19" t="n">
-        <v>6320921</v>
+        <v>6320913</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2921,10 +2902,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851540</v>
+        <v>122841409</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>57372</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2933,46 +2914,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584425</v>
+        <v>584384</v>
       </c>
       <c r="R20" t="n">
-        <v>6320900</v>
+        <v>6320921</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3002,50 +2980,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122841328</v>
+        <v>122851469</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3075,20 +3042,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584336</v>
+        <v>584584</v>
       </c>
       <c r="R21" t="n">
-        <v>6320932</v>
+        <v>6320910</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3115,14 +3090,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3131,28 +3111,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122840491</v>
+        <v>122841328</v>
       </c>
       <c r="B22" t="n">
-        <v>95136</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3161,41 +3142,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584478</v>
+        <v>584336</v>
       </c>
       <c r="R22" t="n">
-        <v>6320912</v>
+        <v>6320932</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3225,6 +3206,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3239,22 +3225,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122851783</v>
+        <v>122841069</v>
       </c>
       <c r="B23" t="n">
-        <v>57369</v>
+        <v>98368</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3263,53 +3249,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584336</v>
+        <v>584349</v>
       </c>
       <c r="R23" t="n">
-        <v>6320920</v>
+        <v>6320925</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3336,19 +3310,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3363,22 +3332,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122840797</v>
+        <v>122851811</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3408,20 +3377,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584406</v>
+        <v>584350</v>
       </c>
       <c r="R24" t="n">
-        <v>6320860</v>
+        <v>6320916</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3448,39 +3425,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122851724</v>
+        <v>122851869</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3512,7 +3500,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -3525,10 +3513,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584375</v>
+        <v>584369</v>
       </c>
       <c r="R25" t="n">
-        <v>6320924</v>
+        <v>6320904</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3601,7 +3589,7 @@
         <v>122842080</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3700,10 +3688,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122840605</v>
+        <v>122840491</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>95139</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3712,38 +3700,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584384</v>
+        <v>584478</v>
       </c>
       <c r="R27" t="n">
-        <v>6320873</v>
+        <v>6320912</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3790,22 +3778,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122851479</v>
+        <v>122841582</v>
       </c>
       <c r="B28" t="n">
-        <v>58156</v>
+        <v>98368</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3814,53 +3802,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584584</v>
+        <v>584345</v>
       </c>
       <c r="R28" t="n">
-        <v>6320910</v>
+        <v>6320948</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3887,19 +3877,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3914,22 +3894,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122851662</v>
+        <v>122851540</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3961,7 +3941,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3974,10 +3954,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584391</v>
+        <v>584425</v>
       </c>
       <c r="R29" t="n">
-        <v>6320923</v>
+        <v>6320900</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4047,10 +4027,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851716</v>
+        <v>122851927</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4082,7 +4062,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -4095,10 +4075,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584419</v>
+        <v>584411</v>
       </c>
       <c r="R30" t="n">
-        <v>6320935</v>
+        <v>6320904</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4171,7 +4151,7 @@
         <v>122851599</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4289,10 +4269,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851862</v>
+        <v>122851662</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4324,7 +4304,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -4337,10 +4317,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584360</v>
+        <v>584391</v>
       </c>
       <c r="R32" t="n">
-        <v>6320915</v>
+        <v>6320923</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4410,10 +4390,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851562</v>
+        <v>122840279</v>
       </c>
       <c r="B33" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4445,26 +4425,22 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584415</v>
+        <v>584419</v>
       </c>
       <c r="R33" t="n">
-        <v>6320915</v>
+        <v>6320836</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4491,50 +4467,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122851575</v>
+        <v>122840605</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4564,28 +4529,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584415</v>
+        <v>584384</v>
       </c>
       <c r="R34" t="n">
-        <v>6320915</v>
+        <v>6320873</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4612,50 +4569,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122839339</v>
+        <v>122841088</v>
       </c>
       <c r="B35" t="n">
-        <v>95136</v>
+        <v>98368</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4664,41 +4610,55 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584548</v>
+        <v>584332</v>
       </c>
       <c r="R35" t="n">
-        <v>6320905</v>
+        <v>6320935</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4754,10 +4714,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122840763</v>
+        <v>122851623</v>
       </c>
       <c r="B36" t="n">
-        <v>57494</v>
+        <v>98368</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4766,41 +4726,49 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584289</v>
+        <v>584406</v>
       </c>
       <c r="R36" t="n">
-        <v>6320925</v>
+        <v>6320924</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4827,14 +4795,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4843,28 +4816,29 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122839920</v>
+        <v>122851783</v>
       </c>
       <c r="B37" t="n">
-        <v>95136</v>
+        <v>57372</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4873,41 +4847,53 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>100001</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584525</v>
+        <v>584336</v>
       </c>
       <c r="R37" t="n">
-        <v>6320880</v>
+        <v>6320920</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4934,14 +4920,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4956,22 +4947,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122841596</v>
+        <v>122851479</v>
       </c>
       <c r="B38" t="n">
-        <v>57494</v>
+        <v>58159</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4980,20 +4971,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5001,20 +4992,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584389</v>
+        <v>584584</v>
       </c>
       <c r="R38" t="n">
-        <v>6320931</v>
+        <v>6320910</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5041,14 +5044,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5063,22 +5071,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851623</v>
+        <v>122851735</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5110,7 +5118,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -5123,10 +5131,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584406</v>
+        <v>584357</v>
       </c>
       <c r="R39" t="n">
-        <v>6320924</v>
+        <v>6320937</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5196,10 +5204,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851590</v>
+        <v>122851605</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5208,30 +5216,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -5244,10 +5252,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584409</v>
+        <v>584395</v>
       </c>
       <c r="R40" t="n">
-        <v>6320920</v>
+        <v>6320916</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5317,10 +5325,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122851756</v>
+        <v>122841878</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5329,49 +5337,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584359</v>
+        <v>584427</v>
       </c>
       <c r="R41" t="n">
-        <v>6320919</v>
+        <v>6320982</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5398,50 +5398,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122841518</v>
+        <v>122851640</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5450,55 +5439,49 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584376</v>
+        <v>584396</v>
       </c>
       <c r="R42" t="n">
-        <v>6320937</v>
+        <v>6320930</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5525,39 +5508,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122840279</v>
+        <v>122839339</v>
       </c>
       <c r="B43" t="n">
-        <v>105471</v>
+        <v>95139</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5570,41 +5564,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584419</v>
+        <v>584548</v>
       </c>
       <c r="R43" t="n">
-        <v>6320836</v>
+        <v>6320905</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5648,22 +5638,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122841912</v>
+        <v>122841596</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>57497</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5672,55 +5662,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584384</v>
+        <v>584389</v>
       </c>
       <c r="R44" t="n">
-        <v>6320970</v>
+        <v>6320931</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5750,6 +5726,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5764,22 +5745,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122851504</v>
+        <v>122841533</v>
       </c>
       <c r="B45" t="n">
-        <v>95136</v>
+        <v>98368</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5788,45 +5769,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584532</v>
+        <v>584369</v>
       </c>
       <c r="R45" t="n">
-        <v>6320881</v>
+        <v>6320926</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5853,19 +5830,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5874,29 +5846,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122851640</v>
+        <v>122841912</v>
       </c>
       <c r="B46" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5905,49 +5876,55 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584396</v>
+        <v>584384</v>
       </c>
       <c r="R46" t="n">
-        <v>6320930</v>
+        <v>6320970</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5974,50 +5951,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851605</v>
+        <v>122851741</v>
       </c>
       <c r="B47" t="n">
-        <v>105471</v>
+        <v>57851</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6030,31 +5996,35 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6062,10 +6032,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584395</v>
+        <v>584357</v>
       </c>
       <c r="R47" t="n">
-        <v>6320916</v>
+        <v>6320937</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6116,7 +6086,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6135,10 +6104,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122841582</v>
+        <v>122851504</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>95139</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6147,55 +6116,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584345</v>
+        <v>584532</v>
       </c>
       <c r="R48" t="n">
-        <v>6320948</v>
+        <v>6320881</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6222,39 +6181,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122839190</v>
+        <v>122851829</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6284,20 +6254,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584581</v>
+        <v>584348</v>
       </c>
       <c r="R49" t="n">
-        <v>6320913</v>
+        <v>6320915</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6324,39 +6302,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122841878</v>
+        <v>122851575</v>
       </c>
       <c r="B50" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6365,41 +6354,49 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584427</v>
+        <v>584415</v>
       </c>
       <c r="R50" t="n">
-        <v>6320982</v>
+        <v>6320915</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6426,39 +6423,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851741</v>
+        <v>122851562</v>
       </c>
       <c r="B51" t="n">
-        <v>57848</v>
+        <v>105474</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6471,35 +6479,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6507,10 +6511,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584357</v>
+        <v>584415</v>
       </c>
       <c r="R51" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6561,6 +6565,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6579,10 +6584,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122841855</v>
+        <v>122840797</v>
       </c>
       <c r="B52" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6615,17 +6620,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584419</v>
+        <v>584406</v>
       </c>
       <c r="R52" t="n">
-        <v>6320986</v>
+        <v>6320860</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6669,22 +6674,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122851869</v>
+        <v>122841855</v>
       </c>
       <c r="B53" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6714,28 +6719,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584369</v>
+        <v>584419</v>
       </c>
       <c r="R53" t="n">
-        <v>6320904</v>
+        <v>6320986</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6762,50 +6759,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851829</v>
+        <v>122851862</v>
       </c>
       <c r="B54" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6837,7 +6823,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6850,7 +6836,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584348</v>
+        <v>584360</v>
       </c>
       <c r="R54" t="n">
         <v>6320915</v>
@@ -6923,10 +6909,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851469</v>
+        <v>122851724</v>
       </c>
       <c r="B55" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6958,7 +6944,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -6971,10 +6957,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584584</v>
+        <v>584375</v>
       </c>
       <c r="R55" t="n">
-        <v>6320910</v>
+        <v>6320924</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7044,10 +7030,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851811</v>
+        <v>122841518</v>
       </c>
       <c r="B56" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7079,26 +7065,32 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584350</v>
+        <v>584376</v>
       </c>
       <c r="R56" t="n">
-        <v>6320916</v>
+        <v>6320937</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7125,50 +7117,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122841069</v>
+        <v>122851756</v>
       </c>
       <c r="B57" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7198,20 +7179,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584349</v>
+        <v>584359</v>
       </c>
       <c r="R57" t="n">
-        <v>6320925</v>
+        <v>6320919</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7238,14 +7227,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7254,28 +7248,29 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122841088</v>
+        <v>122851590</v>
       </c>
       <c r="B58" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7307,32 +7302,26 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584332</v>
+        <v>584409</v>
       </c>
       <c r="R58" t="n">
-        <v>6320935</v>
+        <v>6320920</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7359,39 +7348,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122841533</v>
+        <v>122851716</v>
       </c>
       <c r="B59" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7421,20 +7421,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584369</v>
+        <v>584419</v>
       </c>
       <c r="R59" t="n">
-        <v>6320926</v>
+        <v>6320935</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7461,14 +7469,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7477,28 +7490,29 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122851927</v>
+        <v>122840763</v>
       </c>
       <c r="B60" t="n">
-        <v>98365</v>
+        <v>57497</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7507,49 +7521,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584411</v>
+        <v>584289</v>
       </c>
       <c r="R60" t="n">
-        <v>6320904</v>
+        <v>6320925</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7576,19 +7582,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7597,19 +7598,18 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122839920</v>
+        <v>122841533</v>
       </c>
       <c r="B18" t="n">
-        <v>95139</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2705,25 +2705,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584525</v>
+        <v>584369</v>
       </c>
       <c r="R18" t="n">
-        <v>6320880</v>
+        <v>6320926</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Stora kuddar</t>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122839190</v>
+        <v>122851756</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2833,20 +2833,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584581</v>
+        <v>584359</v>
       </c>
       <c r="R19" t="n">
-        <v>6320913</v>
+        <v>6320919</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2873,39 +2881,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841409</v>
+        <v>122841855</v>
       </c>
       <c r="B20" t="n">
-        <v>57372</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2914,46 +2933,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584384</v>
+        <v>584419</v>
       </c>
       <c r="R20" t="n">
-        <v>6320921</v>
+        <v>6320986</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3009,10 +3023,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122851469</v>
+        <v>122851724</v>
       </c>
       <c r="B21" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3044,7 +3058,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -3057,10 +3071,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584584</v>
+        <v>584375</v>
       </c>
       <c r="R21" t="n">
-        <v>6320910</v>
+        <v>6320924</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3130,10 +3144,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122841328</v>
+        <v>122841088</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3163,20 +3177,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584336</v>
+        <v>584332</v>
       </c>
       <c r="R22" t="n">
-        <v>6320932</v>
+        <v>6320935</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3206,11 +3234,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3225,22 +3248,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122841069</v>
+        <v>122841328</v>
       </c>
       <c r="B23" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3277,10 +3300,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584349</v>
+        <v>584336</v>
       </c>
       <c r="R23" t="n">
-        <v>6320925</v>
+        <v>6320932</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3317,7 +3340,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>50-tal plantor</t>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3344,10 +3367,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851811</v>
+        <v>122841878</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3356,49 +3379,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584350</v>
+        <v>584427</v>
       </c>
       <c r="R24" t="n">
-        <v>6320916</v>
+        <v>6320982</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3425,50 +3440,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122851869</v>
+        <v>122841912</v>
       </c>
       <c r="B25" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3500,26 +3504,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584369</v>
+        <v>584384</v>
       </c>
       <c r="R25" t="n">
-        <v>6320904</v>
+        <v>6320970</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3546,50 +3556,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122842080</v>
+        <v>122851735</v>
       </c>
       <c r="B26" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3619,20 +3618,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584434</v>
+        <v>584357</v>
       </c>
       <c r="R26" t="n">
         <v>6320937</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3659,39 +3666,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122840491</v>
+        <v>122851811</v>
       </c>
       <c r="B27" t="n">
-        <v>95139</v>
+        <v>98370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3700,41 +3718,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584478</v>
+        <v>584350</v>
       </c>
       <c r="R27" t="n">
-        <v>6320912</v>
+        <v>6320916</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3761,39 +3787,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122841582</v>
+        <v>122851741</v>
       </c>
       <c r="B28" t="n">
-        <v>98368</v>
+        <v>57851</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3802,55 +3839,53 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584345</v>
+        <v>584357</v>
       </c>
       <c r="R28" t="n">
-        <v>6320948</v>
+        <v>6320937</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3877,9 +3912,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3894,22 +3939,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122851540</v>
+        <v>122840491</v>
       </c>
       <c r="B29" t="n">
-        <v>98368</v>
+        <v>95141</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3918,49 +3963,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584425</v>
+        <v>584478</v>
       </c>
       <c r="R29" t="n">
-        <v>6320900</v>
+        <v>6320912</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3987,50 +4024,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851927</v>
+        <v>122839920</v>
       </c>
       <c r="B30" t="n">
-        <v>98368</v>
+        <v>95141</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4039,49 +4065,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584411</v>
+        <v>584525</v>
       </c>
       <c r="R30" t="n">
-        <v>6320904</v>
+        <v>6320880</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4108,19 +4126,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4129,29 +4142,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851599</v>
+        <v>122851829</v>
       </c>
       <c r="B31" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4183,7 +4195,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -4196,10 +4208,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584395</v>
+        <v>584348</v>
       </c>
       <c r="R31" t="n">
-        <v>6320916</v>
+        <v>6320915</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4269,10 +4281,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851662</v>
+        <v>122841409</v>
       </c>
       <c r="B32" t="n">
-        <v>98368</v>
+        <v>57372</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4281,46 +4293,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584391</v>
+        <v>584384</v>
       </c>
       <c r="R32" t="n">
-        <v>6320923</v>
+        <v>6320921</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4350,50 +4359,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122840279</v>
+        <v>122851590</v>
       </c>
       <c r="B33" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4402,45 +4400,49 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584419</v>
+        <v>584409</v>
       </c>
       <c r="R33" t="n">
-        <v>6320836</v>
+        <v>6320920</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4467,39 +4469,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122840605</v>
+        <v>122842080</v>
       </c>
       <c r="B34" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4532,14 +4545,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584384</v>
+        <v>584434</v>
       </c>
       <c r="R34" t="n">
-        <v>6320873</v>
+        <v>6320937</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4598,10 +4611,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122841088</v>
+        <v>122840797</v>
       </c>
       <c r="B35" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4631,31 +4644,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584332</v>
+        <v>584406</v>
       </c>
       <c r="R35" t="n">
-        <v>6320935</v>
+        <v>6320860</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4717,7 +4716,7 @@
         <v>122851623</v>
       </c>
       <c r="B36" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4835,10 +4834,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851783</v>
+        <v>122851640</v>
       </c>
       <c r="B37" t="n">
-        <v>57372</v>
+        <v>105476</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4847,39 +4846,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100001</v>
+        <v>221144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4887,10 +4882,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584336</v>
+        <v>584396</v>
       </c>
       <c r="R37" t="n">
-        <v>6320920</v>
+        <v>6320930</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4941,6 +4936,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4959,10 +4955,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851479</v>
+        <v>122851869</v>
       </c>
       <c r="B38" t="n">
-        <v>58159</v>
+        <v>98370</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4971,39 +4967,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5011,10 +5003,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584584</v>
+        <v>584369</v>
       </c>
       <c r="R38" t="n">
-        <v>6320910</v>
+        <v>6320904</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5065,6 +5057,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5083,10 +5076,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851735</v>
+        <v>122851605</v>
       </c>
       <c r="B39" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5095,30 +5088,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -5131,10 +5124,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584357</v>
+        <v>584395</v>
       </c>
       <c r="R39" t="n">
-        <v>6320937</v>
+        <v>6320916</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5204,10 +5197,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122851605</v>
+        <v>122839339</v>
       </c>
       <c r="B40" t="n">
-        <v>105474</v>
+        <v>95141</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5220,45 +5213,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584395</v>
+        <v>584548</v>
       </c>
       <c r="R40" t="n">
-        <v>6320916</v>
+        <v>6320905</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5285,50 +5270,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122841878</v>
+        <v>122841069</v>
       </c>
       <c r="B41" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5337,41 +5311,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584427</v>
+        <v>584349</v>
       </c>
       <c r="R41" t="n">
-        <v>6320982</v>
+        <v>6320925</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5401,6 +5375,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5427,10 +5406,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122851640</v>
+        <v>122841582</v>
       </c>
       <c r="B42" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5439,49 +5418,55 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584396</v>
+        <v>584345</v>
       </c>
       <c r="R42" t="n">
-        <v>6320930</v>
+        <v>6320948</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5508,50 +5493,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122839339</v>
+        <v>122851504</v>
       </c>
       <c r="B43" t="n">
-        <v>95139</v>
+        <v>95141</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5582,19 +5556,23 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584548</v>
+        <v>584532</v>
       </c>
       <c r="R43" t="n">
-        <v>6320905</v>
+        <v>6320881</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5621,39 +5599,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122841596</v>
+        <v>122851469</v>
       </c>
       <c r="B44" t="n">
-        <v>57497</v>
+        <v>98370</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5662,41 +5651,49 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584389</v>
+        <v>584584</v>
       </c>
       <c r="R44" t="n">
-        <v>6320931</v>
+        <v>6320910</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5723,14 +5720,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5739,28 +5741,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122841533</v>
+        <v>122839190</v>
       </c>
       <c r="B45" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5797,10 +5800,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584369</v>
+        <v>584581</v>
       </c>
       <c r="R45" t="n">
-        <v>6320926</v>
+        <v>6320913</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5833,11 +5836,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5864,10 +5862,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122841912</v>
+        <v>122840605</v>
       </c>
       <c r="B46" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5897,34 +5895,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
         <v>584384</v>
       </c>
       <c r="R46" t="n">
-        <v>6320970</v>
+        <v>6320873</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5968,22 +5952,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851741</v>
+        <v>122851540</v>
       </c>
       <c r="B47" t="n">
-        <v>57851</v>
+        <v>98370</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5992,39 +5976,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6032,10 +6012,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584357</v>
+        <v>584425</v>
       </c>
       <c r="R47" t="n">
-        <v>6320937</v>
+        <v>6320900</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6086,6 +6066,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6104,10 +6085,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851504</v>
+        <v>122851479</v>
       </c>
       <c r="B48" t="n">
-        <v>95139</v>
+        <v>58159</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6120,27 +6101,35 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6148,10 +6137,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584532</v>
+        <v>584584</v>
       </c>
       <c r="R48" t="n">
-        <v>6320881</v>
+        <v>6320910</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6202,7 +6191,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6221,10 +6209,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851829</v>
+        <v>122851716</v>
       </c>
       <c r="B49" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6256,7 +6244,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -6269,10 +6257,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584348</v>
+        <v>584419</v>
       </c>
       <c r="R49" t="n">
-        <v>6320915</v>
+        <v>6320935</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6342,10 +6330,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851575</v>
+        <v>122841596</v>
       </c>
       <c r="B50" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6354,49 +6342,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584415</v>
+        <v>584389</v>
       </c>
       <c r="R50" t="n">
-        <v>6320915</v>
+        <v>6320931</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6423,19 +6403,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6444,29 +6419,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851562</v>
+        <v>122851783</v>
       </c>
       <c r="B51" t="n">
-        <v>105474</v>
+        <v>57372</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6475,35 +6449,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>100001</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6511,10 +6489,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584415</v>
+        <v>584336</v>
       </c>
       <c r="R51" t="n">
-        <v>6320915</v>
+        <v>6320920</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6565,7 +6543,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6584,10 +6561,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122840797</v>
+        <v>122851927</v>
       </c>
       <c r="B52" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6617,20 +6594,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584406</v>
+        <v>584411</v>
       </c>
       <c r="R52" t="n">
-        <v>6320860</v>
+        <v>6320904</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6657,39 +6642,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122841855</v>
+        <v>122841518</v>
       </c>
       <c r="B53" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6719,20 +6715,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584419</v>
+        <v>584376</v>
       </c>
       <c r="R53" t="n">
-        <v>6320986</v>
+        <v>6320937</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6776,22 +6786,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851862</v>
+        <v>122851599</v>
       </c>
       <c r="B54" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6823,7 +6833,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6836,10 +6846,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584360</v>
+        <v>584395</v>
       </c>
       <c r="R54" t="n">
-        <v>6320915</v>
+        <v>6320916</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6909,10 +6919,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851724</v>
+        <v>122851862</v>
       </c>
       <c r="B55" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6944,7 +6954,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -6957,10 +6967,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584375</v>
+        <v>584360</v>
       </c>
       <c r="R55" t="n">
-        <v>6320924</v>
+        <v>6320915</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7030,10 +7040,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122841518</v>
+        <v>122851575</v>
       </c>
       <c r="B56" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7065,32 +7075,26 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584376</v>
+        <v>584415</v>
       </c>
       <c r="R56" t="n">
-        <v>6320937</v>
+        <v>6320915</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7117,39 +7121,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851756</v>
+        <v>122851662</v>
       </c>
       <c r="B57" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7181,7 +7196,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
@@ -7194,10 +7209,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584359</v>
+        <v>584391</v>
       </c>
       <c r="R57" t="n">
-        <v>6320919</v>
+        <v>6320923</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7267,10 +7282,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122851590</v>
+        <v>122851562</v>
       </c>
       <c r="B58" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7279,30 +7294,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
@@ -7315,10 +7330,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584409</v>
+        <v>584415</v>
       </c>
       <c r="R58" t="n">
-        <v>6320920</v>
+        <v>6320915</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7388,10 +7403,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122851716</v>
+        <v>122840763</v>
       </c>
       <c r="B59" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7400,49 +7415,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584419</v>
+        <v>584289</v>
       </c>
       <c r="R59" t="n">
-        <v>6320935</v>
+        <v>6320925</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7469,19 +7476,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7490,29 +7492,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122840763</v>
+        <v>122840279</v>
       </c>
       <c r="B60" t="n">
-        <v>57497</v>
+        <v>105476</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7521,41 +7522,45 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584289</v>
+        <v>584419</v>
       </c>
       <c r="R60" t="n">
-        <v>6320925</v>
+        <v>6320836</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7585,11 +7590,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -4160,10 +4160,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851829</v>
+        <v>122841409</v>
       </c>
       <c r="B31" t="n">
-        <v>98370</v>
+        <v>57372</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4172,46 +4172,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584348</v>
+        <v>584384</v>
       </c>
       <c r="R31" t="n">
-        <v>6320915</v>
+        <v>6320921</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4241,50 +4238,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122841409</v>
+        <v>122851829</v>
       </c>
       <c r="B32" t="n">
-        <v>57372</v>
+        <v>98370</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4293,43 +4279,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584384</v>
+        <v>584348</v>
       </c>
       <c r="R32" t="n">
-        <v>6320921</v>
+        <v>6320915</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4359,29 +4348,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122840797</v>
+        <v>122851623</v>
       </c>
       <c r="B35" t="n">
         <v>98370</v>
@@ -4644,20 +4644,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
         <v>584406</v>
       </c>
       <c r="R35" t="n">
-        <v>6320860</v>
+        <v>6320924</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4684,36 +4692,47 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122851623</v>
+        <v>122840797</v>
       </c>
       <c r="B36" t="n">
         <v>98370</v>
@@ -4746,28 +4765,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
         <v>584406</v>
       </c>
       <c r="R36" t="n">
-        <v>6320924</v>
+        <v>6320860</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4794,40 +4805,29 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851479</v>
+        <v>122851783</v>
       </c>
       <c r="B48" t="n">
-        <v>58159</v>
+        <v>57372</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6097,20 +6097,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103044</v>
+        <v>100001</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584584</v>
+        <v>584336</v>
       </c>
       <c r="R48" t="n">
-        <v>6320910</v>
+        <v>6320920</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6209,10 +6209,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851716</v>
+        <v>122841596</v>
       </c>
       <c r="B49" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6221,49 +6221,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584419</v>
+        <v>584389</v>
       </c>
       <c r="R49" t="n">
-        <v>6320935</v>
+        <v>6320931</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6290,19 +6282,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6311,29 +6298,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122841596</v>
+        <v>122851479</v>
       </c>
       <c r="B50" t="n">
-        <v>57497</v>
+        <v>58159</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6342,20 +6328,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6363,20 +6349,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584389</v>
+        <v>584584</v>
       </c>
       <c r="R50" t="n">
-        <v>6320931</v>
+        <v>6320910</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6403,14 +6401,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6425,22 +6428,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851783</v>
+        <v>122851716</v>
       </c>
       <c r="B51" t="n">
-        <v>57372</v>
+        <v>98370</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6449,39 +6452,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6489,10 +6488,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584336</v>
+        <v>584419</v>
       </c>
       <c r="R51" t="n">
-        <v>6320920</v>
+        <v>6320935</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6543,6 +6542,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -2693,10 +2693,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122841533</v>
+        <v>122851590</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2726,20 +2726,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584369</v>
+        <v>584409</v>
       </c>
       <c r="R18" t="n">
-        <v>6320926</v>
+        <v>6320920</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2766,14 +2774,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2782,28 +2795,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851756</v>
+        <v>122842080</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2833,28 +2847,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584359</v>
+        <v>584434</v>
       </c>
       <c r="R19" t="n">
-        <v>6320919</v>
+        <v>6320937</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2881,50 +2887,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122841855</v>
+        <v>122851735</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2954,20 +2949,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584419</v>
+        <v>584357</v>
       </c>
       <c r="R20" t="n">
-        <v>6320986</v>
+        <v>6320937</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2994,39 +2997,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122851724</v>
+        <v>122851662</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3058,7 +3072,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -3071,10 +3085,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584375</v>
+        <v>584391</v>
       </c>
       <c r="R21" t="n">
-        <v>6320924</v>
+        <v>6320923</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3144,10 +3158,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122841088</v>
+        <v>122851829</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3179,32 +3193,26 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584332</v>
+        <v>584348</v>
       </c>
       <c r="R22" t="n">
-        <v>6320935</v>
+        <v>6320915</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3231,39 +3239,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122841328</v>
+        <v>122851540</v>
       </c>
       <c r="B23" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3293,20 +3312,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584336</v>
+        <v>584425</v>
       </c>
       <c r="R23" t="n">
-        <v>6320932</v>
+        <v>6320900</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3333,14 +3360,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3349,28 +3381,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122841878</v>
+        <v>122851927</v>
       </c>
       <c r="B24" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3379,41 +3412,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584427</v>
+        <v>584411</v>
       </c>
       <c r="R24" t="n">
-        <v>6320982</v>
+        <v>6320904</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3440,39 +3481,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122841912</v>
+        <v>122841855</v>
       </c>
       <c r="B25" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3502,31 +3554,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584384</v>
+        <v>584419</v>
       </c>
       <c r="R25" t="n">
-        <v>6320970</v>
+        <v>6320986</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3573,22 +3611,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122851735</v>
+        <v>122851869</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3620,7 +3658,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -3633,10 +3671,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584357</v>
+        <v>584369</v>
       </c>
       <c r="R26" t="n">
-        <v>6320937</v>
+        <v>6320904</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3706,10 +3744,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851811</v>
+        <v>122851756</v>
       </c>
       <c r="B27" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3741,7 +3779,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -3754,10 +3792,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584350</v>
+        <v>584359</v>
       </c>
       <c r="R27" t="n">
-        <v>6320916</v>
+        <v>6320919</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3827,10 +3865,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122851741</v>
+        <v>122851469</v>
       </c>
       <c r="B28" t="n">
-        <v>57851</v>
+        <v>98376</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3839,39 +3877,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3879,10 +3913,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584357</v>
+        <v>584584</v>
       </c>
       <c r="R28" t="n">
-        <v>6320937</v>
+        <v>6320910</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3933,6 +3967,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3951,10 +3986,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122840491</v>
+        <v>122841518</v>
       </c>
       <c r="B29" t="n">
-        <v>95141</v>
+        <v>98376</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3963,38 +3998,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584478</v>
+        <v>584376</v>
       </c>
       <c r="R29" t="n">
-        <v>6320912</v>
+        <v>6320937</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4053,10 +4102,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122839920</v>
+        <v>122841088</v>
       </c>
       <c r="B30" t="n">
-        <v>95141</v>
+        <v>98376</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4065,41 +4114,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584525</v>
+        <v>584332</v>
       </c>
       <c r="R30" t="n">
-        <v>6320880</v>
+        <v>6320935</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4129,11 +4192,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4148,22 +4206,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122841409</v>
+        <v>122840279</v>
       </c>
       <c r="B31" t="n">
-        <v>57372</v>
+        <v>105482</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4172,31 +4230,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100001</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4205,13 +4262,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584384</v>
+        <v>584419</v>
       </c>
       <c r="R31" t="n">
-        <v>6320921</v>
+        <v>6320836</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4267,10 +4324,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851829</v>
+        <v>122851562</v>
       </c>
       <c r="B32" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4279,30 +4336,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -4315,7 +4372,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584348</v>
+        <v>584415</v>
       </c>
       <c r="R32" t="n">
         <v>6320915</v>
@@ -4388,10 +4445,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851590</v>
+        <v>122851811</v>
       </c>
       <c r="B33" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4423,7 +4480,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4436,10 +4493,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584409</v>
+        <v>584350</v>
       </c>
       <c r="R33" t="n">
-        <v>6320920</v>
+        <v>6320916</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4509,10 +4566,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122842080</v>
+        <v>122841582</v>
       </c>
       <c r="B34" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4542,20 +4599,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584434</v>
+        <v>584345</v>
       </c>
       <c r="R34" t="n">
-        <v>6320937</v>
+        <v>6320948</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4599,12 +4670,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4614,7 +4685,7 @@
         <v>122851623</v>
       </c>
       <c r="B35" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4732,10 +4803,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122840797</v>
+        <v>122851724</v>
       </c>
       <c r="B36" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4765,20 +4836,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584406</v>
+        <v>584375</v>
       </c>
       <c r="R36" t="n">
-        <v>6320860</v>
+        <v>6320924</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4805,39 +4884,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851640</v>
+        <v>122851504</v>
       </c>
       <c r="B37" t="n">
-        <v>105476</v>
+        <v>95147</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4850,28 +4940,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -4882,10 +4968,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584396</v>
+        <v>584532</v>
       </c>
       <c r="R37" t="n">
-        <v>6320930</v>
+        <v>6320881</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4955,10 +5041,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851869</v>
+        <v>122851862</v>
       </c>
       <c r="B38" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4990,7 +5076,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5003,10 +5089,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584369</v>
+        <v>584360</v>
       </c>
       <c r="R38" t="n">
-        <v>6320904</v>
+        <v>6320915</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5076,10 +5162,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851605</v>
+        <v>122840797</v>
       </c>
       <c r="B39" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5088,49 +5174,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584395</v>
+        <v>584406</v>
       </c>
       <c r="R39" t="n">
-        <v>6320916</v>
+        <v>6320860</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5157,50 +5235,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122839339</v>
+        <v>122851640</v>
       </c>
       <c r="B40" t="n">
-        <v>95141</v>
+        <v>105482</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5213,37 +5280,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584548</v>
+        <v>584396</v>
       </c>
       <c r="R40" t="n">
-        <v>6320905</v>
+        <v>6320930</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5270,39 +5345,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122841069</v>
+        <v>122841878</v>
       </c>
       <c r="B41" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5311,41 +5397,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>584349</v>
+        <v>584427</v>
       </c>
       <c r="R41" t="n">
-        <v>6320925</v>
+        <v>6320982</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5375,11 +5461,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5406,10 +5487,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122841582</v>
+        <v>122841533</v>
       </c>
       <c r="B42" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5439,34 +5520,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584345</v>
+        <v>584369</v>
       </c>
       <c r="R42" t="n">
-        <v>6320948</v>
+        <v>6320926</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5496,6 +5563,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5510,22 +5582,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851504</v>
+        <v>122851783</v>
       </c>
       <c r="B43" t="n">
-        <v>95141</v>
+        <v>57372</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5534,31 +5606,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>100001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5566,10 +5646,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584532</v>
+        <v>584336</v>
       </c>
       <c r="R43" t="n">
-        <v>6320881</v>
+        <v>6320920</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5620,7 +5700,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5639,10 +5718,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122851469</v>
+        <v>122841069</v>
       </c>
       <c r="B44" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5672,28 +5751,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584584</v>
+        <v>584349</v>
       </c>
       <c r="R44" t="n">
-        <v>6320910</v>
+        <v>6320925</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5720,19 +5791,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5741,29 +5807,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122839190</v>
+        <v>122851599</v>
       </c>
       <c r="B45" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5793,20 +5858,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584581</v>
+        <v>584395</v>
       </c>
       <c r="R45" t="n">
-        <v>6320913</v>
+        <v>6320916</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5833,39 +5906,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122840605</v>
+        <v>122851575</v>
       </c>
       <c r="B46" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5895,20 +5979,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584384</v>
+        <v>584415</v>
       </c>
       <c r="R46" t="n">
-        <v>6320873</v>
+        <v>6320915</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5935,39 +6027,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851540</v>
+        <v>122851741</v>
       </c>
       <c r="B47" t="n">
-        <v>98370</v>
+        <v>57851</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5976,35 +6079,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6012,10 +6119,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584425</v>
+        <v>584357</v>
       </c>
       <c r="R47" t="n">
-        <v>6320900</v>
+        <v>6320937</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6066,7 +6173,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6085,10 +6191,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122851783</v>
+        <v>122841328</v>
       </c>
       <c r="B48" t="n">
-        <v>57372</v>
+        <v>98376</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6097,53 +6203,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
         <v>584336</v>
       </c>
       <c r="R48" t="n">
-        <v>6320920</v>
+        <v>6320932</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6170,19 +6264,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6197,22 +6286,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122841596</v>
+        <v>122851716</v>
       </c>
       <c r="B49" t="n">
-        <v>57497</v>
+        <v>98376</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6221,41 +6310,49 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584389</v>
+        <v>584419</v>
       </c>
       <c r="R49" t="n">
-        <v>6320931</v>
+        <v>6320935</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6282,14 +6379,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6298,28 +6400,29 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851479</v>
+        <v>122840491</v>
       </c>
       <c r="B50" t="n">
-        <v>58159</v>
+        <v>95147</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6332,49 +6435,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584584</v>
+        <v>584478</v>
       </c>
       <c r="R50" t="n">
-        <v>6320910</v>
+        <v>6320912</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6401,19 +6492,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6428,22 +6509,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122851716</v>
+        <v>122840605</v>
       </c>
       <c r="B51" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6473,28 +6554,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584419</v>
+        <v>584384</v>
       </c>
       <c r="R51" t="n">
-        <v>6320935</v>
+        <v>6320873</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6521,50 +6594,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122851927</v>
+        <v>122839339</v>
       </c>
       <c r="B52" t="n">
-        <v>98370</v>
+        <v>95147</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6573,49 +6635,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584411</v>
+        <v>584548</v>
       </c>
       <c r="R52" t="n">
-        <v>6320904</v>
+        <v>6320905</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6642,50 +6696,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122841518</v>
+        <v>122841596</v>
       </c>
       <c r="B53" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6694,55 +6737,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584376</v>
+        <v>584389</v>
       </c>
       <c r="R53" t="n">
-        <v>6320937</v>
+        <v>6320931</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6772,6 +6801,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6786,22 +6820,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851599</v>
+        <v>122840763</v>
       </c>
       <c r="B54" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6810,49 +6844,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584395</v>
+        <v>584289</v>
       </c>
       <c r="R54" t="n">
-        <v>6320916</v>
+        <v>6320925</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6879,19 +6905,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6900,29 +6921,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851862</v>
+        <v>122839190</v>
       </c>
       <c r="B55" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6952,28 +6972,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584360</v>
+        <v>584581</v>
       </c>
       <c r="R55" t="n">
-        <v>6320915</v>
+        <v>6320913</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7000,50 +7012,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851575</v>
+        <v>122841409</v>
       </c>
       <c r="B56" t="n">
-        <v>98370</v>
+        <v>57372</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7052,46 +7053,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584415</v>
+        <v>584384</v>
       </c>
       <c r="R56" t="n">
-        <v>6320915</v>
+        <v>6320921</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7121,50 +7119,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122851662</v>
+        <v>122841912</v>
       </c>
       <c r="B57" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7196,26 +7183,32 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584391</v>
+        <v>584384</v>
       </c>
       <c r="R57" t="n">
-        <v>6320923</v>
+        <v>6320970</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7242,50 +7235,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122851562</v>
+        <v>122851479</v>
       </c>
       <c r="B58" t="n">
-        <v>105476</v>
+        <v>58159</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7298,31 +7280,35 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>103044</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7330,10 +7316,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584415</v>
+        <v>584584</v>
       </c>
       <c r="R58" t="n">
-        <v>6320915</v>
+        <v>6320910</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7384,7 +7370,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7403,10 +7388,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122840763</v>
+        <v>122839920</v>
       </c>
       <c r="B59" t="n">
-        <v>57497</v>
+        <v>95147</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7415,25 +7400,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7443,13 +7428,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584289</v>
+        <v>584525</v>
       </c>
       <c r="R59" t="n">
-        <v>6320925</v>
+        <v>6320880</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7483,7 +7468,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7510,10 +7495,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122840279</v>
+        <v>122851605</v>
       </c>
       <c r="B60" t="n">
-        <v>105476</v>
+        <v>105482</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7545,22 +7530,26 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584419</v>
+        <v>584395</v>
       </c>
       <c r="R60" t="n">
-        <v>6320836</v>
+        <v>6320916</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7587,29 +7576,40 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>7027702</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584380.5569586717</v>
+        <v>584381</v>
       </c>
       <c r="R2" t="n">
-        <v>6320858.679572098</v>
+        <v>6320859</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2013-11-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-11-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7027684</v>
+        <v>101406049</v>
       </c>
       <c r="B3" t="n">
-        <v>95523</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,33 +788,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224364</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kronobäck, Sm</t>
+          <t>Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584510.8754677951</v>
+        <v>584515</v>
       </c>
       <c r="R3" t="n">
-        <v>6320915.233249085</v>
+        <v>6320890</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,22 +854,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-09-01</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-09-01</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,60 +878,56 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99699204</v>
+        <v>107655842</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -943,26 +935,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Sm</t>
+          <t>Ljungnäs 3:3, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584306.078387014</v>
+        <v>584349</v>
       </c>
       <c r="R4" t="n">
-        <v>6320899.63009485</v>
+        <v>6320884</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,64 +1007,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99699337</v>
+        <v>122839339</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584306.078387014</v>
+        <v>584548</v>
       </c>
       <c r="R5" t="n">
-        <v>6320899.63009485</v>
+        <v>6320905</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,22 +1072,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1086,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1153,66 +1104,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99699175</v>
+        <v>122839529</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Sm</t>
+          <t>Ljungnäs, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584351.9162082712</v>
+        <v>584541</v>
       </c>
       <c r="R6" t="n">
-        <v>6320898.929273628</v>
+        <v>6320862</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,22 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,88 +1183,66 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99699223</v>
+        <v>122839627</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584410.0630933376</v>
+        <v>584531</v>
       </c>
       <c r="R7" t="n">
-        <v>6320909.912643597</v>
+        <v>6320858</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1368,22 +1266,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1280,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1411,69 +1298,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99699277</v>
+        <v>122839920</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584374.6191337948</v>
+        <v>584525</v>
       </c>
       <c r="R8" t="n">
-        <v>6320909.191067031</v>
+        <v>6320880</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1497,22 +1363,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stora kuddar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,85 +1382,63 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99699238</v>
+        <v>122840491</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Sm</t>
+          <t>Gränsborg, Gränsborg, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584407.8265212175</v>
+        <v>584478</v>
       </c>
       <c r="R9" t="n">
-        <v>6320912.589254811</v>
+        <v>6320912</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1626,22 +1465,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-04-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1650,7 +1479,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1669,69 +1497,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101363594</v>
+        <v>122851504</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584428.0022988572</v>
+        <v>584532</v>
       </c>
       <c r="R10" t="n">
-        <v>6320913.000123005</v>
+        <v>6320881</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1755,22 +1566,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,67 +1597,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101363640</v>
+        <v>99699337</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1854,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584451.7380804347</v>
+        <v>584306</v>
       </c>
       <c r="R11" t="n">
-        <v>6320899.328395869</v>
+        <v>6320899</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1884,22 +1685,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>2022-04-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>2022-04-06</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1927,66 +1728,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101363610</v>
+        <v>122841954</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584432.4021916448</v>
+        <v>584450</v>
       </c>
       <c r="R12" t="n">
-        <v>6320964.810312384</v>
+        <v>6321001</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2013,22 +1797,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2037,7 +1811,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2056,69 +1829,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101363565</v>
+        <v>122841409</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584377.9130383781</v>
+        <v>584384</v>
       </c>
       <c r="R13" t="n">
-        <v>6320908.169250936</v>
+        <v>6320921</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2142,22 +1899,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2166,88 +1913,78 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101363539</v>
+        <v>122851783</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584376.1971004778</v>
+        <v>584336</v>
       </c>
       <c r="R14" t="n">
-        <v>6320885.268168774</v>
+        <v>6320920</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2271,22 +2008,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2295,88 +2032,78 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101363672</v>
+        <v>122852007</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584580.8281712161</v>
+        <v>584646</v>
       </c>
       <c r="R15" t="n">
-        <v>6320909.037915515</v>
+        <v>6320922</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2400,22 +2127,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2424,34 +2151,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101406049</v>
+        <v>122840763</v>
       </c>
       <c r="B16" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2459,49 +2180,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584515.2028820309</v>
+        <v>584289</v>
       </c>
       <c r="R16" t="n">
-        <v>6320890.277585</v>
+        <v>6320925</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2525,22 +2234,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2549,34 +2253,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107655842</v>
+        <v>122841596</v>
       </c>
       <c r="B17" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2584,49 +2282,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ljungnäs 3:3, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584348.9434296748</v>
+        <v>584389</v>
       </c>
       <c r="R17" t="n">
-        <v>6320884.169098743</v>
+        <v>6320931</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2650,22 +2336,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2674,34 +2355,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122851479</v>
+        <v>122852003</v>
       </c>
       <c r="B18" t="n">
-        <v>58159</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,16 +2384,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2728,14 +2403,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2745,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584584</v>
+        <v>584646</v>
       </c>
       <c r="R18" t="n">
-        <v>6320910</v>
+        <v>6320922</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2817,47 +2492,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122851756</v>
+        <v>122851741</v>
       </c>
       <c r="B19" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2865,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584359</v>
+        <v>584357</v>
       </c>
       <c r="R19" t="n">
-        <v>6320919</v>
+        <v>6320937</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2919,7 +2593,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2938,47 +2611,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122851735</v>
+        <v>122851479</v>
       </c>
       <c r="B20" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2986,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584357</v>
+        <v>584584</v>
       </c>
       <c r="R20" t="n">
-        <v>6320937</v>
+        <v>6320910</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3040,7 +2712,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3059,57 +2730,64 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122851504</v>
+        <v>99699175</v>
       </c>
       <c r="B21" t="n">
-        <v>95150</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584532</v>
+        <v>584352</v>
       </c>
       <c r="R21" t="n">
-        <v>6320881</v>
+        <v>6320899</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3133,22 +2811,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-04-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-04-06</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3164,73 +2842,76 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122851605</v>
+        <v>99699204</v>
       </c>
       <c r="B22" t="n">
-        <v>105485</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584395</v>
+        <v>584306</v>
       </c>
       <c r="R22" t="n">
-        <v>6320916</v>
+        <v>6320899</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3254,22 +2935,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-04-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-04-06</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3285,27 +2966,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122841328</v>
+        <v>99699223</v>
       </c>
       <c r="B23" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3330,20 +3006,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584336</v>
+        <v>584410</v>
       </c>
       <c r="R23" t="n">
-        <v>6320932</v>
+        <v>6320910</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3367,17 +3059,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-04-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>40-tal plantor</t>
+          <t>2022-04-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3386,83 +3083,83 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122851741</v>
+        <v>99699238</v>
       </c>
       <c r="B24" t="n">
-        <v>57851</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584357</v>
+        <v>584408</v>
       </c>
       <c r="R24" t="n">
-        <v>6320937</v>
+        <v>6320913</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3486,22 +3183,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-04-06</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-04-06</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3510,33 +3207,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122841533</v>
+        <v>99699277</v>
       </c>
       <c r="B25" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3561,20 +3254,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584369</v>
+        <v>584375</v>
       </c>
       <c r="R25" t="n">
-        <v>6320926</v>
+        <v>6320909</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3598,17 +3307,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-04-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>100-tal plantor</t>
+          <t>2022-04-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3617,33 +3331,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122851662</v>
+        <v>101363539</v>
       </c>
       <c r="B26" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3670,26 +3380,34 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584391</v>
+        <v>584376</v>
       </c>
       <c r="R26" t="n">
-        <v>6320923</v>
+        <v>6320886</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3713,22 +3431,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3744,73 +3462,76 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122851562</v>
+        <v>101363565</v>
       </c>
       <c r="B27" t="n">
-        <v>105485</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584415</v>
+        <v>584378</v>
       </c>
       <c r="R27" t="n">
-        <v>6320915</v>
+        <v>6320908</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3834,22 +3555,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3865,62 +3586,73 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122840491</v>
+        <v>101363594</v>
       </c>
       <c r="B28" t="n">
-        <v>95150</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gränsborg, Gränsborg, Sm</t>
+          <t>Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584478</v>
+        <v>584428</v>
       </c>
       <c r="R28" t="n">
-        <v>6320912</v>
+        <v>6320913</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3947,12 +3679,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-06-02</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-06-02</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3961,6 +3703,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3979,53 +3722,64 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122839339</v>
+        <v>101363610</v>
       </c>
       <c r="B29" t="n">
-        <v>95150</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>584548</v>
+        <v>584432</v>
       </c>
       <c r="R29" t="n">
-        <v>6320905</v>
+        <v>6320965</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4049,12 +3803,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-06-02</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-06-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4063,6 +3827,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4081,15 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122851590</v>
+        <v>101363640</v>
       </c>
       <c r="B30" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4116,26 +3876,34 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584409</v>
+        <v>584452</v>
       </c>
       <c r="R30" t="n">
-        <v>6320920</v>
+        <v>6320899</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4159,7 +3927,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -4169,7 +3937,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4190,27 +3958,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122851829</v>
+        <v>101363672</v>
       </c>
       <c r="B31" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4237,26 +4000,34 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>584348</v>
+        <v>584581</v>
       </c>
       <c r="R31" t="n">
-        <v>6320915</v>
+        <v>6320909</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4280,22 +4051,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4311,27 +4082,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122851623</v>
+        <v>122839190</v>
       </c>
       <c r="B32" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4356,28 +4122,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>584406</v>
+        <v>584581</v>
       </c>
       <c r="R32" t="n">
-        <v>6320924</v>
+        <v>6320913</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4404,55 +4162,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122851540</v>
+        <v>122840605</v>
       </c>
       <c r="B33" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4477,28 +4219,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>584425</v>
+        <v>584384</v>
       </c>
       <c r="R33" t="n">
-        <v>6320900</v>
+        <v>6320873</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4525,55 +4259,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122842080</v>
+        <v>122840797</v>
       </c>
       <c r="B34" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4601,14 +4319,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Spetalehult, Spetalehult, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>584434</v>
+        <v>584406</v>
       </c>
       <c r="R34" t="n">
-        <v>6320937</v>
+        <v>6320860</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4655,27 +4373,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122841518</v>
+        <v>122841069</v>
       </c>
       <c r="B35" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4700,34 +4413,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>584376</v>
+        <v>584349</v>
       </c>
       <c r="R35" t="n">
-        <v>6320937</v>
+        <v>6320925</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4757,6 +4456,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4771,27 +4475,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122840605</v>
+        <v>122841088</v>
       </c>
       <c r="B36" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4816,17 +4515,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>584384</v>
+        <v>584332</v>
       </c>
       <c r="R36" t="n">
-        <v>6320873</v>
+        <v>6320935</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4873,27 +4586,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122851862</v>
+        <v>122841328</v>
       </c>
       <c r="B37" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4918,28 +4626,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584360</v>
+        <v>584336</v>
       </c>
       <c r="R37" t="n">
-        <v>6320915</v>
+        <v>6320932</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4966,19 +4666,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>40-tal plantor</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4987,34 +4682,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122851575</v>
+        <v>122841518</v>
       </c>
       <c r="B38" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5041,26 +4730,32 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>584415</v>
+        <v>584376</v>
       </c>
       <c r="R38" t="n">
-        <v>6320915</v>
+        <v>6320937</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5087,55 +4782,39 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122851724</v>
+        <v>122841533</v>
       </c>
       <c r="B39" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5160,28 +4839,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Västra hult, Västra hult, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>584375</v>
+        <v>584369</v>
       </c>
       <c r="R39" t="n">
-        <v>6320924</v>
+        <v>6320926</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5208,19 +4879,14 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5229,34 +4895,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122841088</v>
+        <v>122841582</v>
       </c>
       <c r="B40" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5283,7 +4943,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5298,17 +4958,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Oknebäck 3.3, Oknebäck 3.3, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>584332</v>
+        <v>584345</v>
       </c>
       <c r="R40" t="n">
-        <v>6320935</v>
+        <v>6320948</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5364,57 +5024,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122840279</v>
+        <v>122841855</v>
       </c>
       <c r="B41" t="n">
-        <v>105485</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
         <v>584419</v>
       </c>
       <c r="R41" t="n">
-        <v>6320836</v>
+        <v>6320986</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5470,50 +5121,59 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122841878</v>
+        <v>122841912</v>
       </c>
       <c r="B42" t="n">
-        <v>105485</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584427</v>
+        <v>584384</v>
       </c>
       <c r="R42" t="n">
-        <v>6320982</v>
+        <v>6320970</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5560,77 +5220,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122851783</v>
+        <v>122842080</v>
       </c>
       <c r="B43" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Oknöbäck, Mörkeskog, Sm</t>
+          <t>Vidflagen, Vidflagen, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584336</v>
+        <v>584434</v>
       </c>
       <c r="R43" t="n">
-        <v>6320920</v>
+        <v>6320937</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5657,19 +5300,9 @@
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5684,27 +5317,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122841912</v>
+        <v>122851469</v>
       </c>
       <c r="B44" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5731,32 +5359,26 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584384</v>
+        <v>584584</v>
       </c>
       <c r="R44" t="n">
-        <v>6320970</v>
+        <v>6320910</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5783,44 +5405,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122839190</v>
+        <v>122851540</v>
       </c>
       <c r="B45" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5845,20 +5473,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>584581</v>
+        <v>584425</v>
       </c>
       <c r="R45" t="n">
-        <v>6320913</v>
+        <v>6320900</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5885,44 +5521,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122841069</v>
+        <v>122851575</v>
       </c>
       <c r="B46" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5947,20 +5589,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>584349</v>
+        <v>584415</v>
       </c>
       <c r="R46" t="n">
-        <v>6320925</v>
+        <v>6320915</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5987,14 +5637,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6003,33 +5658,29 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122851469</v>
+        <v>122851590</v>
       </c>
       <c r="B47" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6056,7 +5707,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -6069,10 +5720,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>584584</v>
+        <v>584409</v>
       </c>
       <c r="R47" t="n">
-        <v>6320910</v>
+        <v>6320920</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6142,53 +5793,56 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122840763</v>
+        <v>122851599</v>
       </c>
       <c r="B48" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>584289</v>
+        <v>584395</v>
       </c>
       <c r="R48" t="n">
-        <v>6320925</v>
+        <v>6320916</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6215,14 +5869,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6231,60 +5890,56 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122851640</v>
+        <v>122851623</v>
       </c>
       <c r="B49" t="n">
-        <v>105485</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -6297,10 +5952,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>584396</v>
+        <v>584406</v>
       </c>
       <c r="R49" t="n">
-        <v>6320930</v>
+        <v>6320924</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6370,15 +6025,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122851869</v>
+        <v>122851662</v>
       </c>
       <c r="B50" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6405,7 +6055,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -6418,10 +6068,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>584369</v>
+        <v>584391</v>
       </c>
       <c r="R50" t="n">
-        <v>6320904</v>
+        <v>6320923</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6491,53 +6141,56 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122841596</v>
+        <v>122851716</v>
       </c>
       <c r="B51" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>584389</v>
+        <v>584419</v>
       </c>
       <c r="R51" t="n">
-        <v>6320931</v>
+        <v>6320935</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6564,14 +6217,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6580,71 +6238,75 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122839920</v>
+        <v>122851724</v>
       </c>
       <c r="B52" t="n">
-        <v>95150</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>584525</v>
+        <v>584375</v>
       </c>
       <c r="R52" t="n">
-        <v>6320880</v>
+        <v>6320924</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6671,14 +6333,19 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Stora kuddar</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6687,33 +6354,29 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122840797</v>
+        <v>122851735</v>
       </c>
       <c r="B53" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6738,20 +6401,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Spetalehult, Spetalehult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>584406</v>
+        <v>584357</v>
       </c>
       <c r="R53" t="n">
-        <v>6320860</v>
+        <v>6320937</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6778,44 +6449,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122851927</v>
+        <v>122851756</v>
       </c>
       <c r="B54" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6842,7 +6519,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6855,10 +6532,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>584411</v>
+        <v>584359</v>
       </c>
       <c r="R54" t="n">
-        <v>6320904</v>
+        <v>6320919</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6928,15 +6605,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122851716</v>
+        <v>122851811</v>
       </c>
       <c r="B55" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6963,7 +6635,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -6976,10 +6648,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>584419</v>
+        <v>584350</v>
       </c>
       <c r="R55" t="n">
-        <v>6320935</v>
+        <v>6320916</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7049,15 +6721,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122851599</v>
+        <v>122851829</v>
       </c>
       <c r="B56" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7084,7 +6751,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -7097,10 +6764,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>584395</v>
+        <v>584348</v>
       </c>
       <c r="R56" t="n">
-        <v>6320916</v>
+        <v>6320915</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7170,15 +6837,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122841582</v>
+        <v>122851862</v>
       </c>
       <c r="B57" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7205,32 +6867,26 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Oknebäck 3:3, Oknebäck 3:3, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>584345</v>
+        <v>584360</v>
       </c>
       <c r="R57" t="n">
-        <v>6320948</v>
+        <v>6320915</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7257,44 +6913,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122841855</v>
+        <v>122851869</v>
       </c>
       <c r="B58" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7319,20 +6981,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vidflagen, Vidflagen, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>584419</v>
+        <v>584369</v>
       </c>
       <c r="R58" t="n">
-        <v>6320986</v>
+        <v>6320904</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7359,44 +7029,50 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122851811</v>
+        <v>122851918</v>
       </c>
       <c r="B59" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7436,10 +7112,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>584350</v>
+        <v>584390</v>
       </c>
       <c r="R59" t="n">
-        <v>6320916</v>
+        <v>6320982</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7509,55 +7185,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122841409</v>
+        <v>122851927</v>
       </c>
       <c r="B60" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100001</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Västra hult, Västra hult, Sm</t>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>584384</v>
+        <v>584411</v>
       </c>
       <c r="R60" t="n">
-        <v>6320921</v>
+        <v>6320904</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7587,32 +7261,682 @@
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-03-02</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>122840279</v>
+      </c>
+      <c r="B61" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Västra hult, Västra hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>584419</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6320836</v>
+      </c>
+      <c r="S61" t="n">
+        <v>20</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
+      <c r="AX61" t="inlineStr">
         <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY60" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>122841878</v>
+      </c>
+      <c r="B62" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Vidflagen, Vidflagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>584427</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6320982</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>122851562</v>
+      </c>
+      <c r="B63" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>584415</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6320915</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>122851605</v>
+      </c>
+      <c r="B64" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>584395</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6320916</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>122851640</v>
+      </c>
+      <c r="B65" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Oknöbäck, Mörkeskog, Sm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>584396</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6320930</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>7027684</v>
+      </c>
+      <c r="B66" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kronobäck, Sm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>584511</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6320915</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2013-09-01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2013-09-01</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3290-2025 artfynd.xlsx
+++ b/artfynd/A 3290-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7027702</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101406049</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107655842</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122839339</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122839529</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122839627</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1397,6 +1432,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122839920</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1494,6 +1534,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122840491</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1606,6 +1651,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851504</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,6 +1775,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99699337</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1826,6 +1881,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122841954</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1928,6 +1988,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122841409</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2047,6 +2112,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851783</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2166,6 +2236,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122852007</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2268,6 +2343,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122840763</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2370,6 +2450,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122841596</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2489,6 +2574,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122852003</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2608,6 +2698,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851741</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2727,6 +2822,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851479</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2851,6 +2951,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99699175</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2975,6 +3080,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99699204</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3099,6 +3209,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99699223</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3223,6 +3338,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99699238</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3347,6 +3467,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99699277</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3471,6 +3596,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101363539</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3595,6 +3725,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101363565</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3719,6 +3854,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101363594</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3843,6 +3983,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101363610</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3967,6 +4112,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101363640</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4091,6 +4241,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101363672</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4188,6 +4343,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122839190</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4285,6 +4445,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122840605</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4382,6 +4547,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122840797</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4484,6 +4654,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122841069</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4595,6 +4770,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122841088</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4697,6 +4877,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122841328</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4808,6 +4993,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122841518</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4910,6 +5100,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122841533</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5021,6 +5216,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122841582</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5118,6 +5318,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122841855</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5229,6 +5434,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122841912</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5326,6 +5536,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122842080</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5442,6 +5657,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851469</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5558,6 +5778,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851540</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5674,6 +5899,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851575</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5790,6 +6020,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851590</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5906,6 +6141,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851599</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6022,6 +6262,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851623</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6138,6 +6383,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851662</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6254,6 +6504,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851716</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6370,6 +6625,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851724</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6486,6 +6746,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851735</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6602,6 +6867,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851756</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6718,6 +6988,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851811</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6834,6 +7109,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851829</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6950,6 +7230,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851862</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7066,6 +7351,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851869</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7182,6 +7472,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851918</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7298,6 +7593,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851927</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7399,6 +7699,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122840279</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7496,6 +7801,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122841878</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7612,6 +7922,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851562</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7728,6 +8043,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851605</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7844,6 +8164,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122851640</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7937,8 +8262,80 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7027684</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>